--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -9,19 +9,20 @@
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Summary"/>
     <sheet r:id="rId2" sheetId="2" name="Settings"/>
-    <sheet r:id="rId3" sheetId="3" name="2026-02-25"/>
-    <sheet r:id="rId4" sheetId="4" name="2026-02-05"/>
-    <sheet r:id="rId5" sheetId="5" name="2026-02-04"/>
-    <sheet r:id="rId6" sheetId="6" name="2026-02-03"/>
-    <sheet r:id="rId7" sheetId="7" name="2026-02-02"/>
-    <sheet r:id="rId8" sheetId="8" name="2026-02-01"/>
+    <sheet r:id="rId3" sheetId="3" name="2026-02-26"/>
+    <sheet r:id="rId4" sheetId="4" name="2026-02-25"/>
+    <sheet r:id="rId5" sheetId="5" name="2026-02-05"/>
+    <sheet r:id="rId6" sheetId="6" name="2026-02-04"/>
+    <sheet r:id="rId7" sheetId="7" name="2026-02-03"/>
+    <sheet r:id="rId8" sheetId="8" name="2026-02-02"/>
+    <sheet r:id="rId9" sheetId="9" name="2026-02-01"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="174">
   <si>
     <t>game_date</t>
   </si>
@@ -410,6 +411,24 @@
     <t>Smith</t>
   </si>
   <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>Johansson</t>
+  </si>
+  <si>
+    <t>Shesterkin</t>
+  </si>
+  <si>
+    <t>Ersson</t>
+  </si>
+  <si>
+    <t>Grubauer</t>
+  </si>
+  <si>
+    <t>Kuemper</t>
+  </si>
+  <si>
     <t>BETTING TRACKER SETTINGS</t>
   </si>
   <si>
@@ -657,23 +676,20 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -683,6 +699,9 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1019,10 +1038,10 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+        <v>148</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
       <c r="D1" s="22"/>
       <c r="E1" s="5"/>
     </row>
@@ -1035,10 +1054,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
@@ -1053,7 +1072,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
       <c r="A5" s="23" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1069,7 +1088,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B7" s="5">
         <v>25</v>
@@ -1080,7 +1099,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B8" s="5">
         <v>11</v>
@@ -1091,7 +1110,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B9" s="5">
         <v>14</v>
@@ -1102,7 +1121,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B10" s="5">
         <v>0</v>
@@ -1113,10 +1132,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -1124,7 +1143,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B12" s="5">
         <v>-2.84</v>
@@ -1135,10 +1154,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -1160,7 +1179,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="16.5">
       <c r="A16" s="23" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1169,19 +1188,19 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>150</v>
-      </c>
       <c r="E17" s="21" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
@@ -1195,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
@@ -1212,10 +1231,10 @@
         <v>2</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
@@ -1229,10 +1248,10 @@
         <v>5</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -1246,10 +1265,10 @@
         <v>2</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -1263,10 +1282,10 @@
         <v>2</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -1280,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1308,7 +1327,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="19" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B1" s="5"/>
     </row>
@@ -1318,15 +1337,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="20" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -1334,7 +1353,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B5" s="5">
         <v>55</v>
@@ -1342,7 +1361,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B6" s="5">
         <v>65</v>
@@ -1350,7 +1369,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B7" s="5">
         <v>2</v>
@@ -1362,15 +1381,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B10" s="5">
         <v>-110</v>
@@ -1382,15 +1401,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B13" s="5">
         <v>89</v>
@@ -1402,6 +1421,2504 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:W40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+  </cols>
+  <sheetData>
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="13">
+        <v>2025020918</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-121</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-102</v>
+      </c>
+      <c r="H2" s="13">
+        <v>8478007</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="L2" s="14">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M2" s="14">
+        <v>0.3704989850521088</v>
+      </c>
+      <c r="N2" s="14">
+        <v>25.90020370483398</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="14">
+        <v>0.124550461769104</v>
+      </c>
+      <c r="R2" s="15">
+        <v>1</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2025020918</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F3" s="13">
+        <v>-121</v>
+      </c>
+      <c r="G3" s="13">
+        <v>-103</v>
+      </c>
+      <c r="H3" s="13">
+        <v>8476914</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="13">
+        <v>1</v>
+      </c>
+      <c r="L3" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="M3" s="14">
+        <v>0.3032204508781433</v>
+      </c>
+      <c r="N3" s="14">
+        <v>39.35591125488281</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q3" s="14">
+        <v>0.1893903613090515</v>
+      </c>
+      <c r="R3" s="15">
+        <v>1</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="13">
+        <v>2025020919</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="F4" s="13">
+        <v>-115</v>
+      </c>
+      <c r="G4" s="13">
+        <v>-107</v>
+      </c>
+      <c r="H4" s="13">
+        <v>8478009</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="M4" s="14">
+        <v>0.4902715384960175</v>
+      </c>
+      <c r="N4" s="14">
+        <v>1.945692300796509</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>-0.007179796695709229</v>
+      </c>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2025020919</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F5" s="13">
+        <v>-104</v>
+      </c>
+      <c r="G5" s="13">
+        <v>-118</v>
+      </c>
+      <c r="H5" s="13">
+        <v>8478470</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="13">
+        <v>1</v>
+      </c>
+      <c r="L5" s="14">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M5" s="14">
+        <v>0.5576304793357849</v>
+      </c>
+      <c r="N5" s="14">
+        <v>11.52609634399414</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>0.04782652854919434</v>
+      </c>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2025020921</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="F6" s="13">
+        <v>-124</v>
+      </c>
+      <c r="G6" s="13">
+        <v>101</v>
+      </c>
+      <c r="H6" s="13">
+        <v>8479361</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="M6" s="14">
+        <v>0.5010877251625061</v>
+      </c>
+      <c r="N6" s="14">
+        <v>0.2175450325012207</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="14">
+        <v>0.001399844884872437</v>
+      </c>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="13">
+        <v>2025020921</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F7" s="13">
+        <v>-117</v>
+      </c>
+      <c r="G7" s="13">
+        <v>-106</v>
+      </c>
+      <c r="H7" s="13">
+        <v>8475683</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="13">
+        <v>1</v>
+      </c>
+      <c r="L7" s="14">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M7" s="14">
+        <v>0.661739706993103</v>
+      </c>
+      <c r="N7" s="14">
+        <v>32.34794235229492</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q7" s="14">
+        <v>0.12256920337677</v>
+      </c>
+      <c r="R7" s="15">
+        <v>1</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2025020923</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="14">
+        <v>26.5</v>
+      </c>
+      <c r="F8" s="13">
+        <v>100</v>
+      </c>
+      <c r="G8" s="13">
+        <v>-122</v>
+      </c>
+      <c r="H8" s="13">
+        <v>8477992</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="14">
+        <v>26.29999923706055</v>
+      </c>
+      <c r="M8" s="14">
+        <v>0.4696636497974396</v>
+      </c>
+      <c r="N8" s="14">
+        <v>6.067270278930664</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>-0.01921314001083374</v>
+      </c>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" s="13">
+        <v>2025020923</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F9" s="13">
+        <v>-113</v>
+      </c>
+      <c r="G9" s="13">
+        <v>-109</v>
+      </c>
+      <c r="H9" s="13">
+        <v>8483548</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="13">
+        <v>1</v>
+      </c>
+      <c r="L9" s="14">
+        <v>21.89999961853027</v>
+      </c>
+      <c r="M9" s="14">
+        <v>0.5783803462982178</v>
+      </c>
+      <c r="N9" s="14">
+        <v>15.67606925964355</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="14">
+        <v>0.04786390066146851</v>
+      </c>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="13">
+        <v>2025020922</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F10" s="13">
+        <v>-120</v>
+      </c>
+      <c r="G10" s="13">
+        <v>-104</v>
+      </c>
+      <c r="H10" s="13">
+        <v>8474593</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M10" s="14">
+        <v>0.6511525511741638</v>
+      </c>
+      <c r="N10" s="14">
+        <v>30.23051071166992</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="14">
+        <v>0.1056979894638062</v>
+      </c>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="13">
+        <v>2025020922</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F11" s="13">
+        <v>-117</v>
+      </c>
+      <c r="G11" s="13">
+        <v>-105</v>
+      </c>
+      <c r="H11" s="13">
+        <v>8481668</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="13">
+        <v>1</v>
+      </c>
+      <c r="L11" s="14">
+        <v>23.70000076293945</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0.5480008125305176</v>
+      </c>
+      <c r="N11" s="14">
+        <v>9.600162506103516</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="14">
+        <v>0.00883030891418457</v>
+      </c>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="13">
+        <v>2025020920</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="14">
+        <v>22.5</v>
+      </c>
+      <c r="F12" s="13">
+        <v>-108</v>
+      </c>
+      <c r="G12" s="13">
+        <v>-114</v>
+      </c>
+      <c r="H12" s="13">
+        <v>8476999</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="13">
+        <v>1</v>
+      </c>
+      <c r="L12" s="14">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M12" s="14">
+        <v>0.7264260053634644</v>
+      </c>
+      <c r="N12" s="14">
+        <v>45.28520202636719</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>0.2071952223777771</v>
+      </c>
+      <c r="R12" s="15">
+        <v>1</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13" s="13">
+        <v>2025020926</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F13" s="13">
+        <v>-112</v>
+      </c>
+      <c r="G13" s="13">
+        <v>-110</v>
+      </c>
+      <c r="H13" s="13">
+        <v>8481519</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="14">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M13" s="14">
+        <v>0.5337061882019043</v>
+      </c>
+      <c r="N13" s="14">
+        <v>6.741237640380859</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>0.005404293537139893</v>
+      </c>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2025020924</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F14" s="13">
+        <v>-107</v>
+      </c>
+      <c r="G14" s="13">
+        <v>-114</v>
+      </c>
+      <c r="H14" s="13">
+        <v>8478048</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="13">
+        <v>1</v>
+      </c>
+      <c r="L14" s="14">
+        <v>23.39999961853027</v>
+      </c>
+      <c r="M14" s="14">
+        <v>0.4856701791286469</v>
+      </c>
+      <c r="N14" s="14">
+        <v>2.86596417427063</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q14" s="14">
+        <v>-0.01838046312332153</v>
+      </c>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="13">
+        <v>2025020924</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F15" s="13">
+        <v>-120</v>
+      </c>
+      <c r="G15" s="13">
+        <v>-103</v>
+      </c>
+      <c r="H15" s="13">
+        <v>8481035</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="13">
+        <v>0</v>
+      </c>
+      <c r="L15" s="14">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M15" s="14">
+        <v>0.5326305031776428</v>
+      </c>
+      <c r="N15" s="14">
+        <v>6.526100635528564</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q15" s="14">
+        <v>-0.01282405853271484</v>
+      </c>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="13">
+        <v>2025020925</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>22.5</v>
+      </c>
+      <c r="F16" s="13">
+        <v>-103</v>
+      </c>
+      <c r="G16" s="13">
+        <v>-121</v>
+      </c>
+      <c r="H16" s="13">
+        <v>8480981</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="13">
+        <v>1</v>
+      </c>
+      <c r="L16" s="14">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M16" s="14">
+        <v>0.5612866878509521</v>
+      </c>
+      <c r="N16" s="14">
+        <v>12.25733757019043</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q16" s="14">
+        <v>0.05389750003814697</v>
+      </c>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="13">
+        <v>2025020925</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F17" s="13">
+        <v>-122</v>
+      </c>
+      <c r="G17" s="13">
+        <v>100</v>
+      </c>
+      <c r="H17" s="13">
+        <v>8475831</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14">
+        <v>23.39999961853027</v>
+      </c>
+      <c r="M17" s="14">
+        <v>0.4898507595062256</v>
+      </c>
+      <c r="N17" s="14">
+        <v>2.029848098754883</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" s="14">
+        <v>0.01014924049377441</v>
+      </c>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="13">
+        <v>2025020927</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="14">
+        <v>28.5</v>
+      </c>
+      <c r="F18" s="13">
+        <v>-124</v>
+      </c>
+      <c r="G18" s="13">
+        <v>101</v>
+      </c>
+      <c r="H18" s="13">
+        <v>8479406</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="13">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
+        <v>28</v>
+      </c>
+      <c r="M18" s="14">
+        <v>0.4081594049930573</v>
+      </c>
+      <c r="N18" s="14">
+        <v>18.36811828613281</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q18" s="14">
+        <v>0.09432819485664368</v>
+      </c>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="13">
+        <v>2025020927</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F19" s="13">
+        <v>100</v>
+      </c>
+      <c r="G19" s="13">
+        <v>-122</v>
+      </c>
+      <c r="H19" s="13">
+        <v>8478406</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="13">
+        <v>1</v>
+      </c>
+      <c r="L19" s="14">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M19" s="14">
+        <v>0.3616914749145508</v>
+      </c>
+      <c r="N19" s="14">
+        <v>27.66170501708984</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q19" s="14">
+        <v>0.08875900506973267</v>
+      </c>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="13">
+        <v>2025020928</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F20" s="13">
+        <v>-115</v>
+      </c>
+      <c r="G20" s="13">
+        <v>-107</v>
+      </c>
+      <c r="H20" s="13">
+        <v>8482137</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K20" s="13">
+        <v>1</v>
+      </c>
+      <c r="L20" s="14">
+        <v>25.79999923706055</v>
+      </c>
+      <c r="M20" s="14">
+        <v>0.5628782510757446</v>
+      </c>
+      <c r="N20" s="14">
+        <v>12.57565021514893</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q20" s="14">
+        <v>0.02799451351165771</v>
+      </c>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="13">
+        <v>2025020928</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="F21" s="13">
+        <v>-104</v>
+      </c>
+      <c r="G21" s="13">
+        <v>-120</v>
+      </c>
+      <c r="H21" s="13">
+        <v>8481692</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="14">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M21" s="14">
+        <v>0.5284911394119263</v>
+      </c>
+      <c r="N21" s="14">
+        <v>5.698227882385254</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q21" s="14">
+        <v>0.01868718862533569</v>
+      </c>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="13">
+        <v>2025020929</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F22" s="13">
+        <v>-122</v>
+      </c>
+      <c r="G22" s="13">
+        <v>100</v>
+      </c>
+      <c r="H22" s="13">
+        <v>8478971</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="M22" s="14">
+        <v>0.5004458427429199</v>
+      </c>
+      <c r="N22" s="14">
+        <v>0.08916854858398438</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q22" s="14">
+        <v>-0.0004458427429199219</v>
+      </c>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="13">
+        <v>2025020929</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F23" s="13">
+        <v>-107</v>
+      </c>
+      <c r="G23" s="13">
+        <v>-115</v>
+      </c>
+      <c r="H23" s="13">
+        <v>8475311</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="13">
+        <v>1</v>
+      </c>
+      <c r="L23" s="14">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="M23" s="14">
+        <v>0.6448423266410828</v>
+      </c>
+      <c r="N23" s="14">
+        <v>28.96846580505371</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>0.1279340982437134</v>
+      </c>
+      <c r="R23" s="15">
+        <v>1</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="13">
+        <v>2025020918</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F24" s="13">
+        <v>-122</v>
+      </c>
+      <c r="G24" s="13">
+        <v>-106</v>
+      </c>
+      <c r="H24" s="13">
+        <v>8476914</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="13">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="M24" s="14">
+        <v>0.3032204508781433</v>
+      </c>
+      <c r="N24" s="14">
+        <v>39.35591125488281</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q24" s="14">
+        <v>0.182216465473175</v>
+      </c>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="13">
+        <v>2025020918</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="F25" s="13">
+        <v>-123</v>
+      </c>
+      <c r="G25" s="13">
+        <v>-105</v>
+      </c>
+      <c r="H25" s="13">
+        <v>8478007</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="14">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M25" s="14">
+        <v>0.3704989850521088</v>
+      </c>
+      <c r="N25" s="14">
+        <v>25.90020370483398</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q25" s="14">
+        <v>0.1173058748245239</v>
+      </c>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="13">
+        <v>2025020923</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F26" s="13">
+        <v>-116</v>
+      </c>
+      <c r="G26" s="13">
+        <v>-111</v>
+      </c>
+      <c r="H26" s="13">
+        <v>8483548</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="13">
+        <v>1</v>
+      </c>
+      <c r="L26" s="14">
+        <v>21.89999961853027</v>
+      </c>
+      <c r="M26" s="14">
+        <v>0.5783803462982178</v>
+      </c>
+      <c r="N26" s="14">
+        <v>15.67606925964355</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q26" s="14">
+        <v>0.0413433313369751</v>
+      </c>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="13">
+        <v>2025020923</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="14">
+        <v>26.5</v>
+      </c>
+      <c r="F27" s="13">
+        <v>100</v>
+      </c>
+      <c r="G27" s="13">
+        <v>-130</v>
+      </c>
+      <c r="H27" s="13">
+        <v>8477992</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="14">
+        <v>26.29999923706055</v>
+      </c>
+      <c r="M27" s="14">
+        <v>0.4696636497974396</v>
+      </c>
+      <c r="N27" s="14">
+        <v>6.067270278930664</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q27" s="14">
+        <v>-0.03033635020256042</v>
+      </c>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="13">
+        <v>2025020920</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="14">
+        <v>22.5</v>
+      </c>
+      <c r="F28" s="13">
+        <v>-109</v>
+      </c>
+      <c r="G28" s="13">
+        <v>-119</v>
+      </c>
+      <c r="H28" s="13">
+        <v>8476999</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="K28" s="13">
+        <v>1</v>
+      </c>
+      <c r="L28" s="14">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M28" s="14">
+        <v>0.7264260053634644</v>
+      </c>
+      <c r="N28" s="14">
+        <v>45.28520202636719</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q28" s="14">
+        <v>0.2048949003219604</v>
+      </c>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="13">
+        <v>2025020921</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F29" s="13">
+        <v>-119</v>
+      </c>
+      <c r="G29" s="13">
+        <v>-109</v>
+      </c>
+      <c r="H29" s="13">
+        <v>8475683</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="14">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M29" s="14">
+        <v>0.661739706993103</v>
+      </c>
+      <c r="N29" s="14">
+        <v>32.34794235229492</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q29" s="14">
+        <v>0.118360698223114</v>
+      </c>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="13">
+        <v>2025020921</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="F30" s="13">
+        <v>-128</v>
+      </c>
+      <c r="G30" s="13">
+        <v>-101</v>
+      </c>
+      <c r="H30" s="13">
+        <v>8479361</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K30" s="13">
+        <v>0</v>
+      </c>
+      <c r="L30" s="14">
+        <v>27.5</v>
+      </c>
+      <c r="M30" s="14">
+        <v>0.5010877251625061</v>
+      </c>
+      <c r="N30" s="14">
+        <v>0.2175450325012207</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q30" s="14">
+        <v>-0.003575265407562256</v>
+      </c>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="13">
+        <v>2025020926</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F31" s="13">
+        <v>-112</v>
+      </c>
+      <c r="G31" s="13">
+        <v>-115</v>
+      </c>
+      <c r="H31" s="13">
+        <v>8481519</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" s="13">
+        <v>0</v>
+      </c>
+      <c r="L31" s="14">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M31" s="14">
+        <v>0.5337061882019043</v>
+      </c>
+      <c r="N31" s="14">
+        <v>6.741237640380859</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q31" s="14">
+        <v>0.005404293537139893</v>
+      </c>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2025020924</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F32" s="13">
+        <v>-108</v>
+      </c>
+      <c r="G32" s="13">
+        <v>-120</v>
+      </c>
+      <c r="H32" s="13">
+        <v>8478048</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="14">
+        <v>23.39999961853027</v>
+      </c>
+      <c r="M32" s="14">
+        <v>0.4856701791286469</v>
+      </c>
+      <c r="N32" s="14">
+        <v>2.86596417427063</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q32" s="14">
+        <v>-0.0311247706413269</v>
+      </c>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="13">
+        <v>2025020924</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F33" s="13">
+        <v>-123</v>
+      </c>
+      <c r="G33" s="13">
+        <v>-105</v>
+      </c>
+      <c r="H33" s="13">
+        <v>8481035</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="K33" s="13">
+        <v>0</v>
+      </c>
+      <c r="L33" s="14">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M33" s="14">
+        <v>0.5326305031776428</v>
+      </c>
+      <c r="N33" s="14">
+        <v>6.526100635528564</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q33" s="14">
+        <v>-0.01893901824951172</v>
+      </c>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+      <c r="A34" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="13">
+        <v>2025020923</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E34" s="14">
+        <v>21.5</v>
+      </c>
+      <c r="F34" s="13">
+        <v>-115</v>
+      </c>
+      <c r="G34" s="13">
+        <v>-112</v>
+      </c>
+      <c r="H34" s="13">
+        <v>8483548</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" s="13">
+        <v>1</v>
+      </c>
+      <c r="L34" s="14">
+        <v>21.89999961853027</v>
+      </c>
+      <c r="M34" s="14">
+        <v>0.5783803462982178</v>
+      </c>
+      <c r="N34" s="14">
+        <v>15.67606925964355</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q34" s="14">
+        <v>0.04349660873413086</v>
+      </c>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4"/>
+      <c r="V34" s="4"/>
+      <c r="W34" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+      <c r="A35" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="13">
+        <v>2025020919</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F35" s="13">
+        <v>-108</v>
+      </c>
+      <c r="G35" s="13">
+        <v>-120</v>
+      </c>
+      <c r="H35" s="13">
+        <v>8478470</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="14">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M35" s="14">
+        <v>0.5576304793357849</v>
+      </c>
+      <c r="N35" s="14">
+        <v>11.52609634399414</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q35" s="14">
+        <v>0.03839969635009766</v>
+      </c>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4"/>
+      <c r="V35" s="4"/>
+      <c r="W35" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+      <c r="A36" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="13">
+        <v>2025020919</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="F36" s="13">
+        <v>-118</v>
+      </c>
+      <c r="G36" s="13">
+        <v>-110</v>
+      </c>
+      <c r="H36" s="13">
+        <v>8478009</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" s="13">
+        <v>0</v>
+      </c>
+      <c r="L36" s="14">
+        <v>24.5</v>
+      </c>
+      <c r="M36" s="14">
+        <v>0.4902715384960175</v>
+      </c>
+      <c r="N36" s="14">
+        <v>1.945692300796509</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q36" s="14">
+        <v>-0.01408112049102783</v>
+      </c>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+      <c r="A37" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="13">
+        <v>2025020927</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="14">
+        <v>28.5</v>
+      </c>
+      <c r="F37" s="13">
+        <v>-123</v>
+      </c>
+      <c r="G37" s="13">
+        <v>-104</v>
+      </c>
+      <c r="H37" s="13">
+        <v>8479406</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
+        <v>28</v>
+      </c>
+      <c r="M37" s="14">
+        <v>0.4081594049930573</v>
+      </c>
+      <c r="N37" s="14">
+        <v>18.36811828613281</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q37" s="14">
+        <v>0.08203667402267456</v>
+      </c>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+      <c r="A38" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="13">
+        <v>2025020927</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F38" s="13">
+        <v>100</v>
+      </c>
+      <c r="G38" s="13">
+        <v>-130</v>
+      </c>
+      <c r="H38" s="13">
+        <v>8478406</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="14">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M38" s="14">
+        <v>0.3616914749145508</v>
+      </c>
+      <c r="N38" s="14">
+        <v>27.66170501708984</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q38" s="14">
+        <v>0.07309114933013916</v>
+      </c>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="13">
+        <v>2025020929</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="F39" s="13">
+        <v>-125</v>
+      </c>
+      <c r="G39" s="13">
+        <v>-103</v>
+      </c>
+      <c r="H39" s="13">
+        <v>8478971</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K39" s="13">
+        <v>0</v>
+      </c>
+      <c r="L39" s="14">
+        <v>23.5</v>
+      </c>
+      <c r="M39" s="14">
+        <v>0.5004458427429199</v>
+      </c>
+      <c r="N39" s="14">
+        <v>0.08916854858398438</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q39" s="14">
+        <v>-0.007835030555725098</v>
+      </c>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+      <c r="A40" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="13">
+        <v>2025020929</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E40" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="F40" s="13">
+        <v>-105</v>
+      </c>
+      <c r="G40" s="13">
+        <v>-123</v>
+      </c>
+      <c r="H40" s="13">
+        <v>8475311</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K40" s="13">
+        <v>1</v>
+      </c>
+      <c r="L40" s="14">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="M40" s="14">
+        <v>0.6448423266410828</v>
+      </c>
+      <c r="N40" s="14">
+        <v>28.96846580505371</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q40" s="14">
+        <v>0.1326472163200378</v>
+      </c>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -1426,82 +3943,82 @@
     <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="V1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1509,7 +4026,7 @@
       <c r="A2" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="13">
         <v>2025020910</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1518,16 +4035,16 @@
       <c r="D2" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="14">
         <v>26.5</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="13">
         <v>-113</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="13">
         <v>-109</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="13">
         <v>8480045</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -1536,16 +4053,16 @@
       <c r="J2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="K2" s="10">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12">
+      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="L2" s="14">
         <v>26.29999923706055</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="14">
         <v>0.4507197141647339</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="14">
         <v>9.856057167053223</v>
       </c>
       <c r="O2" s="4" t="s">
@@ -1554,23 +4071,29 @@
       <c r="P2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="14">
         <v>0.02774918079376221</v>
       </c>
-      <c r="R2" s="16"/>
+      <c r="R2" s="15"/>
       <c r="S2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="T2" s="13">
+        <v>27</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="13">
+        <v>0</v>
+      </c>
       <c r="W2" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="13">
         <v>2025020910</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1579,16 +4102,16 @@
       <c r="D3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="14">
         <v>22.5</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="13">
         <v>-104</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="13">
         <v>-118</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="13">
         <v>8474596</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -1597,16 +4120,16 @@
       <c r="J3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="13">
         <v>1</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="14">
         <v>23.5</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="14">
         <v>0.7082683444023132</v>
       </c>
-      <c r="N3" s="12">
+      <c r="N3" s="14">
         <v>41.65366744995117</v>
       </c>
       <c r="O3" s="4" t="s">
@@ -1615,25 +4138,31 @@
       <c r="P3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="14">
         <v>0.1984643936157227</v>
       </c>
-      <c r="R3" s="10">
+      <c r="R3" s="13">
         <v>1</v>
       </c>
       <c r="S3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
+      <c r="T3" s="13">
+        <v>28</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V3" s="14">
+        <v>0.9615384615384617</v>
+      </c>
       <c r="W3" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="13">
         <v>2025020911</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -1642,16 +4171,16 @@
       <c r="D4" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="14">
         <v>23.5</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="13">
         <v>-118</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="13">
         <v>-105</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="13">
         <v>8478435</v>
       </c>
       <c r="I4" s="4" t="s">
@@ -1660,16 +4189,16 @@
       <c r="J4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12">
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14">
         <v>22.79999923706055</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="14">
         <v>0.3667729794979095</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="14">
         <v>26.64540481567383</v>
       </c>
       <c r="O4" s="4" t="s">
@@ -1678,25 +4207,31 @@
       <c r="P4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="Q4" s="14">
         <v>0.1210318803787231</v>
       </c>
-      <c r="R4" s="10">
+      <c r="R4" s="13">
         <v>1</v>
       </c>
       <c r="S4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
+      <c r="T4" s="13">
+        <v>26</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" s="13">
+        <v>-1</v>
+      </c>
       <c r="W4" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="13">
         <v>2025020911</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -1705,16 +4240,16 @@
       <c r="D5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="14">
         <v>22.5</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <v>-106</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="13">
         <v>-117</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="13">
         <v>8480313</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -1723,16 +4258,16 @@
       <c r="J5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="13">
         <v>1</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="14">
         <v>22.70000076293945</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="14">
         <v>0.5496154427528381</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="14">
         <v>9.923088073730469</v>
       </c>
       <c r="O5" s="4" t="s">
@@ -1741,23 +4276,29 @@
       <c r="P5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="12">
+      <c r="Q5" s="14">
         <v>0.03505235910415649</v>
       </c>
-      <c r="R5" s="16"/>
+      <c r="R5" s="15"/>
       <c r="S5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
+      <c r="T5" s="13">
+        <v>23</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V5" s="13">
+        <v>0</v>
+      </c>
       <c r="W5" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="13">
         <v>2025020912</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1766,16 +4307,16 @@
       <c r="D6" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="14">
         <v>26.5</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="13">
         <v>-109</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="13">
         <v>-113</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="13">
         <v>8476932</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -1784,16 +4325,16 @@
       <c r="J6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="12">
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
         <v>26.5</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="14">
         <v>0.494999498128891</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="14">
         <v>1.000100374221802</v>
       </c>
       <c r="O6" s="4" t="s">
@@ -1802,23 +4343,29 @@
       <c r="P6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="14">
         <v>-0.02551597356796265</v>
       </c>
-      <c r="R6" s="16"/>
+      <c r="R6" s="15"/>
       <c r="S6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
+      <c r="T6" s="13">
+        <v>32</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V6" s="13">
+        <v>0</v>
+      </c>
       <c r="W6" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="13">
         <v>2025020913</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1827,16 +4374,16 @@
       <c r="D7" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>21.5</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="13">
         <v>-107</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="13">
         <v>-115</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="13">
         <v>8479193</v>
       </c>
       <c r="I7" s="4" t="s">
@@ -1845,16 +4392,16 @@
       <c r="J7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="13">
         <v>1</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="14">
         <v>21.20000076293945</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="14">
         <v>0.4462916254997253</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="14">
         <v>10.74167442321777</v>
       </c>
       <c r="O7" s="4" t="s">
@@ -1863,23 +4410,29 @@
       <c r="P7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="12">
+      <c r="Q7" s="14">
         <v>0.01882463693618774</v>
       </c>
-      <c r="R7" s="16"/>
+      <c r="R7" s="15"/>
       <c r="S7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="T7" s="13">
+        <v>18</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V7" s="13">
+        <v>0</v>
+      </c>
       <c r="W7" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="13">
         <v>2025020914</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1888,16 +4441,16 @@
       <c r="D8" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="14">
         <v>23.5</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="13">
         <v>102</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="13">
         <v>-125</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="13">
         <v>8475809</v>
       </c>
       <c r="I8" s="4" t="s">
@@ -1906,16 +4459,16 @@
       <c r="J8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="12">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="14">
         <v>23.60000038146973</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="14">
         <v>0.5182401537895203</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="14">
         <v>3.648030757904053</v>
       </c>
       <c r="O8" s="4" t="s">
@@ -1924,23 +4477,29 @@
       <c r="P8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="12">
+      <c r="Q8" s="14">
         <v>0.02319064736366272</v>
       </c>
-      <c r="R8" s="16"/>
+      <c r="R8" s="15"/>
       <c r="S8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+      <c r="T8" s="13">
+        <v>28</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V8" s="13">
+        <v>0</v>
+      </c>
       <c r="W8" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="13">
         <v>2025020914</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -1949,16 +4508,16 @@
       <c r="D9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>26.5</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="13">
         <v>-105</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="13">
         <v>-117</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="13">
         <v>8478872</v>
       </c>
       <c r="I9" s="4" t="s">
@@ -1967,16 +4526,16 @@
       <c r="J9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="13">
         <v>1</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="14">
         <v>25.70000076293945</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="14">
         <v>0.3436546325683594</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="14">
         <v>31.26907348632812</v>
       </c>
       <c r="O9" s="4" t="s">
@@ -1985,23 +4544,29 @@
       <c r="P9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="14">
         <v>0.1171748638153076</v>
       </c>
-      <c r="R9" s="16"/>
+      <c r="R9" s="15"/>
       <c r="S9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
+      <c r="T9" s="13">
+        <v>22</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V9" s="13">
+        <v>0</v>
+      </c>
       <c r="W9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="13">
         <v>2025020916</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -2010,16 +4575,16 @@
       <c r="D10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <v>22.5</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="13">
         <v>-124</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="13">
         <v>101</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="13">
         <v>8478499</v>
       </c>
       <c r="I10" s="4" t="s">
@@ -2028,16 +4593,16 @@
       <c r="J10" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="K10" s="10">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12">
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14">
         <v>23.29999923706055</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="14">
         <v>0.6558282971382141</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="14">
         <v>31.16565895080566</v>
       </c>
       <c r="O10" s="4" t="s">
@@ -2046,23 +4611,29 @@
       <c r="P10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q10" s="12">
+      <c r="Q10" s="14">
         <v>0.1022568941116333</v>
       </c>
-      <c r="R10" s="16"/>
+      <c r="R10" s="15"/>
       <c r="S10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="T10" s="13">
+        <v>15</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V10" s="13">
+        <v>0</v>
+      </c>
       <c r="W10" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="13">
         <v>2025020916</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -2071,16 +4642,16 @@
       <c r="D11" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>22.5</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="13">
         <v>-113</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="13">
         <v>-109</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="13">
         <v>8476341</v>
       </c>
       <c r="I11" s="4" t="s">
@@ -2089,16 +4660,16 @@
       <c r="J11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="13">
         <v>1</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="14">
         <v>23.20000076293945</v>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="14">
         <v>0.6437569260597229</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="14">
         <v>28.75138473510742</v>
       </c>
       <c r="O11" s="4" t="s">
@@ -2107,23 +4678,29 @@
       <c r="P11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="14">
         <v>0.1132404804229736</v>
       </c>
-      <c r="R11" s="16"/>
+      <c r="R11" s="15"/>
       <c r="S11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
+      <c r="T11" s="13">
+        <v>19</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V11" s="13">
+        <v>0</v>
+      </c>
       <c r="W11" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="13">
         <v>2025020915</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -2132,16 +4709,16 @@
       <c r="D12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
         <v>23.5</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="13">
         <v>-103</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="13">
         <v>-121</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="13">
         <v>8477480</v>
       </c>
       <c r="I12" s="4" t="s">
@@ -2150,16 +4727,16 @@
       <c r="J12" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="14">
         <v>23.79999923706055</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="14">
         <v>0.5509867072105408</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="14">
         <v>10.19734191894531</v>
       </c>
       <c r="O12" s="4" t="s">
@@ -2168,23 +4745,29 @@
       <c r="P12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q12" s="12">
+      <c r="Q12" s="14">
         <v>0.0435975193977356</v>
       </c>
-      <c r="R12" s="16"/>
+      <c r="R12" s="15"/>
       <c r="S12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="T12" s="13">
+        <v>21</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V12" s="13">
+        <v>0</v>
+      </c>
       <c r="W12" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="13">
         <v>2025020915</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -2193,16 +4776,16 @@
       <c r="D13" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="14">
         <v>23.5</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="13">
         <v>-107</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="13">
         <v>-115</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="13">
         <v>8484268</v>
       </c>
       <c r="I13" s="4" t="s">
@@ -2211,16 +4794,16 @@
       <c r="J13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="13">
         <v>1</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="14">
         <v>23.29999923706055</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="14">
         <v>0.4554983079433441</v>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="14">
         <v>8.900338172912598</v>
       </c>
       <c r="O13" s="4" t="s">
@@ -2229,23 +4812,29 @@
       <c r="P13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q13" s="12">
+      <c r="Q13" s="14">
         <v>0.009617924690246582</v>
       </c>
-      <c r="R13" s="16"/>
+      <c r="R13" s="15"/>
       <c r="S13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
+      <c r="T13" s="13">
+        <v>25</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V13" s="13">
+        <v>0</v>
+      </c>
       <c r="W13" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="13">
         <v>2025020917</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -2254,16 +4843,16 @@
       <c r="D14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="14">
         <v>23.5</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="13">
         <v>-118</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="13">
         <v>-104</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="13">
         <v>8477465</v>
       </c>
       <c r="I14" s="4" t="s">
@@ -2272,16 +4861,16 @@
       <c r="J14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="12">
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="14">
         <v>24.79999923706055</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="14">
         <v>0.7561129331588745</v>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="14">
         <v>51.22258758544922</v>
       </c>
       <c r="O14" s="4" t="s">
@@ -2290,25 +4879,31 @@
       <c r="P14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q14" s="12">
+      <c r="Q14" s="14">
         <v>0.2148285508155823</v>
       </c>
-      <c r="R14" s="10">
+      <c r="R14" s="13">
         <v>1</v>
       </c>
       <c r="S14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
+      <c r="T14" s="13">
+        <v>20</v>
+      </c>
+      <c r="U14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V14" s="13">
+        <v>-1</v>
+      </c>
       <c r="W14" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="13">
         <v>2025020917</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -2317,16 +4912,16 @@
       <c r="D15" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="14">
         <v>26.5</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="13">
         <v>-114</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="13">
         <v>-108</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="13">
         <v>8480843</v>
       </c>
       <c r="I15" s="4" t="s">
@@ -2335,16 +4930,16 @@
       <c r="J15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="13">
         <v>1</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="13">
         <v>26</v>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="14">
         <v>0.403830349445343</v>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="14">
         <v>19.23393058776855</v>
       </c>
       <c r="O15" s="4" t="s">
@@ -2353,23 +4948,29 @@
       <c r="P15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="14">
         <v>0.07693886756896973</v>
       </c>
-      <c r="R15" s="16"/>
+      <c r="R15" s="15"/>
       <c r="S15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
+      <c r="T15" s="13">
+        <v>22</v>
+      </c>
+      <c r="U15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V15" s="13">
+        <v>0</v>
+      </c>
       <c r="W15" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="13">
         <v>2025020913</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -2378,14 +4979,14 @@
       <c r="D16" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="14">
         <v>29.5</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="13">
         <v>-127</v>
       </c>
-      <c r="G16" s="17"/>
-      <c r="H16" s="10">
+      <c r="G16" s="16"/>
+      <c r="H16" s="13">
         <v>8479193</v>
       </c>
       <c r="I16" s="4" t="s">
@@ -2394,29 +4995,29 @@
       <c r="J16" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="13">
         <v>1</v>
       </c>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="16"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="15"/>
       <c r="S16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T16" s="4"/>
+      <c r="T16" s="16"/>
       <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
+      <c r="V16" s="16"/>
       <c r="W16" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="13">
         <v>2025020910</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -2425,16 +5026,16 @@
       <c r="D17" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="14">
         <v>26.5</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="13">
         <v>-114</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="13">
         <v>-114</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="13">
         <v>8480045</v>
       </c>
       <c r="I17" s="4" t="s">
@@ -2443,16 +5044,16 @@
       <c r="J17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="K17" s="10">
-        <v>0</v>
-      </c>
-      <c r="L17" s="12">
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="14">
         <v>26.29999923706055</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="14">
         <v>0.4507197141647339</v>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="14">
         <v>9.856057167053223</v>
       </c>
       <c r="O17" s="4" t="s">
@@ -2461,23 +5062,29 @@
       <c r="P17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q17" s="12">
+      <c r="Q17" s="14">
         <v>0.01657003164291382</v>
       </c>
-      <c r="R17" s="16"/>
+      <c r="R17" s="15"/>
       <c r="S17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
+      <c r="T17" s="13">
+        <v>27</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V17" s="13">
+        <v>0</v>
+      </c>
       <c r="W17" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="13">
         <v>2025020910</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -2486,16 +5093,16 @@
       <c r="D18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="14">
         <v>22.5</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="13">
         <v>-105</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="13">
         <v>-123</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="13">
         <v>8474596</v>
       </c>
       <c r="I18" s="4" t="s">
@@ -2504,16 +5111,16 @@
       <c r="J18" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="13">
         <v>1</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="14">
         <v>23.5</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="14">
         <v>0.7082683444023132</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="14">
         <v>41.65366744995117</v>
       </c>
       <c r="O18" s="4" t="s">
@@ -2522,23 +5129,29 @@
       <c r="P18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="Q18" s="14">
         <v>0.1960732340812683</v>
       </c>
-      <c r="R18" s="16"/>
+      <c r="R18" s="15"/>
       <c r="S18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
+      <c r="T18" s="13">
+        <v>28</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V18" s="13">
+        <v>0</v>
+      </c>
       <c r="W18" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="13">
         <v>2025020911</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -2547,16 +5160,16 @@
       <c r="D19" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="14">
         <v>23.5</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="13">
         <v>-119</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="13">
         <v>-109</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="13">
         <v>8478435</v>
       </c>
       <c r="I19" s="4" t="s">
@@ -2565,16 +5178,16 @@
       <c r="J19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K19" s="10">
-        <v>0</v>
-      </c>
-      <c r="L19" s="12">
+      <c r="K19" s="13">
+        <v>0</v>
+      </c>
+      <c r="L19" s="14">
         <v>22.79999923706055</v>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="14">
         <v>0.3667729794979095</v>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="14">
         <v>26.64540481567383</v>
       </c>
       <c r="O19" s="4" t="s">
@@ -2583,23 +5196,29 @@
       <c r="P19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="14">
         <v>0.1116958856582642</v>
       </c>
-      <c r="R19" s="16"/>
+      <c r="R19" s="15"/>
       <c r="S19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
+      <c r="T19" s="13">
+        <v>26</v>
+      </c>
+      <c r="U19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V19" s="13">
+        <v>0</v>
+      </c>
       <c r="W19" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="13">
         <v>2025020911</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -2608,16 +5227,16 @@
       <c r="D20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="14">
         <v>22.5</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="13">
         <v>-106</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="13">
         <v>-122</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="13">
         <v>8480313</v>
       </c>
       <c r="I20" s="4" t="s">
@@ -2626,16 +5245,16 @@
       <c r="J20" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="13">
         <v>1</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="14">
         <v>22.70000076293945</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="14">
         <v>0.5496154427528381</v>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="14">
         <v>9.923088073730469</v>
       </c>
       <c r="O20" s="4" t="s">
@@ -2644,23 +5263,29 @@
       <c r="P20" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q20" s="12">
+      <c r="Q20" s="14">
         <v>0.03505235910415649</v>
       </c>
-      <c r="R20" s="16"/>
+      <c r="R20" s="15"/>
       <c r="S20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
+      <c r="T20" s="13">
+        <v>23</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V20" s="13">
+        <v>0</v>
+      </c>
       <c r="W20" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="13">
         <v>2025020912</v>
       </c>
       <c r="C21" s="4" t="s">
@@ -2669,16 +5294,16 @@
       <c r="D21" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="14">
         <v>26.5</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="13">
         <v>-111</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="13">
         <v>-116</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="13">
         <v>8476932</v>
       </c>
       <c r="I21" s="4" t="s">
@@ -2687,16 +5312,16 @@
       <c r="J21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K21" s="10">
-        <v>0</v>
-      </c>
-      <c r="L21" s="12">
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="14">
         <v>26.5</v>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="14">
         <v>0.494999498128891</v>
       </c>
-      <c r="N21" s="12">
+      <c r="N21" s="14">
         <v>1.000100374221802</v>
       </c>
       <c r="O21" s="4" t="s">
@@ -2705,23 +5330,29 @@
       <c r="P21" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q21" s="12">
+      <c r="Q21" s="14">
         <v>-0.03106686472892761</v>
       </c>
-      <c r="R21" s="16"/>
+      <c r="R21" s="15"/>
       <c r="S21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
+      <c r="T21" s="13">
+        <v>32</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V21" s="13">
+        <v>0</v>
+      </c>
       <c r="W21" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="13">
         <v>2025020913</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -2730,16 +5361,16 @@
       <c r="D22" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="14">
         <v>21.5</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="13">
         <v>-106</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="13">
         <v>-122</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="13">
         <v>8479193</v>
       </c>
       <c r="I22" s="4" t="s">
@@ -2748,16 +5379,16 @@
       <c r="J22" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="13">
         <v>1</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="14">
         <v>21.20000076293945</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="14">
         <v>0.4462916254997253</v>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="14">
         <v>10.74167442321777</v>
       </c>
       <c r="O22" s="4" t="s">
@@ -2766,23 +5397,29 @@
       <c r="P22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q22" s="12">
+      <c r="Q22" s="14">
         <v>0.004158854484558105</v>
       </c>
-      <c r="R22" s="16"/>
+      <c r="R22" s="15"/>
       <c r="S22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
+      <c r="T22" s="13">
+        <v>18</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V22" s="13">
+        <v>0</v>
+      </c>
       <c r="W22" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="13">
         <v>2025020915</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -2791,16 +5428,16 @@
       <c r="D23" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="14">
         <v>23.5</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="13">
         <v>-101</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="13">
         <v>-128</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="13">
         <v>8477480</v>
       </c>
       <c r="I23" s="4" t="s">
@@ -2809,16 +5446,16 @@
       <c r="J23" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K23" s="10">
-        <v>0</v>
-      </c>
-      <c r="L23" s="12">
+      <c r="K23" s="13">
+        <v>0</v>
+      </c>
+      <c r="L23" s="14">
         <v>23.79999923706055</v>
       </c>
-      <c r="M23" s="12">
+      <c r="M23" s="14">
         <v>0.5509867072105408</v>
       </c>
-      <c r="N23" s="12">
+      <c r="N23" s="14">
         <v>10.19734191894531</v>
       </c>
       <c r="O23" s="4" t="s">
@@ -2827,23 +5464,29 @@
       <c r="P23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q23" s="12">
+      <c r="Q23" s="14">
         <v>0.04849916696548462</v>
       </c>
-      <c r="R23" s="16"/>
+      <c r="R23" s="15"/>
       <c r="S23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
+      <c r="T23" s="13">
+        <v>21</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V23" s="13">
+        <v>0</v>
+      </c>
       <c r="W23" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="13">
         <v>2025020910</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -2852,16 +5495,16 @@
       <c r="D24" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="14">
         <v>22.5</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="13">
         <v>-118</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="13">
         <v>-105</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="13">
         <v>8474596</v>
       </c>
       <c r="I24" s="4" t="s">
@@ -2870,16 +5513,16 @@
       <c r="J24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="13">
         <v>1</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="14">
         <v>23.5</v>
       </c>
-      <c r="M24" s="12">
+      <c r="M24" s="14">
         <v>0.7082683444023132</v>
       </c>
-      <c r="N24" s="12">
+      <c r="N24" s="14">
         <v>41.65366744995117</v>
       </c>
       <c r="O24" s="4" t="s">
@@ -2888,23 +5531,29 @@
       <c r="P24" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q24" s="12">
+      <c r="Q24" s="14">
         <v>0.166983962059021</v>
       </c>
-      <c r="R24" s="16"/>
+      <c r="R24" s="15"/>
       <c r="S24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
+      <c r="T24" s="13">
+        <v>28</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V24" s="13">
+        <v>0</v>
+      </c>
       <c r="W24" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="13">
         <v>2025020911</v>
       </c>
       <c r="C25" s="4" t="s">
@@ -2913,16 +5562,16 @@
       <c r="D25" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="14">
         <v>22.5</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="13">
         <v>-115</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="13">
         <v>-107</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="13">
         <v>8480313</v>
       </c>
       <c r="I25" s="4" t="s">
@@ -2931,16 +5580,16 @@
       <c r="J25" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="13">
         <v>1</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="14">
         <v>22.70000076293945</v>
       </c>
-      <c r="M25" s="12">
+      <c r="M25" s="14">
         <v>0.5496154427528381</v>
       </c>
-      <c r="N25" s="12">
+      <c r="N25" s="14">
         <v>9.923088073730469</v>
       </c>
       <c r="O25" s="4" t="s">
@@ -2949,23 +5598,29 @@
       <c r="P25" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q25" s="12">
+      <c r="Q25" s="14">
         <v>0.01473170518875122</v>
       </c>
-      <c r="R25" s="16"/>
+      <c r="R25" s="15"/>
       <c r="S25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
+      <c r="T25" s="13">
+        <v>23</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V25" s="13">
+        <v>0</v>
+      </c>
       <c r="W25" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="13">
         <v>2025020913</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -2974,16 +5629,16 @@
       <c r="D26" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="14">
         <v>21.5</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="13">
         <v>-121</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="13">
         <v>-102</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="13">
         <v>8479193</v>
       </c>
       <c r="I26" s="4" t="s">
@@ -2992,16 +5647,16 @@
       <c r="J26" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="13">
         <v>1</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="14">
         <v>21.20000076293945</v>
       </c>
-      <c r="M26" s="12">
+      <c r="M26" s="14">
         <v>0.4462916254997253</v>
       </c>
-      <c r="N26" s="12">
+      <c r="N26" s="14">
         <v>10.74167442321777</v>
       </c>
       <c r="O26" s="4" t="s">
@@ -3010,23 +5665,29 @@
       <c r="P26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q26" s="12">
+      <c r="Q26" s="14">
         <v>0.04875785112380981</v>
       </c>
-      <c r="R26" s="16"/>
+      <c r="R26" s="15"/>
       <c r="S26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
+      <c r="T26" s="13">
+        <v>18</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V26" s="13">
+        <v>0</v>
+      </c>
       <c r="W26" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="13">
         <v>2025020914</v>
       </c>
       <c r="C27" s="4" t="s">
@@ -3035,16 +5696,16 @@
       <c r="D27" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="14">
         <v>23.5</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="13">
         <v>-112</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="13">
         <v>-110</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="13">
         <v>8475809</v>
       </c>
       <c r="I27" s="4" t="s">
@@ -3053,16 +5714,16 @@
       <c r="J27" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K27" s="10">
-        <v>0</v>
-      </c>
-      <c r="L27" s="12">
+      <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="14">
         <v>23.60000038146973</v>
       </c>
-      <c r="M27" s="12">
+      <c r="M27" s="14">
         <v>0.5182401537895203</v>
       </c>
-      <c r="N27" s="12">
+      <c r="N27" s="14">
         <v>3.648030757904053</v>
       </c>
       <c r="O27" s="4" t="s">
@@ -3071,23 +5732,29 @@
       <c r="P27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q27" s="12">
+      <c r="Q27" s="14">
         <v>-0.01006174087524414</v>
       </c>
-      <c r="R27" s="16"/>
+      <c r="R27" s="15"/>
       <c r="S27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
+      <c r="T27" s="13">
+        <v>28</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V27" s="13">
+        <v>0</v>
+      </c>
       <c r="W27" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="13">
         <v>2025020916</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -3096,16 +5763,16 @@
       <c r="D28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="14">
         <v>23.5</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="13">
         <v>-110</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="13">
         <v>-112</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="13">
         <v>8478499</v>
       </c>
       <c r="I28" s="4" t="s">
@@ -3114,16 +5781,16 @@
       <c r="J28" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="K28" s="10">
-        <v>0</v>
-      </c>
-      <c r="L28" s="10">
+      <c r="K28" s="13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
         <v>24</v>
       </c>
-      <c r="M28" s="12">
+      <c r="M28" s="14">
         <v>0.6058622598648071</v>
       </c>
-      <c r="N28" s="12">
+      <c r="N28" s="14">
         <v>21.17245101928711</v>
       </c>
       <c r="O28" s="4" t="s">
@@ -3132,23 +5799,29 @@
       <c r="P28" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q28" s="12">
+      <c r="Q28" s="14">
         <v>0.08205270767211914</v>
       </c>
-      <c r="R28" s="16"/>
+      <c r="R28" s="15"/>
       <c r="S28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
+      <c r="T28" s="13">
+        <v>15</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V28" s="13">
+        <v>0</v>
+      </c>
       <c r="W28" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="13">
         <v>2025020915</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -3157,16 +5830,16 @@
       <c r="D29" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="14">
         <v>23.5</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="13">
         <v>-115</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="13">
         <v>-107</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="13">
         <v>8477480</v>
       </c>
       <c r="I29" s="4" t="s">
@@ -3175,16 +5848,16 @@
       <c r="J29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K29" s="10">
-        <v>0</v>
-      </c>
-      <c r="L29" s="12">
+      <c r="K29" s="13">
+        <v>0</v>
+      </c>
+      <c r="L29" s="14">
         <v>23.79999923706055</v>
       </c>
-      <c r="M29" s="12">
+      <c r="M29" s="14">
         <v>0.5509867072105408</v>
       </c>
-      <c r="N29" s="12">
+      <c r="N29" s="14">
         <v>10.19734191894531</v>
       </c>
       <c r="O29" s="4" t="s">
@@ -3193,23 +5866,29 @@
       <c r="P29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q29" s="12">
+      <c r="Q29" s="14">
         <v>0.01610296964645386</v>
       </c>
-      <c r="R29" s="16"/>
+      <c r="R29" s="15"/>
       <c r="S29" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
+      <c r="T29" s="13">
+        <v>21</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V29" s="13">
+        <v>0</v>
+      </c>
       <c r="W29" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="13">
         <v>2025020913</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -3218,14 +5897,14 @@
       <c r="D30" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="14">
         <v>29.5</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="13">
         <v>-127</v>
       </c>
-      <c r="G30" s="17"/>
-      <c r="H30" s="10">
+      <c r="G30" s="16"/>
+      <c r="H30" s="13">
         <v>8479193</v>
       </c>
       <c r="I30" s="4" t="s">
@@ -3234,29 +5913,29 @@
       <c r="J30" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="13">
         <v>1</v>
       </c>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
+      <c r="L30" s="17"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="16"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="15"/>
       <c r="S30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T30" s="4"/>
+      <c r="T30" s="16"/>
       <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
+      <c r="V30" s="16"/>
       <c r="W30" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="13">
         <v>2025020910</v>
       </c>
       <c r="C31" s="4" t="s">
@@ -3265,16 +5944,16 @@
       <c r="D31" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="14">
         <v>22.5</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="13">
         <v>-112</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="13">
         <v>-115</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="13">
         <v>8474596</v>
       </c>
       <c r="I31" s="4" t="s">
@@ -3283,16 +5962,16 @@
       <c r="J31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="13">
         <v>1</v>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="14">
         <v>23.5</v>
       </c>
-      <c r="M31" s="12">
+      <c r="M31" s="14">
         <v>0.7082683444023132</v>
       </c>
-      <c r="N31" s="12">
+      <c r="N31" s="14">
         <v>41.65366744995117</v>
       </c>
       <c r="O31" s="4" t="s">
@@ -3301,23 +5980,29 @@
       <c r="P31" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q31" s="12">
+      <c r="Q31" s="14">
         <v>0.1799664497375488</v>
       </c>
-      <c r="R31" s="16"/>
+      <c r="R31" s="15"/>
       <c r="S31" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
+      <c r="T31" s="13">
+        <v>28</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V31" s="13">
+        <v>0</v>
+      </c>
       <c r="W31" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="13">
         <v>2025020911</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -3326,16 +6011,16 @@
       <c r="D32" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="14">
         <v>22.5</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="13">
         <v>-112</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="13">
         <v>-115</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="13">
         <v>8480313</v>
       </c>
       <c r="I32" s="4" t="s">
@@ -3344,16 +6029,16 @@
       <c r="J32" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="13">
         <v>1</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="14">
         <v>22.70000076293945</v>
       </c>
-      <c r="M32" s="12">
+      <c r="M32" s="14">
         <v>0.5496154427528381</v>
       </c>
-      <c r="N32" s="12">
+      <c r="N32" s="14">
         <v>9.923088073730469</v>
       </c>
       <c r="O32" s="4" t="s">
@@ -3362,23 +6047,29 @@
       <c r="P32" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q32" s="12">
+      <c r="Q32" s="14">
         <v>0.02131354808807373</v>
       </c>
-      <c r="R32" s="16"/>
+      <c r="R32" s="15"/>
       <c r="S32" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
+      <c r="T32" s="13">
+        <v>23</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V32" s="13">
+        <v>0</v>
+      </c>
       <c r="W32" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="13">
         <v>2025020913</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -3387,16 +6078,16 @@
       <c r="D33" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="14">
         <v>21.5</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="13">
         <v>-118</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="13">
         <v>-110</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="13">
         <v>8479193</v>
       </c>
       <c r="I33" s="4" t="s">
@@ -3405,16 +6096,16 @@
       <c r="J33" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="13">
         <v>1</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="14">
         <v>21.20000076293945</v>
       </c>
-      <c r="M33" s="12">
+      <c r="M33" s="14">
         <v>0.4462916254997253</v>
       </c>
-      <c r="N33" s="12">
+      <c r="N33" s="14">
         <v>10.74167442321777</v>
       </c>
       <c r="O33" s="4" t="s">
@@ -3423,23 +6114,29 @@
       <c r="P33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q33" s="12">
+      <c r="Q33" s="14">
         <v>0.02989882230758667</v>
       </c>
-      <c r="R33" s="16"/>
+      <c r="R33" s="15"/>
       <c r="S33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
+      <c r="T33" s="13">
+        <v>18</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V33" s="13">
+        <v>0</v>
+      </c>
       <c r="W33" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="13">
         <v>2025020914</v>
       </c>
       <c r="C34" s="4" t="s">
@@ -3448,16 +6145,16 @@
       <c r="D34" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="14">
         <v>26.5</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="13">
         <v>-108</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="13">
         <v>-120</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="13">
         <v>8478872</v>
       </c>
       <c r="I34" s="4" t="s">
@@ -3466,16 +6163,16 @@
       <c r="J34" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="13">
         <v>1</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="14">
         <v>25.70000076293945</v>
       </c>
-      <c r="M34" s="12">
+      <c r="M34" s="14">
         <v>0.3436546325683594</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N34" s="14">
         <v>31.26907348632812</v>
       </c>
       <c r="O34" s="4" t="s">
@@ -3484,23 +6181,29 @@
       <c r="P34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q34" s="12">
+      <c r="Q34" s="14">
         <v>0.110890805721283</v>
       </c>
-      <c r="R34" s="16"/>
+      <c r="R34" s="15"/>
       <c r="S34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
+      <c r="T34" s="13">
+        <v>22</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V34" s="13">
+        <v>0</v>
+      </c>
       <c r="W34" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="13">
         <v>2025020914</v>
       </c>
       <c r="C35" s="4" t="s">
@@ -3509,16 +6212,16 @@
       <c r="D35" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="14">
         <v>23.5</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="13">
         <v>-106</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="13">
         <v>-122</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="13">
         <v>8475809</v>
       </c>
       <c r="I35" s="4" t="s">
@@ -3527,16 +6230,16 @@
       <c r="J35" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K35" s="10">
-        <v>0</v>
-      </c>
-      <c r="L35" s="12">
+      <c r="K35" s="13">
+        <v>0</v>
+      </c>
+      <c r="L35" s="14">
         <v>23.60000038146973</v>
       </c>
-      <c r="M35" s="12">
+      <c r="M35" s="14">
         <v>0.5182401537895203</v>
       </c>
-      <c r="N35" s="12">
+      <c r="N35" s="14">
         <v>3.648030757904053</v>
       </c>
       <c r="O35" s="4" t="s">
@@ -3545,23 +6248,29 @@
       <c r="P35" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q35" s="12">
+      <c r="Q35" s="14">
         <v>0.003677070140838623</v>
       </c>
-      <c r="R35" s="16"/>
+      <c r="R35" s="15"/>
       <c r="S35" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
+      <c r="T35" s="13">
+        <v>28</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V35" s="13">
+        <v>0</v>
+      </c>
       <c r="W35" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="13">
         <v>2025020916</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -3570,16 +6279,16 @@
       <c r="D36" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="14">
         <v>22.5</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="13">
         <v>-111</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="13">
         <v>-116</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="13">
         <v>8476341</v>
       </c>
       <c r="I36" s="4" t="s">
@@ -3588,16 +6297,16 @@
       <c r="J36" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="13">
         <v>1</v>
       </c>
-      <c r="L36" s="12">
+      <c r="L36" s="14">
         <v>23.20000076293945</v>
       </c>
-      <c r="M36" s="12">
+      <c r="M36" s="14">
         <v>0.6437569260597229</v>
       </c>
-      <c r="N36" s="12">
+      <c r="N36" s="14">
         <v>28.75138473510742</v>
       </c>
       <c r="O36" s="4" t="s">
@@ -3606,23 +6315,29 @@
       <c r="P36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q36" s="12">
+      <c r="Q36" s="14">
         <v>0.1176905632019043</v>
       </c>
-      <c r="R36" s="16"/>
+      <c r="R36" s="15"/>
       <c r="S36" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
+      <c r="T36" s="13">
+        <v>19</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V36" s="13">
+        <v>0</v>
+      </c>
       <c r="W36" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="13">
         <v>2025020916</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -3631,16 +6346,16 @@
       <c r="D37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="14">
         <v>23.5</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="13">
         <v>-108</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="13">
         <v>-120</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="13">
         <v>8478499</v>
       </c>
       <c r="I37" s="4" t="s">
@@ -3649,16 +6364,16 @@
       <c r="J37" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="K37" s="10">
-        <v>0</v>
-      </c>
-      <c r="L37" s="10">
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
         <v>24</v>
       </c>
-      <c r="M37" s="12">
+      <c r="M37" s="14">
         <v>0.6058622598648071</v>
       </c>
-      <c r="N37" s="12">
+      <c r="N37" s="14">
         <v>21.17245101928711</v>
       </c>
       <c r="O37" s="4" t="s">
@@ -3667,23 +6382,29 @@
       <c r="P37" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q37" s="12">
+      <c r="Q37" s="14">
         <v>0.08663147687911987</v>
       </c>
-      <c r="R37" s="16"/>
+      <c r="R37" s="15"/>
       <c r="S37" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
+      <c r="T37" s="13">
+        <v>15</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V37" s="13">
+        <v>0</v>
+      </c>
       <c r="W37" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="13">
         <v>2025020915</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -3692,16 +6413,16 @@
       <c r="D38" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="14">
         <v>23.5</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="13">
         <v>-110</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="13">
         <v>-118</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="13">
         <v>8477480</v>
       </c>
       <c r="I38" s="4" t="s">
@@ -3710,16 +6431,16 @@
       <c r="J38" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K38" s="10">
-        <v>0</v>
-      </c>
-      <c r="L38" s="12">
+      <c r="K38" s="13">
+        <v>0</v>
+      </c>
+      <c r="L38" s="14">
         <v>23.79999923706055</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="14">
         <v>0.5509867072105408</v>
       </c>
-      <c r="N38" s="12">
+      <c r="N38" s="14">
         <v>10.19734191894531</v>
       </c>
       <c r="O38" s="4" t="s">
@@ -3728,23 +6449,29 @@
       <c r="P38" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q38" s="12">
+      <c r="Q38" s="14">
         <v>0.02717715501785278</v>
       </c>
-      <c r="R38" s="16"/>
+      <c r="R38" s="15"/>
       <c r="S38" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
+      <c r="T38" s="13">
+        <v>21</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V38" s="13">
+        <v>0</v>
+      </c>
       <c r="W38" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="13">
         <v>2025020917</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -3753,16 +6480,16 @@
       <c r="D39" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="14">
         <v>26.5</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="13">
         <v>-115</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="13">
         <v>-112</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="13">
         <v>8480843</v>
       </c>
       <c r="I39" s="4" t="s">
@@ -3771,16 +6498,16 @@
       <c r="J39" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="13">
         <v>1</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="13">
         <v>26</v>
       </c>
-      <c r="M39" s="12">
+      <c r="M39" s="14">
         <v>0.403830349445343</v>
       </c>
-      <c r="N39" s="12">
+      <c r="N39" s="14">
         <v>19.23393058776855</v>
       </c>
       <c r="O39" s="4" t="s">
@@ -3789,23 +6516,29 @@
       <c r="P39" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q39" s="12">
+      <c r="Q39" s="14">
         <v>0.06786775588989258</v>
       </c>
-      <c r="R39" s="16"/>
+      <c r="R39" s="15"/>
       <c r="S39" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
+      <c r="T39" s="13">
+        <v>22</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V39" s="13">
+        <v>0</v>
+      </c>
       <c r="W39" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="13">
         <v>2025020917</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -3814,16 +6547,16 @@
       <c r="D40" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E40" s="12">
+      <c r="E40" s="14">
         <v>23.5</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="13">
         <v>-123</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="13">
         <v>-105</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="13">
         <v>8477465</v>
       </c>
       <c r="I40" s="4" t="s">
@@ -3832,16 +6565,16 @@
       <c r="J40" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K40" s="10">
-        <v>0</v>
-      </c>
-      <c r="L40" s="12">
+      <c r="K40" s="13">
+        <v>0</v>
+      </c>
+      <c r="L40" s="14">
         <v>24.79999923706055</v>
       </c>
-      <c r="M40" s="12">
+      <c r="M40" s="14">
         <v>0.7561129331588745</v>
       </c>
-      <c r="N40" s="12">
+      <c r="N40" s="14">
         <v>51.22258758544922</v>
       </c>
       <c r="O40" s="4" t="s">
@@ -3850,23 +6583,29 @@
       <c r="P40" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q40" s="12">
+      <c r="Q40" s="14">
         <v>0.20454341173172</v>
       </c>
-      <c r="R40" s="16"/>
+      <c r="R40" s="15"/>
       <c r="S40" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
+      <c r="T40" s="13">
+        <v>20</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V40" s="13">
+        <v>0</v>
+      </c>
       <c r="W40" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="13">
         <v>2025020914</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -3875,16 +6614,16 @@
       <c r="D41" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E41" s="12">
+      <c r="E41" s="14">
         <v>26.5</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="13">
         <v>-110</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="13">
         <v>-112</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="13">
         <v>8478872</v>
       </c>
       <c r="I41" s="4" t="s">
@@ -3893,16 +6632,16 @@
       <c r="J41" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="13">
         <v>1</v>
       </c>
-      <c r="L41" s="12">
+      <c r="L41" s="14">
         <v>25.70000076293945</v>
       </c>
-      <c r="M41" s="12">
+      <c r="M41" s="14">
         <v>0.3436546325683594</v>
       </c>
-      <c r="N41" s="12">
+      <c r="N41" s="14">
         <v>31.26907348632812</v>
       </c>
       <c r="O41" s="4" t="s">
@@ -3911,25 +6650,31 @@
       <c r="P41" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q41" s="12">
+      <c r="Q41" s="14">
         <v>0.1280434727668762</v>
       </c>
-      <c r="R41" s="16">
+      <c r="R41" s="13">
         <v>1</v>
       </c>
       <c r="S41" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
+      <c r="T41" s="13">
+        <v>22</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="V41" s="14">
+        <v>0.8928571428571428</v>
+      </c>
       <c r="W41" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="13">
         <v>2025020914</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -3938,16 +6683,16 @@
       <c r="D42" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E42" s="12">
+      <c r="E42" s="14">
         <v>23.5</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="13">
         <v>-115</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="13">
         <v>-107</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="13">
         <v>8475809</v>
       </c>
       <c r="I42" s="4" t="s">
@@ -3956,16 +6701,16 @@
       <c r="J42" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K42" s="10">
-        <v>0</v>
-      </c>
-      <c r="L42" s="12">
+      <c r="K42" s="13">
+        <v>0</v>
+      </c>
+      <c r="L42" s="14">
         <v>23.60000038146973</v>
       </c>
-      <c r="M42" s="12">
+      <c r="M42" s="14">
         <v>0.5182401537895203</v>
       </c>
-      <c r="N42" s="12">
+      <c r="N42" s="14">
         <v>3.648030757904053</v>
       </c>
       <c r="O42" s="4" t="s">
@@ -3974,23 +6719,29 @@
       <c r="P42" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q42" s="12">
+      <c r="Q42" s="14">
         <v>-0.01664358377456665</v>
       </c>
-      <c r="R42" s="16"/>
+      <c r="R42" s="15"/>
       <c r="S42" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
+      <c r="T42" s="13">
+        <v>28</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V42" s="13">
+        <v>0</v>
+      </c>
       <c r="W42" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="13">
         <v>2025020915</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -3999,16 +6750,16 @@
       <c r="D43" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="12">
+      <c r="E43" s="14">
         <v>23.5</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="13">
         <v>-117</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="13">
         <v>-106</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="13">
         <v>8484268</v>
       </c>
       <c r="I43" s="4" t="s">
@@ -4017,16 +6768,16 @@
       <c r="J43" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="13">
         <v>1</v>
       </c>
-      <c r="L43" s="12">
+      <c r="L43" s="14">
         <v>23.29999923706055</v>
       </c>
-      <c r="M43" s="12">
+      <c r="M43" s="14">
         <v>0.4554983079433441</v>
       </c>
-      <c r="N43" s="12">
+      <c r="N43" s="14">
         <v>8.900338172912598</v>
       </c>
       <c r="O43" s="4" t="s">
@@ -4035,23 +6786,29 @@
       <c r="P43" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q43" s="12">
+      <c r="Q43" s="14">
         <v>0.02993857860565186</v>
       </c>
-      <c r="R43" s="16"/>
+      <c r="R43" s="15"/>
       <c r="S43" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
+      <c r="T43" s="13">
+        <v>25</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V43" s="13">
+        <v>0</v>
+      </c>
       <c r="W43" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="13">
         <v>2025020917</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -4060,16 +6817,16 @@
       <c r="D44" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="12">
+      <c r="E44" s="14">
         <v>24.5</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="13">
         <v>-104</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="13">
         <v>-118</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="13">
         <v>8477465</v>
       </c>
       <c r="I44" s="4" t="s">
@@ -4078,16 +6835,16 @@
       <c r="J44" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K44" s="10">
-        <v>0</v>
-      </c>
-      <c r="L44" s="12">
+      <c r="K44" s="13">
+        <v>0</v>
+      </c>
+      <c r="L44" s="14">
         <v>25.5</v>
       </c>
-      <c r="M44" s="12">
+      <c r="M44" s="14">
         <v>0.7027168869972229</v>
       </c>
-      <c r="N44" s="12">
+      <c r="N44" s="14">
         <v>40.54337692260742</v>
       </c>
       <c r="O44" s="4" t="s">
@@ -4096,23 +6853,29 @@
       <c r="P44" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q44" s="12">
+      <c r="Q44" s="14">
         <v>0.1929129362106323</v>
       </c>
-      <c r="R44" s="16"/>
+      <c r="R44" s="15"/>
       <c r="S44" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
-      <c r="V44" s="4"/>
+      <c r="T44" s="13">
+        <v>20</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V44" s="13">
+        <v>0</v>
+      </c>
       <c r="W44" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="13">
         <v>2025020913</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -4121,14 +6884,14 @@
       <c r="D45" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="12">
+      <c r="E45" s="14">
         <v>29.5</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="13">
         <v>-127</v>
       </c>
-      <c r="G45" s="17"/>
-      <c r="H45" s="10">
+      <c r="G45" s="16"/>
+      <c r="H45" s="13">
         <v>8479193</v>
       </c>
       <c r="I45" s="4" t="s">
@@ -4137,29 +6900,29 @@
       <c r="J45" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="13">
         <v>1</v>
       </c>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="16"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="15"/>
       <c r="S45" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T45" s="4"/>
+      <c r="T45" s="16"/>
       <c r="U45" s="4"/>
-      <c r="V45" s="4"/>
+      <c r="V45" s="16"/>
       <c r="W45" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="13">
         <v>2025020913</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -4168,16 +6931,16 @@
       <c r="D46" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="12">
+      <c r="E46" s="14">
         <v>21.5</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="13">
         <v>-125</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="13">
         <v>-103</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="13">
         <v>8479193</v>
       </c>
       <c r="I46" s="4" t="s">
@@ -4186,16 +6949,16 @@
       <c r="J46" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="13">
         <v>1</v>
       </c>
-      <c r="L46" s="12">
+      <c r="L46" s="14">
         <v>21.20000076293945</v>
       </c>
-      <c r="M46" s="12">
+      <c r="M46" s="14">
         <v>0.4462916254997253</v>
       </c>
-      <c r="N46" s="12">
+      <c r="N46" s="14">
         <v>10.74167442321777</v>
       </c>
       <c r="O46" s="4" t="s">
@@ -4204,23 +6967,29 @@
       <c r="P46" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q46" s="12">
+      <c r="Q46" s="14">
         <v>0.04631918668746948</v>
       </c>
-      <c r="R46" s="16"/>
+      <c r="R46" s="15"/>
       <c r="S46" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
-      <c r="V46" s="4"/>
+      <c r="T46" s="13">
+        <v>18</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V46" s="13">
+        <v>0</v>
+      </c>
       <c r="W46" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="13">
         <v>2025020913</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -4229,16 +6998,16 @@
       <c r="D47" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E47" s="14">
         <v>23.5</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="13">
         <v>-114</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="13">
         <v>-114</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="13">
         <v>8478916</v>
       </c>
       <c r="I47" s="4" t="s">
@@ -4247,16 +7016,16 @@
       <c r="J47" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K47" s="10">
-        <v>0</v>
-      </c>
-      <c r="L47" s="12">
+      <c r="K47" s="13">
+        <v>0</v>
+      </c>
+      <c r="L47" s="14">
         <v>24.20000076293945</v>
       </c>
-      <c r="M47" s="12">
+      <c r="M47" s="14">
         <v>0.6356678009033203</v>
       </c>
-      <c r="N47" s="12">
+      <c r="N47" s="14">
         <v>27.13356018066406</v>
       </c>
       <c r="O47" s="4" t="s">
@@ -4265,23 +7034,29 @@
       <c r="P47" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q47" s="12">
+      <c r="Q47" s="14">
         <v>0.102957546710968</v>
       </c>
-      <c r="R47" s="16"/>
+      <c r="R47" s="15"/>
       <c r="S47" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
+      <c r="T47" s="13">
+        <v>28</v>
+      </c>
+      <c r="U47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V47" s="13">
+        <v>0</v>
+      </c>
       <c r="W47" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="13">
         <v>2025020914</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -4290,16 +7065,16 @@
       <c r="D48" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="12">
+      <c r="E48" s="14">
         <v>26.5</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="13">
         <v>-116</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="13">
         <v>-111</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="13">
         <v>8478872</v>
       </c>
       <c r="I48" s="4" t="s">
@@ -4308,16 +7083,16 @@
       <c r="J48" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K48" s="13">
         <v>1</v>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="14">
         <v>25.70000076293945</v>
       </c>
-      <c r="M48" s="12">
+      <c r="M48" s="14">
         <v>0.3436546325683594</v>
       </c>
-      <c r="N48" s="12">
+      <c r="N48" s="14">
         <v>31.26907348632812</v>
       </c>
       <c r="O48" s="4" t="s">
@@ -4326,23 +7101,29 @@
       <c r="P48" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="Q48" s="12">
+      <c r="Q48" s="14">
         <v>0.130279004573822</v>
       </c>
-      <c r="R48" s="16"/>
+      <c r="R48" s="15"/>
       <c r="S48" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
+      <c r="T48" s="13">
+        <v>22</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V48" s="13">
+        <v>0</v>
+      </c>
       <c r="W48" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="13">
         <v>2025020914</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -4351,16 +7132,16 @@
       <c r="D49" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E49" s="12">
+      <c r="E49" s="14">
         <v>23.5</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="13">
         <v>-115</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="13">
         <v>-112</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="13">
         <v>8475809</v>
       </c>
       <c r="I49" s="4" t="s">
@@ -4369,16 +7150,16 @@
       <c r="J49" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K49" s="10">
-        <v>0</v>
-      </c>
-      <c r="L49" s="12">
+      <c r="K49" s="13">
+        <v>0</v>
+      </c>
+      <c r="L49" s="14">
         <v>23.60000038146973</v>
       </c>
-      <c r="M49" s="12">
+      <c r="M49" s="14">
         <v>0.5182401537895203</v>
       </c>
-      <c r="N49" s="12">
+      <c r="N49" s="14">
         <v>3.648030757904053</v>
       </c>
       <c r="O49" s="4" t="s">
@@ -4387,23 +7168,29 @@
       <c r="P49" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q49" s="12">
+      <c r="Q49" s="14">
         <v>-0.01664358377456665</v>
       </c>
-      <c r="R49" s="16"/>
+      <c r="R49" s="15"/>
       <c r="S49" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
+      <c r="T49" s="13">
+        <v>28</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V49" s="13">
+        <v>0</v>
+      </c>
       <c r="W49" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="13">
         <v>2025020915</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -4412,16 +7199,16 @@
       <c r="D50" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E50" s="12">
+      <c r="E50" s="14">
         <v>23.5</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="13">
         <v>-115</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="13">
         <v>-112</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="13">
         <v>8477480</v>
       </c>
       <c r="I50" s="4" t="s">
@@ -4430,16 +7217,16 @@
       <c r="J50" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K50" s="10">
-        <v>0</v>
-      </c>
-      <c r="L50" s="12">
+      <c r="K50" s="13">
+        <v>0</v>
+      </c>
+      <c r="L50" s="14">
         <v>23.79999923706055</v>
       </c>
-      <c r="M50" s="12">
+      <c r="M50" s="14">
         <v>0.5509867072105408</v>
       </c>
-      <c r="N50" s="12">
+      <c r="N50" s="14">
         <v>10.19734191894531</v>
       </c>
       <c r="O50" s="4" t="s">
@@ -4448,23 +7235,29 @@
       <c r="P50" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="Q50" s="12">
+      <c r="Q50" s="14">
         <v>0.01610296964645386</v>
       </c>
-      <c r="R50" s="16"/>
+      <c r="R50" s="15"/>
       <c r="S50" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
+      <c r="T50" s="13">
+        <v>21</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V50" s="13">
+        <v>0</v>
+      </c>
       <c r="W50" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="13">
         <v>2025020917</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -4473,16 +7266,16 @@
       <c r="D51" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E51" s="14">
         <v>24.5</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="13">
         <v>-102</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="13">
         <v>-127</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="13">
         <v>8477465</v>
       </c>
       <c r="I51" s="4" t="s">
@@ -4491,16 +7284,16 @@
       <c r="J51" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K51" s="10">
-        <v>0</v>
-      </c>
-      <c r="L51" s="12">
+      <c r="K51" s="13">
+        <v>0</v>
+      </c>
+      <c r="L51" s="14">
         <v>25.5</v>
       </c>
-      <c r="M51" s="12">
+      <c r="M51" s="14">
         <v>0.7027168869972229</v>
       </c>
-      <c r="N51" s="12">
+      <c r="N51" s="14">
         <v>40.54337692260742</v>
       </c>
       <c r="O51" s="4" t="s">
@@ -4509,16 +7302,22 @@
       <c r="P51" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Q51" s="12">
+      <c r="Q51" s="14">
         <v>0.1977663636207581</v>
       </c>
-      <c r="R51" s="16"/>
+      <c r="R51" s="15"/>
       <c r="S51" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
+      <c r="T51" s="13">
+        <v>20</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V51" s="13">
+        <v>0</v>
+      </c>
       <c r="W51" s="4"/>
     </row>
   </sheetData>
@@ -4526,7 +7325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -4551,7 +7350,7 @@
     <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -4682,7 +7481,7 @@
       <c r="Q2" s="6">
         <v>0.04561102390289307</v>
       </c>
-      <c r="R2" s="10"/>
+      <c r="R2" s="5"/>
       <c r="S2" s="4" t="s">
         <v>30</v>
       </c>
@@ -4749,7 +7548,7 @@
       <c r="Q3" s="6">
         <v>-0.01903098821640015</v>
       </c>
-      <c r="R3" s="10"/>
+      <c r="R3" s="5"/>
       <c r="S3" s="4" t="s">
         <v>30</v>
       </c>
@@ -4816,7 +7615,7 @@
       <c r="Q4" s="6">
         <v>0.1133634150028229</v>
       </c>
-      <c r="R4" s="10"/>
+      <c r="R4" s="5"/>
       <c r="S4" s="4" t="s">
         <v>30</v>
       </c>
@@ -4883,7 +7682,7 @@
       <c r="Q5" s="6">
         <v>-0.003613471984863281</v>
       </c>
-      <c r="R5" s="10"/>
+      <c r="R5" s="5"/>
       <c r="S5" s="4" t="s">
         <v>30</v>
       </c>
@@ -4950,7 +7749,7 @@
       <c r="Q6" s="6">
         <v>0.008081912994384766</v>
       </c>
-      <c r="R6" s="10"/>
+      <c r="R6" s="5"/>
       <c r="S6" s="4" t="s">
         <v>30</v>
       </c>
@@ -5086,7 +7885,7 @@
       <c r="Q8" s="6">
         <v>0.03892982006072998</v>
       </c>
-      <c r="R8" s="10"/>
+      <c r="R8" s="5"/>
       <c r="S8" s="4" t="s">
         <v>30</v>
       </c>
@@ -5153,13 +7952,13 @@
       <c r="Q9" s="6">
         <v>0.182127833366394</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="R9" s="5"/>
       <c r="S9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T9" s="10"/>
+      <c r="T9" s="5"/>
       <c r="U9" s="4"/>
-      <c r="V9" s="10"/>
+      <c r="V9" s="5"/>
       <c r="W9" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -5214,7 +8013,7 @@
       <c r="Q10" s="6">
         <v>-0.01932746171951294</v>
       </c>
-      <c r="R10" s="10"/>
+      <c r="R10" s="5"/>
       <c r="S10" s="4" t="s">
         <v>30</v>
       </c>
@@ -5281,7 +8080,7 @@
       <c r="Q11" s="6">
         <v>0.1380934119224548</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="R11" s="5"/>
       <c r="S11" s="4" t="s">
         <v>30</v>
       </c>
@@ -5486,7 +8285,7 @@
       <c r="Q14" s="6">
         <v>0.1179535388946533</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="R14" s="5"/>
       <c r="S14" s="4" t="s">
         <v>30</v>
       </c>
@@ -5553,7 +8352,7 @@
       <c r="Q15" s="6">
         <v>0.1964856386184692</v>
       </c>
-      <c r="R15" s="10"/>
+      <c r="R15" s="5"/>
       <c r="S15" s="4" t="s">
         <v>30</v>
       </c>
@@ -5620,7 +8419,7 @@
       <c r="Q16" s="6">
         <v>0.008081912994384766</v>
       </c>
-      <c r="R16" s="10"/>
+      <c r="R16" s="5"/>
       <c r="S16" s="4" t="s">
         <v>30</v>
       </c>
@@ -5687,7 +8486,7 @@
       <c r="Q17" s="6">
         <v>-0.02024471759796143</v>
       </c>
-      <c r="R17" s="10"/>
+      <c r="R17" s="5"/>
       <c r="S17" s="4" t="s">
         <v>30</v>
       </c>
@@ -5754,7 +8553,7 @@
       <c r="Q18" s="6">
         <v>0.1010237336158752</v>
       </c>
-      <c r="R18" s="10"/>
+      <c r="R18" s="5"/>
       <c r="S18" s="4" t="s">
         <v>30</v>
       </c>
@@ -5821,7 +8620,7 @@
       <c r="Q19" s="6">
         <v>0.01318985223770142</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="5"/>
       <c r="S19" s="4" t="s">
         <v>30</v>
       </c>
@@ -5888,7 +8687,7 @@
       <c r="Q20" s="6">
         <v>0.1059253811836243</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="R20" s="5"/>
       <c r="S20" s="4" t="s">
         <v>30</v>
       </c>
@@ -5955,7 +8754,7 @@
       <c r="Q21" s="6">
         <v>-0.0127716064453125</v>
       </c>
-      <c r="R21" s="10"/>
+      <c r="R21" s="5"/>
       <c r="S21" s="4" t="s">
         <v>30</v>
       </c>
@@ -6022,7 +8821,7 @@
       <c r="Q22" s="6">
         <v>-0.01090991497039795</v>
       </c>
-      <c r="R22" s="10"/>
+      <c r="R22" s="5"/>
       <c r="S22" s="4" t="s">
         <v>30</v>
       </c>
@@ -6089,7 +8888,7 @@
       <c r="Q23" s="6">
         <v>-0.02807682752609253</v>
       </c>
-      <c r="R23" s="10"/>
+      <c r="R23" s="5"/>
       <c r="S23" s="4" t="s">
         <v>30</v>
       </c>
@@ -6156,7 +8955,7 @@
       <c r="Q24" s="6">
         <v>0.1121453642845154</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="R24" s="5"/>
       <c r="S24" s="4" t="s">
         <v>30</v>
       </c>
@@ -6292,7 +9091,7 @@
       <c r="Q26" s="6">
         <v>-0.02352333068847656</v>
       </c>
-      <c r="R26" s="10"/>
+      <c r="R26" s="5"/>
       <c r="S26" s="4" t="s">
         <v>30</v>
       </c>
@@ -6359,7 +9158,7 @@
       <c r="Q27" s="6">
         <v>-0.00355231761932373</v>
       </c>
-      <c r="R27" s="10"/>
+      <c r="R27" s="5"/>
       <c r="S27" s="4" t="s">
         <v>30</v>
       </c>
@@ -6426,7 +9225,7 @@
       <c r="Q28" s="6">
         <v>0.01116985082626343</v>
       </c>
-      <c r="R28" s="10"/>
+      <c r="R28" s="5"/>
       <c r="S28" s="4" t="s">
         <v>30</v>
       </c>
@@ -6493,7 +9292,7 @@
       <c r="Q29" s="6">
         <v>-0.008236348628997803</v>
       </c>
-      <c r="R29" s="10"/>
+      <c r="R29" s="5"/>
       <c r="S29" s="4" t="s">
         <v>30</v>
       </c>
@@ -6560,7 +9359,7 @@
       <c r="Q30" s="6">
         <v>0.1840580105781555</v>
       </c>
-      <c r="R30" s="10"/>
+      <c r="R30" s="5"/>
       <c r="S30" s="4" t="s">
         <v>30</v>
       </c>
@@ -6627,7 +9426,7 @@
       <c r="Q31" s="6">
         <v>0.09622359275817871</v>
       </c>
-      <c r="R31" s="10"/>
+      <c r="R31" s="5"/>
       <c r="S31" s="4" t="s">
         <v>30</v>
       </c>
@@ -6694,7 +9493,7 @@
       <c r="Q32" s="6">
         <v>0.0132947564125061</v>
       </c>
-      <c r="R32" s="10"/>
+      <c r="R32" s="5"/>
       <c r="S32" s="4" t="s">
         <v>30</v>
       </c>
@@ -6761,7 +9560,7 @@
       <c r="Q33" s="6">
         <v>-0.01932746171951294</v>
       </c>
-      <c r="R33" s="10"/>
+      <c r="R33" s="5"/>
       <c r="S33" s="4" t="s">
         <v>30</v>
       </c>
@@ -6828,13 +9627,13 @@
       <c r="Q34" s="6">
         <v>0.1845425963401794</v>
       </c>
-      <c r="R34" s="10"/>
+      <c r="R34" s="5"/>
       <c r="S34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T34" s="10"/>
+      <c r="T34" s="5"/>
       <c r="U34" s="4"/>
-      <c r="V34" s="10"/>
+      <c r="V34" s="5"/>
       <c r="W34" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
@@ -6889,7 +9688,7 @@
       <c r="Q35" s="6">
         <v>0.1033974885940552</v>
       </c>
-      <c r="R35" s="10"/>
+      <c r="R35" s="5"/>
       <c r="S35" s="4" t="s">
         <v>30</v>
       </c>
@@ -6956,7 +9755,7 @@
       <c r="Q36" s="6">
         <v>0.1275660991668701</v>
       </c>
-      <c r="R36" s="10"/>
+      <c r="R36" s="5"/>
       <c r="S36" s="4" t="s">
         <v>30</v>
       </c>
@@ -6976,7 +9775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -7001,7 +9800,7 @@
     <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -7132,7 +9931,7 @@
       <c r="Q2" s="6">
         <v>0.1039508879184723</v>
       </c>
-      <c r="R2" s="10"/>
+      <c r="R2" s="5"/>
       <c r="S2" s="4" t="s">
         <v>30</v>
       </c>
@@ -7268,7 +10067,7 @@
       <c r="Q4" s="6">
         <v>0.0535832941532135</v>
       </c>
-      <c r="R4" s="10"/>
+      <c r="R4" s="5"/>
       <c r="S4" s="4" t="s">
         <v>30</v>
       </c>
@@ -7335,7 +10134,7 @@
       <c r="Q5" s="6">
         <v>0.02456402778625488</v>
       </c>
-      <c r="R5" s="10"/>
+      <c r="R5" s="5"/>
       <c r="S5" s="4" t="s">
         <v>30</v>
       </c>
@@ -7402,7 +10201,7 @@
       <c r="Q6" s="6">
         <v>0.01113182306289673</v>
       </c>
-      <c r="R6" s="10"/>
+      <c r="R6" s="5"/>
       <c r="S6" s="4" t="s">
         <v>30</v>
       </c>
@@ -7538,7 +10337,7 @@
       <c r="Q8" s="6">
         <v>-0.01313227415084839</v>
       </c>
-      <c r="R8" s="10"/>
+      <c r="R8" s="5"/>
       <c r="S8" s="4" t="s">
         <v>30</v>
       </c>
@@ -7674,7 +10473,7 @@
       <c r="Q10" s="6">
         <v>-0.02214467525482178</v>
       </c>
-      <c r="R10" s="10"/>
+      <c r="R10" s="5"/>
       <c r="S10" s="4" t="s">
         <v>30</v>
       </c>
@@ -7741,7 +10540,7 @@
       <c r="Q11" s="6">
         <v>-0.004803240299224854</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="R11" s="5"/>
       <c r="S11" s="4" t="s">
         <v>30</v>
       </c>
@@ -7808,7 +10607,7 @@
       <c r="Q12" s="6">
         <v>0.1171183586120605</v>
       </c>
-      <c r="R12" s="10"/>
+      <c r="R12" s="5"/>
       <c r="S12" s="4" t="s">
         <v>30</v>
       </c>
@@ -7875,7 +10674,7 @@
       <c r="Q13" s="6">
         <v>-0.02570521831512451</v>
       </c>
-      <c r="R13" s="10"/>
+      <c r="R13" s="5"/>
       <c r="S13" s="4" t="s">
         <v>30</v>
       </c>
@@ -7942,7 +10741,7 @@
       <c r="Q14" s="6">
         <v>0.007090091705322266</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="R14" s="5"/>
       <c r="S14" s="4" t="s">
         <v>30</v>
       </c>
@@ -8078,7 +10877,7 @@
       <c r="Q16" s="6">
         <v>0.01513433456420898</v>
       </c>
-      <c r="R16" s="10"/>
+      <c r="R16" s="5"/>
       <c r="S16" s="4" t="s">
         <v>30</v>
       </c>
@@ -8283,7 +11082,7 @@
       <c r="Q19" s="6">
         <v>0.04834049940109253</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="5"/>
       <c r="S19" s="4" t="s">
         <v>30</v>
       </c>
@@ -8350,7 +11149,7 @@
       <c r="Q20" s="6">
         <v>0.03854042291641235</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="R20" s="5"/>
       <c r="S20" s="4" t="s">
         <v>30</v>
       </c>
@@ -8417,7 +11216,7 @@
       <c r="Q21" s="6">
         <v>0.0822325348854065</v>
       </c>
-      <c r="R21" s="10"/>
+      <c r="R21" s="5"/>
       <c r="S21" s="4" t="s">
         <v>30</v>
       </c>
@@ -8484,7 +11283,7 @@
       <c r="Q22" s="6">
         <v>0.05464631319046021</v>
       </c>
-      <c r="R22" s="10"/>
+      <c r="R22" s="5"/>
       <c r="S22" s="4" t="s">
         <v>30</v>
       </c>
@@ -8620,7 +11419,7 @@
       <c r="Q24" s="6">
         <v>0.006723463535308838</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="R24" s="5"/>
       <c r="S24" s="4" t="s">
         <v>30</v>
       </c>
@@ -8687,7 +11486,7 @@
       <c r="Q25" s="6">
         <v>0.02656590938568115</v>
       </c>
-      <c r="R25" s="10"/>
+      <c r="R25" s="5"/>
       <c r="S25" s="4" t="s">
         <v>30</v>
       </c>
@@ -8754,7 +11553,7 @@
       <c r="Q26" s="6">
         <v>0.04614520072937012</v>
       </c>
-      <c r="R26" s="10"/>
+      <c r="R26" s="5"/>
       <c r="S26" s="4" t="s">
         <v>30</v>
       </c>
@@ -8821,7 +11620,7 @@
       <c r="Q27" s="6">
         <v>-0.02606046199798584</v>
       </c>
-      <c r="R27" s="10"/>
+      <c r="R27" s="5"/>
       <c r="S27" s="4" t="s">
         <v>30</v>
       </c>
@@ -8888,7 +11687,7 @@
       <c r="Q28" s="6">
         <v>-0.009130001068115234</v>
       </c>
-      <c r="R28" s="10"/>
+      <c r="R28" s="5"/>
       <c r="S28" s="4" t="s">
         <v>30</v>
       </c>
@@ -8955,7 +11754,7 @@
       <c r="Q29" s="6">
         <v>0.1097291707992554</v>
       </c>
-      <c r="R29" s="10"/>
+      <c r="R29" s="5"/>
       <c r="S29" s="4" t="s">
         <v>30</v>
       </c>
@@ -9022,7 +11821,7 @@
       <c r="Q30" s="6">
         <v>-0.03032809495925903</v>
       </c>
-      <c r="R30" s="10"/>
+      <c r="R30" s="5"/>
       <c r="S30" s="4" t="s">
         <v>30</v>
       </c>
@@ -9089,7 +11888,7 @@
       <c r="Q31" s="6">
         <v>-0.01775515079498291</v>
       </c>
-      <c r="R31" s="10"/>
+      <c r="R31" s="5"/>
       <c r="S31" s="4" t="s">
         <v>30</v>
       </c>
@@ -9156,7 +11955,7 @@
       <c r="Q32" s="6">
         <v>0.1179110407829285</v>
       </c>
-      <c r="R32" s="10"/>
+      <c r="R32" s="5"/>
       <c r="S32" s="4" t="s">
         <v>30</v>
       </c>
@@ -9223,7 +12022,7 @@
       <c r="Q33" s="6">
         <v>0.002722799777984619</v>
       </c>
-      <c r="R33" s="10"/>
+      <c r="R33" s="5"/>
       <c r="S33" s="4" t="s">
         <v>30</v>
       </c>
@@ -9290,7 +12089,7 @@
       <c r="Q34" s="6">
         <v>0.003760874271392822</v>
       </c>
-      <c r="R34" s="10"/>
+      <c r="R34" s="5"/>
       <c r="S34" s="4" t="s">
         <v>30</v>
       </c>
@@ -9426,7 +12225,7 @@
       <c r="Q36" s="6">
         <v>0.03396165370941162</v>
       </c>
-      <c r="R36" s="10"/>
+      <c r="R36" s="5"/>
       <c r="S36" s="4" t="s">
         <v>30</v>
       </c>
@@ -9493,7 +12292,7 @@
       <c r="Q37" s="6">
         <v>0.04606205224990845</v>
       </c>
-      <c r="R37" s="10"/>
+      <c r="R37" s="5"/>
       <c r="S37" s="4" t="s">
         <v>30</v>
       </c>
@@ -9560,7 +12359,7 @@
       <c r="Q38" s="6">
         <v>0.1220819354057312</v>
       </c>
-      <c r="R38" s="10"/>
+      <c r="R38" s="5"/>
       <c r="S38" s="4" t="s">
         <v>30</v>
       </c>
@@ -9627,7 +12426,7 @@
       <c r="Q39" s="6">
         <v>0.07000714540481567</v>
       </c>
-      <c r="R39" s="10"/>
+      <c r="R39" s="5"/>
       <c r="S39" s="4" t="s">
         <v>30</v>
       </c>
@@ -9694,7 +12493,7 @@
       <c r="Q40" s="6">
         <v>-0.02607107162475586</v>
       </c>
-      <c r="R40" s="10"/>
+      <c r="R40" s="5"/>
       <c r="S40" s="4" t="s">
         <v>30</v>
       </c>
@@ -9761,7 +12560,7 @@
       <c r="Q41" s="6">
         <v>0.1169484555721283</v>
       </c>
-      <c r="R41" s="10"/>
+      <c r="R41" s="5"/>
       <c r="S41" s="4" t="s">
         <v>30</v>
       </c>
@@ -9828,7 +12627,7 @@
       <c r="Q42" s="6">
         <v>0.03685104846954346</v>
       </c>
-      <c r="R42" s="10"/>
+      <c r="R42" s="5"/>
       <c r="S42" s="4" t="s">
         <v>30</v>
       </c>
@@ -9895,7 +12694,7 @@
       <c r="Q43" s="6">
         <v>0.1752002239227295</v>
       </c>
-      <c r="R43" s="10"/>
+      <c r="R43" s="5"/>
       <c r="S43" s="4" t="s">
         <v>30</v>
       </c>
@@ -9962,7 +12761,7 @@
       <c r="Q44" s="6">
         <v>0.01336735486984253</v>
       </c>
-      <c r="R44" s="10"/>
+      <c r="R44" s="5"/>
       <c r="S44" s="4" t="s">
         <v>30</v>
       </c>
@@ -9996,7 +12795,7 @@
       <c r="F45" s="5">
         <v>-130</v>
       </c>
-      <c r="G45" s="10"/>
+      <c r="G45" s="5"/>
       <c r="H45" s="5">
         <v>8475683</v>
       </c>
@@ -10009,19 +12808,19 @@
       <c r="K45" s="5">
         <v>1</v>
       </c>
-      <c r="L45" s="12"/>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
       <c r="O45" s="4"/>
       <c r="P45" s="4"/>
-      <c r="Q45" s="12"/>
-      <c r="R45" s="10"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="5"/>
       <c r="S45" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T45" s="10"/>
+      <c r="T45" s="5"/>
       <c r="U45" s="4"/>
-      <c r="V45" s="10"/>
+      <c r="V45" s="5"/>
       <c r="W45" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
@@ -10043,7 +12842,7 @@
       <c r="F46" s="5">
         <v>-119</v>
       </c>
-      <c r="G46" s="10"/>
+      <c r="G46" s="5"/>
       <c r="H46" s="5">
         <v>8476914</v>
       </c>
@@ -10056,19 +12855,19 @@
       <c r="K46" s="5">
         <v>0</v>
       </c>
-      <c r="L46" s="12"/>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
       <c r="O46" s="4"/>
       <c r="P46" s="4"/>
-      <c r="Q46" s="12"/>
-      <c r="R46" s="10"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="5"/>
       <c r="S46" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="T46" s="10"/>
+      <c r="T46" s="5"/>
       <c r="U46" s="4"/>
-      <c r="V46" s="10"/>
+      <c r="V46" s="5"/>
       <c r="W46" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -10123,7 +12922,7 @@
       <c r="Q47" s="6">
         <v>0.03475642204284668</v>
       </c>
-      <c r="R47" s="10"/>
+      <c r="R47" s="5"/>
       <c r="S47" s="4" t="s">
         <v>30</v>
       </c>
@@ -10190,7 +12989,7 @@
       <c r="Q48" s="6">
         <v>0.07490524649620056</v>
       </c>
-      <c r="R48" s="10"/>
+      <c r="R48" s="5"/>
       <c r="S48" s="4" t="s">
         <v>30</v>
       </c>
@@ -10257,7 +13056,7 @@
       <c r="Q49" s="6">
         <v>-0.01547199487686157</v>
       </c>
-      <c r="R49" s="10"/>
+      <c r="R49" s="5"/>
       <c r="S49" s="4" t="s">
         <v>30</v>
       </c>
@@ -10324,7 +13123,7 @@
       <c r="Q50" s="6">
         <v>0.1245075166225433</v>
       </c>
-      <c r="R50" s="10"/>
+      <c r="R50" s="5"/>
       <c r="S50" s="4" t="s">
         <v>30</v>
       </c>
@@ -10391,7 +13190,7 @@
       <c r="Q51" s="6">
         <v>-0.03248739242553711</v>
       </c>
-      <c r="R51" s="10"/>
+      <c r="R51" s="5"/>
       <c r="S51" s="4" t="s">
         <v>30</v>
       </c>
@@ -10458,7 +13257,7 @@
       <c r="Q52" s="6">
         <v>0.01116511225700378</v>
       </c>
-      <c r="R52" s="10"/>
+      <c r="R52" s="5"/>
       <c r="S52" s="4" t="s">
         <v>30</v>
       </c>
@@ -10525,7 +13324,7 @@
       <c r="Q53" s="6">
         <v>0.0362401008605957</v>
       </c>
-      <c r="R53" s="10"/>
+      <c r="R53" s="5"/>
       <c r="S53" s="4" t="s">
         <v>30</v>
       </c>
@@ -10592,7 +13391,7 @@
       <c r="Q54" s="6">
         <v>0.04834049940109253</v>
       </c>
-      <c r="R54" s="10"/>
+      <c r="R54" s="5"/>
       <c r="S54" s="4" t="s">
         <v>30</v>
       </c>
@@ -10612,7 +13411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -10637,7 +13436,7 @@
     <col min="15" max="15" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -10768,7 +13567,7 @@
       <c r="Q2" s="6">
         <v>-0.007238090038299561</v>
       </c>
-      <c r="R2" s="10"/>
+      <c r="R2" s="5"/>
       <c r="S2" s="4" t="s">
         <v>30</v>
       </c>
@@ -10835,7 +13634,7 @@
       <c r="Q3" s="6">
         <v>-0.01135414838790894</v>
       </c>
-      <c r="R3" s="10"/>
+      <c r="R3" s="5"/>
       <c r="S3" s="4" t="s">
         <v>30</v>
       </c>
@@ -10902,7 +13701,7 @@
       <c r="Q4" s="6">
         <v>0.1053570508956909</v>
       </c>
-      <c r="R4" s="10"/>
+      <c r="R4" s="5"/>
       <c r="S4" s="4" t="s">
         <v>30</v>
       </c>
@@ -10969,7 +13768,7 @@
       <c r="Q5" s="6">
         <v>-0.01579836010932922</v>
       </c>
-      <c r="R5" s="10"/>
+      <c r="R5" s="5"/>
       <c r="S5" s="4" t="s">
         <v>30</v>
       </c>
@@ -11036,7 +13835,7 @@
       <c r="Q6" s="6">
         <v>-0.0183846652507782</v>
       </c>
-      <c r="R6" s="10"/>
+      <c r="R6" s="5"/>
       <c r="S6" s="4" t="s">
         <v>30</v>
       </c>
@@ -11103,7 +13902,7 @@
       <c r="Q7" s="6">
         <v>0.04997831583023071</v>
       </c>
-      <c r="R7" s="10"/>
+      <c r="R7" s="5"/>
       <c r="S7" s="4" t="s">
         <v>30</v>
       </c>
@@ -11170,7 +13969,7 @@
       <c r="Q8" s="6">
         <v>-0.01553666591644287</v>
       </c>
-      <c r="R8" s="10"/>
+      <c r="R8" s="5"/>
       <c r="S8" s="4" t="s">
         <v>30</v>
       </c>
@@ -11237,7 +14036,7 @@
       <c r="Q9" s="6">
         <v>-0.009258091449737549</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="R9" s="5"/>
       <c r="S9" s="4" t="s">
         <v>30</v>
       </c>
@@ -11304,7 +14103,7 @@
       <c r="Q10" s="6">
         <v>0.01179498434066772</v>
       </c>
-      <c r="R10" s="10"/>
+      <c r="R10" s="5"/>
       <c r="S10" s="4" t="s">
         <v>30</v>
       </c>
@@ -11371,7 +14170,7 @@
       <c r="Q11" s="6">
         <v>0.018074631690979</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="R11" s="5"/>
       <c r="S11" s="4" t="s">
         <v>30</v>
       </c>
@@ -11438,7 +14237,7 @@
       <c r="Q12" s="6">
         <v>0.02991747856140137</v>
       </c>
-      <c r="R12" s="10"/>
+      <c r="R12" s="5"/>
       <c r="S12" s="4" t="s">
         <v>30</v>
       </c>
@@ -11505,7 +14304,7 @@
       <c r="Q13" s="6">
         <v>0.005486428737640381</v>
       </c>
-      <c r="R13" s="10"/>
+      <c r="R13" s="5"/>
       <c r="S13" s="4" t="s">
         <v>30</v>
       </c>
@@ -11641,7 +14440,7 @@
       <c r="Q15" s="6">
         <v>-0.001067578792572021</v>
       </c>
-      <c r="R15" s="10"/>
+      <c r="R15" s="5"/>
       <c r="S15" s="4" t="s">
         <v>30</v>
       </c>
@@ -11708,7 +14507,7 @@
       <c r="Q16" s="6">
         <v>0.04005646705627441</v>
       </c>
-      <c r="R16" s="10"/>
+      <c r="R16" s="5"/>
       <c r="S16" s="4" t="s">
         <v>30</v>
       </c>
@@ -11775,7 +14574,7 @@
       <c r="Q17" s="6">
         <v>-0.02333515882492065</v>
       </c>
-      <c r="R17" s="10"/>
+      <c r="R17" s="5"/>
       <c r="S17" s="4" t="s">
         <v>30</v>
       </c>
@@ -11911,7 +14710,7 @@
       <c r="Q19" s="6">
         <v>-0.001394748687744141</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="5"/>
       <c r="S19" s="4" t="s">
         <v>30</v>
       </c>
@@ -11978,7 +14777,7 @@
       <c r="Q20" s="6">
         <v>0.001027047634124756</v>
       </c>
-      <c r="R20" s="10"/>
+      <c r="R20" s="5"/>
       <c r="S20" s="4" t="s">
         <v>30</v>
       </c>
@@ -12045,7 +14844,7 @@
       <c r="Q21" s="6">
         <v>0.006680965423583984</v>
       </c>
-      <c r="R21" s="10"/>
+      <c r="R21" s="5"/>
       <c r="S21" s="4" t="s">
         <v>30</v>
       </c>
@@ -12112,7 +14911,7 @@
       <c r="Q22" s="6">
         <v>0.0161786675453186</v>
       </c>
-      <c r="R22" s="10"/>
+      <c r="R22" s="5"/>
       <c r="S22" s="4" t="s">
         <v>30</v>
       </c>
@@ -12179,7 +14978,7 @@
       <c r="Q23" s="6">
         <v>0.03812432289123535</v>
       </c>
-      <c r="R23" s="10"/>
+      <c r="R23" s="5"/>
       <c r="S23" s="4" t="s">
         <v>30</v>
       </c>
@@ -12246,7 +15045,7 @@
       <c r="Q24" s="6">
         <v>0.1927165985107422</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="R24" s="5"/>
       <c r="S24" s="4" t="s">
         <v>30</v>
       </c>
@@ -12313,7 +15112,7 @@
       <c r="Q25" s="6">
         <v>-0.003809511661529541</v>
       </c>
-      <c r="R25" s="10"/>
+      <c r="R25" s="5"/>
       <c r="S25" s="4" t="s">
         <v>30</v>
       </c>
@@ -12380,7 +15179,7 @@
       <c r="Q26" s="6">
         <v>0.0184141993522644</v>
       </c>
-      <c r="R26" s="10"/>
+      <c r="R26" s="5"/>
       <c r="S26" s="4" t="s">
         <v>30</v>
       </c>
@@ -12447,7 +15246,7 @@
       <c r="Q27" s="6">
         <v>0.1005036234855652</v>
       </c>
-      <c r="R27" s="10"/>
+      <c r="R27" s="5"/>
       <c r="S27" s="4" t="s">
         <v>30</v>
       </c>
@@ -12514,7 +15313,7 @@
       <c r="Q28" s="6">
         <v>0.1906410455703735</v>
       </c>
-      <c r="R28" s="10"/>
+      <c r="R28" s="5"/>
       <c r="S28" s="4" t="s">
         <v>30</v>
       </c>
@@ -12581,7 +15380,7 @@
       <c r="Q29" s="6">
         <v>0.008916497230529785</v>
       </c>
-      <c r="R29" s="10"/>
+      <c r="R29" s="5"/>
       <c r="S29" s="4" t="s">
         <v>30</v>
       </c>
@@ -12648,7 +15447,7 @@
       <c r="Q30" s="6">
         <v>0.00318610668182373</v>
       </c>
-      <c r="R30" s="10"/>
+      <c r="R30" s="5"/>
       <c r="S30" s="4" t="s">
         <v>30</v>
       </c>
@@ -12715,7 +15514,7 @@
       <c r="Q31" s="6">
         <v>0.1029183864593506</v>
       </c>
-      <c r="R31" s="10"/>
+      <c r="R31" s="5"/>
       <c r="S31" s="4" t="s">
         <v>30</v>
       </c>
@@ -12851,7 +15650,7 @@
       <c r="Q33" s="6">
         <v>-0.01468655467033386</v>
       </c>
-      <c r="R33" s="10"/>
+      <c r="R33" s="5"/>
       <c r="S33" s="4" t="s">
         <v>30</v>
       </c>
@@ -12918,7 +15717,7 @@
       <c r="Q34" s="6">
         <v>0.04574540257453918</v>
       </c>
-      <c r="R34" s="10"/>
+      <c r="R34" s="5"/>
       <c r="S34" s="4" t="s">
         <v>30</v>
       </c>
@@ -13054,7 +15853,7 @@
       <c r="Q36" s="6">
         <v>0.05374270677566528</v>
       </c>
-      <c r="R36" s="10"/>
+      <c r="R36" s="5"/>
       <c r="S36" s="4" t="s">
         <v>30</v>
       </c>
@@ -13121,7 +15920,7 @@
       <c r="Q37" s="6">
         <v>-0.003143131732940674</v>
       </c>
-      <c r="R37" s="10"/>
+      <c r="R37" s="5"/>
       <c r="S37" s="4" t="s">
         <v>30</v>
       </c>
@@ -13188,7 +15987,7 @@
       <c r="Q38" s="6">
         <v>0.0111733078956604</v>
       </c>
-      <c r="R38" s="10"/>
+      <c r="R38" s="5"/>
       <c r="S38" s="4" t="s">
         <v>30</v>
       </c>
@@ -13255,7 +16054,7 @@
       <c r="Q39" s="6">
         <v>-0.01935425400733948</v>
       </c>
-      <c r="R39" s="10"/>
+      <c r="R39" s="5"/>
       <c r="S39" s="4" t="s">
         <v>30</v>
       </c>
@@ -13322,7 +16121,7 @@
       <c r="Q40" s="6">
         <v>0.03439640998840332</v>
       </c>
-      <c r="R40" s="10"/>
+      <c r="R40" s="5"/>
       <c r="S40" s="4" t="s">
         <v>30</v>
       </c>
@@ -13389,7 +16188,7 @@
       <c r="Q41" s="6">
         <v>0.04397225379943848</v>
       </c>
-      <c r="R41" s="10"/>
+      <c r="R41" s="5"/>
       <c r="S41" s="4" t="s">
         <v>30</v>
       </c>
@@ -13456,7 +16255,7 @@
       <c r="Q42" s="6">
         <v>0.001043915748596191</v>
       </c>
-      <c r="R42" s="10"/>
+      <c r="R42" s="5"/>
       <c r="S42" s="4" t="s">
         <v>30</v>
       </c>
@@ -13523,7 +16322,7 @@
       <c r="Q43" s="6">
         <v>0.2077014148235321</v>
       </c>
-      <c r="R43" s="10"/>
+      <c r="R43" s="5"/>
       <c r="S43" s="4" t="s">
         <v>30</v>
       </c>
@@ -13543,7 +16342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -17154,7 +19953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1688,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2581,6 +2581,83 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025020931</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.36635622382164</v>
+      </c>
+      <c r="N12" t="n">
+        <v>26.72875595092773</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.08613240718841553</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -6289,7 +6289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7977,6 +7977,65 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025020945</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>8479193</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -6289,7 +6289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8036,6 +8036,65 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025020945</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>8479193</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -6289,7 +6289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8095,6 +8095,65 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025020945</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>8479193</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -10039,7 +10039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10389,6 +10389,83 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020950</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5447976589202881</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8.959531784057617</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.03984713554382324</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -10039,7 +10039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10466,6 +10466,391 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025020951</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hofer</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8480981</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>25.29999923706055</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4678607881069183</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6.427842140197754</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0223352313041687</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025020951</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4928354918956757</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.432901620864868</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.01935961842536926</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025020948</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rittich</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8479496</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5199296474456787</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.985929489135742</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.008372247219085693</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025020952</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25.29999923706055</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.454034149646759</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.193170547485352</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02215629816055298</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025020952</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cooley</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8482445</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4930788278579712</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.384234428405762</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.0213807225227356</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -14665,7 +14665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14843,6 +14843,83 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025020954</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3958574831485748</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20.8285026550293</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.08261144161224365</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -14665,7 +14665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14920,6 +14920,83 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025020953</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shesterkin</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8478048</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.79999923706055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5511664748191833</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10.23329544067383</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.02963536977767944</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -14665,7 +14665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14997,6 +14997,160 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020953</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Merzlikins</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8478007</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3875715136528015</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22.48569679260254</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09089738130569458</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025020954</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.267238974571228</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.55220413208008</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2352485954761505</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -8,17 +8,18 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -37,17 +38,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color indexed="64"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color indexed="64"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color indexed="64"/>
       <sz val="12"/>
     </font>
     <font>
@@ -58,13 +56,23 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -92,16 +100,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -115,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,6 +852,3087 @@
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:W36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="3" max="4"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="11" min="5" max="5"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="8"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="9" max="10"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="11" min="12" max="14"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="15" max="16"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="11" min="17" max="17"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="18" max="18"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="19" max="19"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="20" max="20"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="21" max="21"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1" s="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>game_date</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>game_id</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>goalie_name</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>betting_line</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>line_over</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>line_under</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>goalie_id</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>team_abbrev</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>opponent_team</t>
+        </is>
+      </c>
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>predicted_saves</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>prob_over</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>confidence_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="18" t="inlineStr">
+        <is>
+          <t>confidence_bucket</t>
+        </is>
+      </c>
+      <c r="P1" s="18" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="Q1" s="20" t="inlineStr">
+        <is>
+          <t>ev</t>
+        </is>
+      </c>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
+          <t>bet_amount</t>
+        </is>
+      </c>
+      <c r="S1" s="18" t="inlineStr">
+        <is>
+          <t>bet_selection</t>
+        </is>
+      </c>
+      <c r="T1" s="19" t="inlineStr">
+        <is>
+          <t>actual_saves</t>
+        </is>
+      </c>
+      <c r="U1" s="18" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="V1" s="19" t="inlineStr">
+        <is>
+          <t>profit_loss</t>
+        </is>
+      </c>
+      <c r="W1" s="18" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1" s="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>2025020908</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Annunen</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>8481020</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="21" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="M2" s="21" t="n">
+        <v>0.4469998180866241</v>
+      </c>
+      <c r="N2" s="21" t="n">
+        <v>10.60003662109375</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q2" s="21" t="n">
+        <v>0.04561102390289307</v>
+      </c>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" customHeight="1" s="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>2025020903</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>8479312</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M3" s="21" t="n">
+        <v>0.5047785639762878</v>
+      </c>
+      <c r="N3" s="21" t="n">
+        <v>0.9557127952575684</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q3" s="21" t="n">
+        <v>-0.01903098821640015</v>
+      </c>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" customHeight="1" s="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="M4" s="21" t="n">
+        <v>0.6084129214286804</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>21.68258476257324</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q4" s="21" t="n">
+        <v>0.1133634150028229</v>
+      </c>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1" s="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M5" s="21" t="n">
+        <v>0.4867052435874939</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>2.658951282501221</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" s="21" t="n">
+        <v>-0.003613471984863281</v>
+      </c>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" s="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2025020906</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="21" t="n">
+        <v>20.60000038146973</v>
+      </c>
+      <c r="M6" s="21" t="n">
+        <v>0.5226449966430664</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>4.528999328613281</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" s="21" t="n">
+        <v>0.008081912994384766</v>
+      </c>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" s="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2025020906</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>8471734</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="21" t="n">
+        <v>25.29999923706055</v>
+      </c>
+      <c r="M7" s="21" t="n">
+        <v>0.2686306536197662</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>46.27386856079102</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q7" s="21" t="n">
+        <v>0.2075598239898682</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" s="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2025020908</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Annunen</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>8481020</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="21" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>0.4372606575489044</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>12.5478687286377</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" s="21" t="n">
+        <v>0.03892982006072998</v>
+      </c>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1" s="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2025020907</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M9" s="21" t="n">
+        <v>0.6919317841529846</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>38.38635635375977</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q9" s="21" t="n">
+        <v>0.182127833366394</v>
+      </c>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1" s="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2025020907</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="21" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M10" s="21" t="n">
+        <v>0.5261270999908447</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>5.225419998168945</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" s="21" t="n">
+        <v>-0.01932746171951294</v>
+      </c>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1" s="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2025020904</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tarasov</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>8480193</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>23.29999923706055</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>0.6663953065872192</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>33.27906036376953</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q11" s="21" t="n">
+        <v>0.1380934119224548</v>
+      </c>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1" s="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2025020904</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="21" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M12" s="21" t="n">
+        <v>0.3159419894218445</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>36.81160354614258</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="n">
+        <v>0.1914471685886383</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1" s="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2025020909</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="21" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="M13" s="21" t="n">
+        <v>0.6107866764068604</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>22.15733528137207</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" s="21" t="n">
+        <v>0.09387844800949097</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V13" s="21" t="n">
+        <v>1.869158878504673</v>
+      </c>
+    </row>
+    <row r="14" ht="18.75" customHeight="1" s="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2025020909</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Forsberg</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>8476341</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>0.367483377456665</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>26.50332450866699</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q14" s="21" t="n">
+        <v>0.1179535388946533</v>
+      </c>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" customHeight="1" s="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2025020906</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>8471734</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>25.29999923706055</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>0.2686306536197662</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>46.27386856079102</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q15" s="21" t="n">
+        <v>0.1964856386184692</v>
+      </c>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18.75" customHeight="1" s="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2025020906</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>20.60000038146973</v>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>0.5226449966430664</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>4.528999328613281</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" s="21" t="n">
+        <v>0.008081912994384766</v>
+      </c>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" s="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2025020903</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>0.5333266854286194</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>6.665337085723877</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" s="21" t="n">
+        <v>-0.02024471759796143</v>
+      </c>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18.75" customHeight="1" s="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="M18" s="21" t="n">
+        <v>0.6084129214286804</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>21.68258476257324</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" s="21" t="n">
+        <v>0.1010237336158752</v>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" s="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2025020908</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Annunen</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>8481020</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>0.4372606575489044</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>12.5478687286377</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" s="21" t="n">
+        <v>0.01318985223770142</v>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="18.75" customHeight="1" s="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-101</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>0.6084129214286804</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>21.68258476257324</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" s="21" t="n">
+        <v>0.1059253811836243</v>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="18.75" customHeight="1" s="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="21" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M21" s="21" t="n">
+        <v>0.4867052435874939</v>
+      </c>
+      <c r="N21" s="21" t="n">
+        <v>2.658951282501221</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" s="21" t="n">
+        <v>-0.0127716064453125</v>
+      </c>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="18.75" customHeight="1" s="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2025020907</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-116</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="21" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>0.5261270999908447</v>
+      </c>
+      <c r="N22" s="21" t="n">
+        <v>5.225419998168945</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>-0.01090991497039795</v>
+      </c>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18.75" customHeight="1" s="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2025020903</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-128</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="21" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M23" s="21" t="n">
+        <v>0.5333266854286194</v>
+      </c>
+      <c r="N23" s="21" t="n">
+        <v>6.665337085723877</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q23" s="21" t="n">
+        <v>-0.02807682752609253</v>
+      </c>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="18.75" customHeight="1" s="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>2025020908</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="21" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M24" s="21" t="n">
+        <v>0.6616948843002319</v>
+      </c>
+      <c r="N24" s="21" t="n">
+        <v>32.3389778137207</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" s="21" t="n">
+        <v>0.1121453642845154</v>
+      </c>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V24" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18.75" customHeight="1" s="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>2025020909</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Forsberg</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>8476341</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>0.367483377456665</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>26.50332450866699</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q25" s="21" t="n">
+        <v>0.1275660991668701</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V25" s="21" t="n">
+        <v>1.96078431372549</v>
+      </c>
+    </row>
+    <row r="26" ht="18.75" customHeight="1" s="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>2025020903</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>8479312</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>0.5047785639762878</v>
+      </c>
+      <c r="N26" s="21" t="n">
+        <v>0.9557127952575684</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" s="21" t="n">
+        <v>-0.02352333068847656</v>
+      </c>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18.75" customHeight="1" s="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2025020903</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>-137</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="21" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M27" s="21" t="n">
+        <v>0.4254932403564453</v>
+      </c>
+      <c r="N27" s="21" t="n">
+        <v>14.90135192871094</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q27" s="21" t="n">
+        <v>-0.00355231761932373</v>
+      </c>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18.75" customHeight="1" s="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2025020908</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Annunen</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-123</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>8481020</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="21" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="M28" s="21" t="n">
+        <v>0.4372606575489044</v>
+      </c>
+      <c r="N28" s="21" t="n">
+        <v>12.5478687286377</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" s="21" t="n">
+        <v>0.01116985082626343</v>
+      </c>
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V28" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18.75" customHeight="1" s="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-119</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>0.4867052435874939</v>
+      </c>
+      <c r="N29" s="21" t="n">
+        <v>2.658951282501221</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q29" s="21" t="n">
+        <v>-0.008236348628997803</v>
+      </c>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18.75" customHeight="1" s="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2025020904</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="21" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M30" s="21" t="n">
+        <v>0.3159419894218445</v>
+      </c>
+      <c r="N30" s="21" t="n">
+        <v>36.81160354614258</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q30" s="21" t="n">
+        <v>0.1840580105781555</v>
+      </c>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18.75" customHeight="1" s="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2025020909</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" s="21" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="M31" s="21" t="n">
+        <v>0.6107866764068604</v>
+      </c>
+      <c r="N31" s="21" t="n">
+        <v>22.15733528137207</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q31" s="21" t="n">
+        <v>0.09622359275817871</v>
+      </c>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T31" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V31" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18.75" customHeight="1" s="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2025020905</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="21" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M32" s="21" t="n">
+        <v>0.4867052435874939</v>
+      </c>
+      <c r="N32" s="21" t="n">
+        <v>2.658951282501221</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q32" s="21" t="n">
+        <v>0.0132947564125061</v>
+      </c>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18.75" customHeight="1" s="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2025020907</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="21" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M33" s="21" t="n">
+        <v>0.5261270999908447</v>
+      </c>
+      <c r="N33" s="21" t="n">
+        <v>5.225419998168945</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q33" s="21" t="n">
+        <v>-0.01932746171951294</v>
+      </c>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18.75" customHeight="1" s="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2025020907</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M34" s="21" t="n">
+        <v>0.6919317841529846</v>
+      </c>
+      <c r="N34" s="21" t="n">
+        <v>38.38635635375977</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q34" s="21" t="n">
+        <v>0.1845425963401794</v>
+      </c>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T34" s="5" t="n"/>
+      <c r="V34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="18.75" customHeight="1" s="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2025020909</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" s="21" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="M35" s="21" t="n">
+        <v>0.6107866764068604</v>
+      </c>
+      <c r="N35" s="21" t="n">
+        <v>22.15733528137207</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q35" s="21" t="n">
+        <v>0.1033974885940552</v>
+      </c>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18.75" customHeight="1" s="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2025020909</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BetOnline</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Forsberg</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>8476341</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="21" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M36" s="21" t="n">
+        <v>0.367483377456665</v>
+      </c>
+      <c r="N36" s="21" t="n">
+        <v>26.50332450866699</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q36" s="21" t="n">
+        <v>0.1275660991668701</v>
+      </c>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5396,7 +8488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -9083,7 +12175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -13620,7 +16712,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -14337,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14460,11 +17552,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2025020956</v>
+        <v>2025020962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14473,38 +17565,56 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29.5</v>
+        <v>24.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-127</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>-107</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-115</v>
+      </c>
       <c r="H2" t="n">
-        <v>8479193</v>
+        <v>8480313</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.4343631863594055</v>
+      </c>
+      <c r="N2" t="n">
+        <v>13.12736320495605</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.03075307607650757</v>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
@@ -14519,11 +17629,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2025020954</v>
+        <v>2025020960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -14532,46 +17642,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stolarz</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="F3" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G3" t="n">
         <v>-113</v>
       </c>
-      <c r="G3" t="n">
-        <v>-109</v>
-      </c>
       <c r="H3" t="n">
-        <v>8476932</v>
+        <v>8479312</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BUF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>VGK</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3958574831485748</v>
+        <v>0.4842335283756256</v>
       </c>
       <c r="N3" t="n">
-        <v>20.8285026550293</v>
+        <v>3.153294324874878</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -14580,7 +17690,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0.08261144161224365</v>
+        <v>-0.01474994421005249</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
@@ -14596,11 +17706,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2025020953</v>
+        <v>2025020965</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -14609,42 +17719,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shesterkin</t>
+          <t>DeSmith</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="F4" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G4" t="n">
         <v>-109</v>
       </c>
-      <c r="G4" t="n">
-        <v>-113</v>
-      </c>
       <c r="H4" t="n">
-        <v>8478048</v>
+        <v>8479193</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NYR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CBJ</t>
+          <t>CGY</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>25.79999923706055</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5511664748191833</v>
+        <v>0.4482367932796478</v>
       </c>
       <c r="N4" t="n">
-        <v>10.23329544067383</v>
+        <v>10.35264110565186</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -14657,877 +17767,18 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0.02963536977767944</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
+        <v>0.03023207187652588</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2025020953</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Merzlikins</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-113</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-109</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8478007</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CBJ</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NYR</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22.89999961853027</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.3875715136528015</v>
-      </c>
-      <c r="N5" t="n">
-        <v>22.48569679260254</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.09089738130569458</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2025020954</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Vladar</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-124</v>
-      </c>
-      <c r="G6" t="n">
-        <v>101</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8478435</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21.29999923706055</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.267238974571228</v>
-      </c>
-      <c r="N6" t="n">
-        <v>46.55220413208008</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.2352485954761505</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2025020954</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Vladar</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>101</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-124</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8478435</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>22.20000076293945</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2345519512891769</v>
-      </c>
-      <c r="N7" t="n">
-        <v>53.08960723876953</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>75%+</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.2118766307830811</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2025020954</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stolarz</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-108</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8476932</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>24</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.3958574831485748</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20.8285026550293</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.07143229246139526</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2025020957</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Daccord</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-117</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8478916</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.490447998046875</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.910400390625</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.02411508560180664</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2025020957</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Andersen</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>103</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8475883</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>21.20000076293945</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.4318583309650421</v>
-      </c>
-      <c r="N10" t="n">
-        <v>13.62833404541016</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.01258611679077148</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2025020956</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Oettinger</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-102</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-121</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8479979</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>VAN</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>23.29999923706055</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.466573566198349</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.685286521911621</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.01408493518829346</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2025020956</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Tolopilo</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-124</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8484268</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>VAN</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>23</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.40764981508255</v>
-      </c>
-      <c r="N12" t="n">
-        <v>18.47003746032715</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.03877878189086914</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025020958</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Blackwood</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8478406</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>23.70000076293945</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.5325372815132141</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.507456302642822</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.008727729320526123</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025020958</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Forsberg</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-117</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8476341</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>26.20000076293945</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2425356060266495</v>
-      </c>
-      <c r="N14" t="n">
-        <v>51.49288177490234</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>75%+</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2182939052581787</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025020955</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Gibson</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8476434</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NSH</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>24.10000038146973</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.225562646985054</v>
-      </c>
-      <c r="N15" t="n">
-        <v>54.88747406005859</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>75%+</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.2506278157234192</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15535,6 +17786,1281 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>game_date</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>game_id</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>goalie_name</t>
+        </is>
+      </c>
+      <c r="E1" s="22" t="inlineStr">
+        <is>
+          <t>betting_line</t>
+        </is>
+      </c>
+      <c r="F1" s="22" t="inlineStr">
+        <is>
+          <t>line_over</t>
+        </is>
+      </c>
+      <c r="G1" s="22" t="inlineStr">
+        <is>
+          <t>line_under</t>
+        </is>
+      </c>
+      <c r="H1" s="22" t="inlineStr">
+        <is>
+          <t>goalie_id</t>
+        </is>
+      </c>
+      <c r="I1" s="22" t="inlineStr">
+        <is>
+          <t>team_abbrev</t>
+        </is>
+      </c>
+      <c r="J1" s="22" t="inlineStr">
+        <is>
+          <t>opponent_team</t>
+        </is>
+      </c>
+      <c r="K1" s="22" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="L1" s="22" t="inlineStr">
+        <is>
+          <t>predicted_saves</t>
+        </is>
+      </c>
+      <c r="M1" s="22" t="inlineStr">
+        <is>
+          <t>prob_over</t>
+        </is>
+      </c>
+      <c r="N1" s="22" t="inlineStr">
+        <is>
+          <t>confidence_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="22" t="inlineStr">
+        <is>
+          <t>confidence_bucket</t>
+        </is>
+      </c>
+      <c r="P1" s="22" t="inlineStr">
+        <is>
+          <t>recommendation</t>
+        </is>
+      </c>
+      <c r="Q1" s="22" t="inlineStr">
+        <is>
+          <t>ev</t>
+        </is>
+      </c>
+      <c r="R1" s="22" t="inlineStr">
+        <is>
+          <t>bet_amount</t>
+        </is>
+      </c>
+      <c r="S1" s="22" t="inlineStr">
+        <is>
+          <t>bet_selection</t>
+        </is>
+      </c>
+      <c r="T1" s="22" t="inlineStr">
+        <is>
+          <t>actual_saves</t>
+        </is>
+      </c>
+      <c r="U1" s="22" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="V1" s="22" t="inlineStr">
+        <is>
+          <t>profit_loss</t>
+        </is>
+      </c>
+      <c r="W1" s="22" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2025020956</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8479193</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025020954</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>24</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3958574831485748</v>
+      </c>
+      <c r="N3" t="n">
+        <v>20.8285026550293</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.08261144161224365</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>23</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025020953</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Shesterkin</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8478048</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.79999923706055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5511664748191833</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10.23329544067383</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.02963536977767944</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>23</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020953</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Merzlikins</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8478007</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3875715136528015</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22.48569679260254</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09089738130569458</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>29</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025020954</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G6" t="n">
+        <v>101</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.267238974571228</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.55220413208008</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2352485954761505</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>29</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025020954</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>101</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2345519512891769</v>
+      </c>
+      <c r="N7" t="n">
+        <v>53.08960723876953</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2118766307830811</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>29</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025020954</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3958574831485748</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20.8285026550293</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.07143229246139526</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>23</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025020957</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Daccord</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8478916</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.490447998046875</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.910400390625</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.02411508560180664</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>35</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025020957</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Andersen</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>103</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8475883</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>21.20000076293945</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4318583309650421</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13.62833404541016</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01258611679077148</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>13</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025020956</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>23.29999923706055</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.466573566198349</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.685286521911621</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.01408493518829346</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>13</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025020956</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tolopilo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8484268</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.40764981508255</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18.47003746032715</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.03877878189086914</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>31</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025020958</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Blackwood</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8478406</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23.70000076293945</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5325372815132141</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.507456302642822</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.008727729320526123</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>19</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025020958</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Forsberg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8476341</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2425356060266495</v>
+      </c>
+      <c r="N14" t="n">
+        <v>51.49288177490234</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2182939052581787</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>35</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025020955</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.225562646985054</v>
+      </c>
+      <c r="N15" t="n">
+        <v>54.88747406005859</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2506278157234192</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>1.818181818181818</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
@@ -16315,7 +19841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
@@ -18493,7 +22019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -19236,7 +22762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -22673,7 +26199,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
@@ -26943,3085 +30469,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:W36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="3" max="4"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="11" min="5" max="5"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="6" max="8"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="9" max="10"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="11" max="11"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="11" min="12" max="14"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="15" max="16"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="11" min="17" max="17"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="18" max="18"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="19" max="19"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="20" max="20"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="21" max="21"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="22" max="22"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="1" min="23" max="23"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>game_date</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>game_id</t>
-        </is>
-      </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>book</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>goalie_name</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>betting_line</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>line_over</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>line_under</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>goalie_id</t>
-        </is>
-      </c>
-      <c r="I1" s="18" t="inlineStr">
-        <is>
-          <t>team_abbrev</t>
-        </is>
-      </c>
-      <c r="J1" s="18" t="inlineStr">
-        <is>
-          <t>opponent_team</t>
-        </is>
-      </c>
-      <c r="K1" s="19" t="inlineStr">
-        <is>
-          <t>is_home</t>
-        </is>
-      </c>
-      <c r="L1" s="20" t="inlineStr">
-        <is>
-          <t>predicted_saves</t>
-        </is>
-      </c>
-      <c r="M1" s="20" t="inlineStr">
-        <is>
-          <t>prob_over</t>
-        </is>
-      </c>
-      <c r="N1" s="20" t="inlineStr">
-        <is>
-          <t>confidence_pct</t>
-        </is>
-      </c>
-      <c r="O1" s="18" t="inlineStr">
-        <is>
-          <t>confidence_bucket</t>
-        </is>
-      </c>
-      <c r="P1" s="18" t="inlineStr">
-        <is>
-          <t>recommendation</t>
-        </is>
-      </c>
-      <c r="Q1" s="20" t="inlineStr">
-        <is>
-          <t>ev</t>
-        </is>
-      </c>
-      <c r="R1" s="19" t="inlineStr">
-        <is>
-          <t>bet_amount</t>
-        </is>
-      </c>
-      <c r="S1" s="18" t="inlineStr">
-        <is>
-          <t>bet_selection</t>
-        </is>
-      </c>
-      <c r="T1" s="19" t="inlineStr">
-        <is>
-          <t>actual_saves</t>
-        </is>
-      </c>
-      <c r="U1" s="18" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="V1" s="19" t="inlineStr">
-        <is>
-          <t>profit_loss</t>
-        </is>
-      </c>
-      <c r="W1" s="18" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1" s="1">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>2025020908</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Annunen</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>-121</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>8481020</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>NSH</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="21" t="n">
-        <v>24.20000076293945</v>
-      </c>
-      <c r="M2" s="21" t="n">
-        <v>0.4469998180866241</v>
-      </c>
-      <c r="N2" s="21" t="n">
-        <v>10.60003662109375</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q2" s="21" t="n">
-        <v>0.04561102390289307</v>
-      </c>
-      <c r="R2" s="5" t="n"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" customHeight="1" s="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>2025020903</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>8479312</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="M3" s="21" t="n">
-        <v>0.5047785639762878</v>
-      </c>
-      <c r="N3" s="21" t="n">
-        <v>0.9557127952575684</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q3" s="21" t="n">
-        <v>-0.01903098821640015</v>
-      </c>
-      <c r="R3" s="5" t="n"/>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1" s="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Allen</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>8474596</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="M4" s="21" t="n">
-        <v>0.6084129214286804</v>
-      </c>
-      <c r="N4" s="21" t="n">
-        <v>21.68258476257324</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="n">
-        <v>0.1133634150028229</v>
-      </c>
-      <c r="R4" s="5" t="n"/>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V4" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1" s="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sorokin</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>-115</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>-107</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>8478009</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="21" t="n">
-        <v>25.39999961853027</v>
-      </c>
-      <c r="M5" s="21" t="n">
-        <v>0.4867052435874939</v>
-      </c>
-      <c r="N5" s="21" t="n">
-        <v>2.658951282501221</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q5" s="21" t="n">
-        <v>-0.003613471984863281</v>
-      </c>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" customHeight="1" s="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>2025020906</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Bussi</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>-117</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>8483548</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NYR</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="21" t="n">
-        <v>20.60000038146973</v>
-      </c>
-      <c r="M6" s="21" t="n">
-        <v>0.5226449966430664</v>
-      </c>
-      <c r="N6" s="21" t="n">
-        <v>4.528999328613281</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="n">
-        <v>0.008081912994384766</v>
-      </c>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V6" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" customHeight="1" s="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>2025020906</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Quick</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>8471734</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NYR</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="21" t="n">
-        <v>25.29999923706055</v>
-      </c>
-      <c r="M7" s="21" t="n">
-        <v>0.2686306536197662</v>
-      </c>
-      <c r="N7" s="21" t="n">
-        <v>46.27386856079102</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="n">
-        <v>0.2075598239898682</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1" s="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>2025020908</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Annunen</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>8481020</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NSH</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>25.20000076293945</v>
-      </c>
-      <c r="M8" s="21" t="n">
-        <v>0.4372606575489044</v>
-      </c>
-      <c r="N8" s="21" t="n">
-        <v>12.5478687286377</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="n">
-        <v>0.03892982006072998</v>
-      </c>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T8" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1" s="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>2025020907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ullmark</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>-104</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>-118</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>8476999</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>OTT</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="M9" s="21" t="n">
-        <v>0.6919317841529846</v>
-      </c>
-      <c r="N9" s="21" t="n">
-        <v>38.38635635375977</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>65-70%</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="Q9" s="21" t="n">
-        <v>0.182127833366394</v>
-      </c>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1" s="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>2025020907</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Vladar</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-120</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>8478435</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>OTT</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="21" t="n">
-        <v>22.60000038146973</v>
-      </c>
-      <c r="M10" s="21" t="n">
-        <v>0.5261270999908447</v>
-      </c>
-      <c r="N10" s="21" t="n">
-        <v>5.225419998168945</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q10" s="21" t="n">
-        <v>-0.01932746171951294</v>
-      </c>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1" s="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>2025020904</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tarasov</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>-110</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>8480193</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>FLA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>TBL</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="21" t="n">
-        <v>23.29999923706055</v>
-      </c>
-      <c r="M11" s="21" t="n">
-        <v>0.6663953065872192</v>
-      </c>
-      <c r="N11" s="21" t="n">
-        <v>33.27906036376953</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>65-70%</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="Q11" s="21" t="n">
-        <v>0.1380934119224548</v>
-      </c>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1" s="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>2025020904</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Vasilevskiy</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>103</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>8476883</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>TBL</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>FLA</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="21" t="n">
-        <v>22.60000038146973</v>
-      </c>
-      <c r="M12" s="21" t="n">
-        <v>0.3159419894218445</v>
-      </c>
-      <c r="N12" s="21" t="n">
-        <v>36.81160354614258</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>65-70%</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q12" s="21" t="n">
-        <v>0.1914471685886383</v>
-      </c>
-      <c r="R12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>LOSS</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1" s="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>2025020909</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>-107</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>8478499</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>VGK</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="21" t="n">
-        <v>22.10000038146973</v>
-      </c>
-      <c r="M13" s="21" t="n">
-        <v>0.6107866764068604</v>
-      </c>
-      <c r="N13" s="21" t="n">
-        <v>22.15733528137207</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="n">
-        <v>0.09387844800949097</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="V13" s="21" t="n">
-        <v>1.869158878504673</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" customHeight="1" s="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>2025020909</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Forsberg</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-117</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>8476341</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>VGK</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="21" t="n">
-        <v>23.79999923706055</v>
-      </c>
-      <c r="M14" s="21" t="n">
-        <v>0.367483377456665</v>
-      </c>
-      <c r="N14" s="21" t="n">
-        <v>26.50332450866699</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q14" s="21" t="n">
-        <v>0.1179535388946533</v>
-      </c>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" s="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>2025020906</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Quick</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>8471734</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>NYR</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="21" t="n">
-        <v>25.29999923706055</v>
-      </c>
-      <c r="M15" s="21" t="n">
-        <v>0.2686306536197662</v>
-      </c>
-      <c r="N15" s="21" t="n">
-        <v>46.27386856079102</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>70-75%</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q15" s="21" t="n">
-        <v>0.1964856386184692</v>
-      </c>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" s="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>2025020906</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bussi</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>8483548</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CAR</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NYR</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="21" t="n">
-        <v>20.60000038146973</v>
-      </c>
-      <c r="M16" s="21" t="n">
-        <v>0.5226449966430664</v>
-      </c>
-      <c r="N16" s="21" t="n">
-        <v>4.528999328613281</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q16" s="21" t="n">
-        <v>0.008081912994384766</v>
-      </c>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" s="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>2025020903</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Silovs</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>-124</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>8481668</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="21" t="n">
-        <v>22.70000076293945</v>
-      </c>
-      <c r="M17" s="21" t="n">
-        <v>0.5333266854286194</v>
-      </c>
-      <c r="N17" s="21" t="n">
-        <v>6.665337085723877</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q17" s="21" t="n">
-        <v>-0.02024471759796143</v>
-      </c>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" customHeight="1" s="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Allen</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-120</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>8474596</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="M18" s="21" t="n">
-        <v>0.6084129214286804</v>
-      </c>
-      <c r="N18" s="21" t="n">
-        <v>21.68258476257324</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q18" s="21" t="n">
-        <v>0.1010237336158752</v>
-      </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V18" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" s="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>2025020908</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Annunen</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>8481020</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>NSH</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="21" t="n">
-        <v>25.20000076293945</v>
-      </c>
-      <c r="M19" s="21" t="n">
-        <v>0.4372606575489044</v>
-      </c>
-      <c r="N19" s="21" t="n">
-        <v>12.5478687286377</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q19" s="21" t="n">
-        <v>0.01318985223770142</v>
-      </c>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V19" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" customHeight="1" s="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Allen</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-101</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>8474596</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="M20" s="21" t="n">
-        <v>0.6084129214286804</v>
-      </c>
-      <c r="N20" s="21" t="n">
-        <v>21.68258476257324</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q20" s="21" t="n">
-        <v>0.1059253811836243</v>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T20" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V20" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="18.75" customHeight="1" s="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sorokin</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>-116</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>8478009</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="21" t="n">
-        <v>25.39999961853027</v>
-      </c>
-      <c r="M21" s="21" t="n">
-        <v>0.4867052435874939</v>
-      </c>
-      <c r="N21" s="21" t="n">
-        <v>2.658951282501221</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q21" s="21" t="n">
-        <v>-0.0127716064453125</v>
-      </c>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V21" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" customHeight="1" s="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2025020907</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Vladar</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>-116</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>8478435</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>OTT</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="21" t="n">
-        <v>22.60000038146973</v>
-      </c>
-      <c r="M22" s="21" t="n">
-        <v>0.5261270999908447</v>
-      </c>
-      <c r="N22" s="21" t="n">
-        <v>5.225419998168945</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q22" s="21" t="n">
-        <v>-0.01090991497039795</v>
-      </c>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="18.75" customHeight="1" s="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>2025020903</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Silovs</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>-128</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-101</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>8481668</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="21" t="n">
-        <v>22.70000076293945</v>
-      </c>
-      <c r="M23" s="21" t="n">
-        <v>0.5333266854286194</v>
-      </c>
-      <c r="N23" s="21" t="n">
-        <v>6.665337085723877</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q23" s="21" t="n">
-        <v>-0.02807682752609253</v>
-      </c>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T23" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V23" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="18.75" customHeight="1" s="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>2025020908</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Thompson</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>8480313</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>NSH</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="21" t="n">
-        <v>24.29999923706055</v>
-      </c>
-      <c r="M24" s="21" t="n">
-        <v>0.6616948843002319</v>
-      </c>
-      <c r="N24" s="21" t="n">
-        <v>32.3389778137207</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>65-70%</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q24" s="21" t="n">
-        <v>0.1121453642845154</v>
-      </c>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T24" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V24" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="18.75" customHeight="1" s="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>2025020909</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Forsberg</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>-121</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>8476341</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>VGK</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="21" t="n">
-        <v>23.79999923706055</v>
-      </c>
-      <c r="M25" s="21" t="n">
-        <v>0.367483377456665</v>
-      </c>
-      <c r="N25" s="21" t="n">
-        <v>26.50332450866699</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q25" s="21" t="n">
-        <v>0.1275660991668701</v>
-      </c>
-      <c r="R25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>WIN</t>
-        </is>
-      </c>
-      <c r="V25" s="21" t="n">
-        <v>1.96078431372549</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" customHeight="1" s="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>2025020903</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>-112</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-115</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>8479312</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="M26" s="21" t="n">
-        <v>0.5047785639762878</v>
-      </c>
-      <c r="N26" s="21" t="n">
-        <v>0.9557127952575684</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q26" s="21" t="n">
-        <v>-0.02352333068847656</v>
-      </c>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V26" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" customHeight="1" s="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>2025020903</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Silovs</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-137</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>8481668</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>PIT</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>BUF</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="21" t="n">
-        <v>23.10000038146973</v>
-      </c>
-      <c r="M27" s="21" t="n">
-        <v>0.4254932403564453</v>
-      </c>
-      <c r="N27" s="21" t="n">
-        <v>14.90135192871094</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q27" s="21" t="n">
-        <v>-0.00355231761932373</v>
-      </c>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V27" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" customHeight="1" s="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>2025020908</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Annunen</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>-105</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-123</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>8481020</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>NSH</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>WSH</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="21" t="n">
-        <v>25.20000076293945</v>
-      </c>
-      <c r="M28" s="21" t="n">
-        <v>0.4372606575489044</v>
-      </c>
-      <c r="N28" s="21" t="n">
-        <v>12.5478687286377</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>55-60%</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q28" s="21" t="n">
-        <v>0.01116985082626343</v>
-      </c>
-      <c r="R28" s="5" t="n"/>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="18.75" customHeight="1" s="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sorokin</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>-119</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-109</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>8478009</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="21" t="n">
-        <v>25.39999961853027</v>
-      </c>
-      <c r="M29" s="21" t="n">
-        <v>0.4867052435874939</v>
-      </c>
-      <c r="N29" s="21" t="n">
-        <v>2.658951282501221</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q29" s="21" t="n">
-        <v>-0.008236348628997803</v>
-      </c>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V29" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" customHeight="1" s="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>2025020904</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Vasilevskiy</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>-130</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>8476883</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>TBL</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>FLA</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="21" t="n">
-        <v>22.60000038146973</v>
-      </c>
-      <c r="M30" s="21" t="n">
-        <v>0.3159419894218445</v>
-      </c>
-      <c r="N30" s="21" t="n">
-        <v>36.81160354614258</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>65-70%</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q30" s="21" t="n">
-        <v>0.1840580105781555</v>
-      </c>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="18.75" customHeight="1" s="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>2025020909</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>-106</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>8478499</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>VGK</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="21" t="n">
-        <v>22.10000038146973</v>
-      </c>
-      <c r="M31" s="21" t="n">
-        <v>0.6107866764068604</v>
-      </c>
-      <c r="N31" s="21" t="n">
-        <v>22.15733528137207</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q31" s="21" t="n">
-        <v>0.09622359275817871</v>
-      </c>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V31" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75" customHeight="1" s="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>2025020905</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Underdog</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Sorokin</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>-122</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>8478009</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>NYI</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>NJD</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="21" t="n">
-        <v>25.39999961853027</v>
-      </c>
-      <c r="M32" s="21" t="n">
-        <v>0.4867052435874939</v>
-      </c>
-      <c r="N32" s="21" t="n">
-        <v>2.658951282501221</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q32" s="21" t="n">
-        <v>0.0132947564125061</v>
-      </c>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T32" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V32" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" customHeight="1" s="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>2025020907</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Vladar</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>-120</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>-108</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>8478435</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>OTT</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="21" t="n">
-        <v>22.60000038146973</v>
-      </c>
-      <c r="M33" s="21" t="n">
-        <v>0.5261270999908447</v>
-      </c>
-      <c r="N33" s="21" t="n">
-        <v>5.225419998168945</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>50-55%</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q33" s="21" t="n">
-        <v>-0.01932746171951294</v>
-      </c>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" customHeight="1" s="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>2025020907</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Ullmark</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>8476999</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>OTT</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="M34" s="21" t="n">
-        <v>0.6919317841529846</v>
-      </c>
-      <c r="N34" s="21" t="n">
-        <v>38.38635635375977</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>65-70%</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="Q34" s="21" t="n">
-        <v>0.1845425963401794</v>
-      </c>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="n"/>
-      <c r="V34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="18.75" customHeight="1" s="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>2025020909</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hill</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>-103</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>-125</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>8478499</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>VGK</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="21" t="n">
-        <v>22.10000038146973</v>
-      </c>
-      <c r="M35" s="21" t="n">
-        <v>0.6107866764068604</v>
-      </c>
-      <c r="N35" s="21" t="n">
-        <v>22.15733528137207</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="Q35" s="21" t="n">
-        <v>0.1033974885940552</v>
-      </c>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T35" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="18.75" customHeight="1" s="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>2025020909</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>BetOnline</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Forsberg</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-127</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>8476341</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>LAK</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>VGK</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="21" t="n">
-        <v>23.79999923706055</v>
-      </c>
-      <c r="M36" s="21" t="n">
-        <v>0.367483377456665</v>
-      </c>
-      <c r="N36" s="21" t="n">
-        <v>26.50332450866699</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>60-65%</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q36" s="21" t="n">
-        <v>0.1275660991668701</v>
-      </c>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T36" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>NO BET</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-</worksheet>
 </file>
--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -17429,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17779,6 +17779,237 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020959</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5909621715545654</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18.19243431091309</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.05607843399047852</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025020959</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Skinner</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8479973</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>24</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3963110446929932</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20.73779106140137</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.06880521774291992</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025020964</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>104</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4475766718387604</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10.4846658706665</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.00704801082611084</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -56,23 +56,13 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -123,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,9 +176,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -521,7 +508,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-01 10:39:38</t>
+          <t>2026-03-04 09:01:13</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -558,7 +545,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -571,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -584,7 +571,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -611,7 +598,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -626,7 +613,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -641,7 +628,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -705,7 +692,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>0</v>
@@ -717,7 +704,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-100.00%</t>
         </is>
       </c>
     </row>
@@ -728,19 +715,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>+26.77%</t>
+          <t>-6.82%</t>
         </is>
       </c>
     </row>
@@ -751,19 +738,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+57.63%</t>
+          <t>+43.97%</t>
         </is>
       </c>
     </row>
@@ -797,19 +784,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>-5.54%</t>
         </is>
       </c>
     </row>
@@ -820,19 +807,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>-100.00%</t>
+          <t>-3.91%</t>
         </is>
       </c>
     </row>
@@ -17429,7 +17416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17615,16 +17602,22 @@
       <c r="Q2" t="n">
         <v>0.03075307607650757</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>20</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17692,16 +17685,22 @@
       <c r="Q3" t="n">
         <v>-0.01474994421005249</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>27</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17769,16 +17768,22 @@
       <c r="Q4" t="n">
         <v>0.03023207187652588</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17846,16 +17851,22 @@
       <c r="Q5" t="n">
         <v>0.05607843399047852</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>34</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17923,16 +17934,22 @@
       <c r="Q6" t="n">
         <v>0.06880521774291992</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>26</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18000,16 +18017,1623 @@
       <c r="Q7" t="n">
         <v>-0.00704801082611084</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025020961</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Markstrom</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8474593</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>24.39999961853027</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2889412343502045</v>
+      </c>
+      <c r="N8" t="n">
+        <v>42.21175384521484</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1697743535041809</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0.847457627118644</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025020961</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bobrovsky</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8475683</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6027283668518066</v>
+      </c>
+      <c r="N9" t="n">
+        <v>20.54567337036133</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.07891881465911865</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>28</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025020963</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2372244596481323</v>
+      </c>
+      <c r="N10" t="n">
+        <v>52.55510711669922</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2458673119544983</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1.869158878504673</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025020963</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Annunen</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G11" t="n">
+        <v>101</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8481020</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3792397379875183</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24.15205192565918</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1232478320598602</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>24</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025020959</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G12" t="n">
+        <v>104</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5909621715545654</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18.19243431091309</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.03149080276489258</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>34</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0.7874015748031495</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025020959</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Skinner</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>103</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8479973</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3963110446929932</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20.73779106140137</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.04813337326049805</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>26</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025020962</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5843039751052856</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16.86079406738281</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.02874839305877686</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>23</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025020960</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Schmid</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G15" t="n">
+        <v>103</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8481033</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5436999797821045</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.739995956420898</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.0118556022644043</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>25</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025020964</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>102</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21.20000076293945</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4475766718387604</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.4846658706665</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.05737385153770447</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>18</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025020964</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G17" t="n">
+        <v>101</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8481519</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4476724565029144</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.46550846099854</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.05481508374214172</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>29</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025020965</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5884131789207458</v>
+      </c>
+      <c r="N18" t="n">
+        <v>17.68263626098633</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.07860922813415527</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>13</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025020966</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5123406648635864</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.468132972717285</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.01234066486358643</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>32</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025020966</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6054297089576721</v>
+      </c>
+      <c r="N20" t="n">
+        <v>21.08594131469727</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.07491326332092285</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>17</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025020967</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G21" t="n">
+        <v>105</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4147835671901703</v>
+      </c>
+      <c r="N21" t="n">
+        <v>17.04328727722168</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.09741151332855225</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>24</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025020967</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.3592054545879364</v>
+      </c>
+      <c r="N22" t="n">
+        <v>28.15890884399414</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.1309905648231506</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>17</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>1.923076923076923</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025020968</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3410094082355499</v>
+      </c>
+      <c r="N23" t="n">
+        <v>31.79811859130859</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1198201179504395</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>27</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025020968</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>28.60000038146973</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3189163506031036</v>
+      </c>
+      <c r="N24" t="n">
+        <v>36.21672821044922</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1335723400115967</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>21</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025020969</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G25" t="n">
+        <v>100</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.7159388065338135</v>
+      </c>
+      <c r="N25" t="n">
+        <v>43.18775939941406</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1663892865180969</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>21</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025020969</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Askarov</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8482137</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4216651022434235</v>
+      </c>
+      <c r="N26" t="n">
+        <v>15.66697978973389</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.05910414457321167</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>32</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>-1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18019,124 +19643,124 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>game_date</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>game_id</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>goalie_name</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>betting_line</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>line_over</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>line_under</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>goalie_id</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>team_abbrev</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>opponent_team</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>is_home</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>predicted_saves</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>prob_over</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>confidence_pct</t>
         </is>
       </c>
-      <c r="O1" s="22" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>confidence_bucket</t>
         </is>
       </c>
-      <c r="P1" s="22" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="Q1" s="22" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>ev</t>
         </is>
       </c>
-      <c r="R1" s="22" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>bet_amount</t>
         </is>
       </c>
-      <c r="S1" s="22" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>bet_selection</t>
         </is>
       </c>
-      <c r="T1" s="22" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>actual_saves</t>
         </is>
       </c>
-      <c r="U1" s="22" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="V1" s="22" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>profit_loss</t>
         </is>
       </c>
-      <c r="W1" s="22" t="inlineStr">
+      <c r="W1" s="10" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -19287,7 +20911,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -31,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -58,23 +58,13 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -125,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,9 +178,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -523,7 +510,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-04 09:01:13</t>
+          <t>2026-03-06 08:55:42</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -560,7 +547,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -573,7 +560,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -586,7 +573,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -613,7 +600,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -628,7 +615,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>+6.40</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -643,7 +630,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+9.27%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -753,10 +740,10 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -765,7 +752,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+43.97%</t>
+          <t>+44.26%</t>
         </is>
       </c>
     </row>
@@ -776,19 +763,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>-27.90%</t>
+          <t>-14.08%</t>
         </is>
       </c>
     </row>
@@ -799,19 +786,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>-5.54%</t>
+          <t>+13.20%</t>
         </is>
       </c>
     </row>
@@ -25140,7 +25127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25326,16 +25313,659 @@
       <c r="Q2" t="n">
         <v>-0.01362764835357666</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>30</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025020978</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Slip 1 (4-pick, 30% NHL Boost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025020975</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Woll</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G4" t="n">
+        <v>102</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8479361</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Slip 1 (4-pick, 30% NHL Boost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020976</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>20</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Slip 1 (4-pick, 30% NHL Boost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025020979</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Korpisalo</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8476914</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>23</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Slip 1 (4-pick, 30% NHL Boost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025020977</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Luukkonen</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8480045</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>27</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Slip 2 (3-pick Champions, $50 entry, $401.28 payout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025020978</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tarasov</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8480193</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>24</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>1.834862385321101</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Slip 2 (3-pick Champions, $50 entry, $401.28 payout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025020979</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Saros</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8477424</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>20</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.9803921568627452</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Slip 2 (3-pick Champions, $50 entry, $401.28 payout)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25345,124 +25975,124 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>game_date</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>game_id</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>goalie_name</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>betting_line</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>line_over</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>line_under</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>goalie_id</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>team_abbrev</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>opponent_team</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>is_home</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>predicted_saves</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>prob_over</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>confidence_pct</t>
         </is>
       </c>
-      <c r="O1" s="22" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>confidence_bucket</t>
         </is>
       </c>
-      <c r="P1" s="22" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="Q1" s="22" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>ev</t>
         </is>
       </c>
-      <c r="R1" s="22" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>bet_amount</t>
         </is>
       </c>
-      <c r="S1" s="22" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>bet_selection</t>
         </is>
       </c>
-      <c r="T1" s="22" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>actual_saves</t>
         </is>
       </c>
-      <c r="U1" s="22" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="V1" s="22" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>profit_loss</t>
         </is>
       </c>
-      <c r="W1" s="22" t="inlineStr">
+      <c r="W1" s="10" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -25801,131 +26431,133 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>game_date</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>game_id</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>goalie_name</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>betting_line</t>
         </is>
       </c>
-      <c r="F1" s="22" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>line_over</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>line_under</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>goalie_id</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>team_abbrev</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>opponent_team</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>is_home</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>predicted_saves</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>prob_over</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>confidence_pct</t>
         </is>
       </c>
-      <c r="O1" s="22" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>confidence_bucket</t>
         </is>
       </c>
-      <c r="P1" s="22" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="Q1" s="22" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>ev</t>
         </is>
       </c>
-      <c r="R1" s="22" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>bet_amount</t>
         </is>
       </c>
-      <c r="S1" s="22" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>bet_selection</t>
         </is>
       </c>
-      <c r="T1" s="22" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>actual_saves</t>
         </is>
       </c>
-      <c r="U1" s="22" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="V1" s="22" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>profit_loss</t>
         </is>
       </c>
-      <c r="W1" s="22" t="inlineStr">
+      <c r="W1" s="10" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -28031,7 +28663,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-06 08:55:42</t>
+          <t>2026-03-07 09:52:53</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+6.40</t>
+          <t>+7.29</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+9.27%</t>
+          <t>+10.12%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+44.26%</t>
+          <t>+37.05%</t>
         </is>
       </c>
     </row>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>-14.08%</t>
+          <t>-3.22%</t>
         </is>
       </c>
     </row>
@@ -25884,7 +25884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26070,16 +26070,295 @@
       <c r="Q2" t="n">
         <v>0.07564014196395874</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025020983</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>20</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Champions 3-pick (1.12x, 40% Boost, Won)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025020986</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8477465</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>26</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Champions 3-pick (1.12x, 40% Boost, Won)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020987</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0.9803921568627452</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Champions 3-pick (1.12x, 40% Boost, Won)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-07 09:52:53</t>
+          <t>2026-03-08 07:42:08</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+7.29</t>
+          <t>+9.09</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+10.12%</t>
+          <t>+11.65%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -755,19 +755,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+37.05%</t>
+          <t>+30.52%</t>
         </is>
       </c>
     </row>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>+13.15%</t>
         </is>
       </c>
     </row>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>+13.20%</t>
+          <t>+6.91%</t>
         </is>
       </c>
     </row>
@@ -28063,7 +28063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28249,16 +28249,22 @@
       <c r="Q2" t="n">
         <v>-0.02667444944381714</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28326,16 +28332,485 @@
       <c r="Q3" t="n">
         <v>0.08780920505523682</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>21</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Slip 2 (Champions 3-pick, $30 entry, $125.30 payout, Lost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025020993</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>20</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Slip 1 (Champions 3-pick, 30% NHL Boost, Won)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025020995</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Merzlikins</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8478007</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Slip 1 (Champions 3-pick, 30% NHL Boost, Won)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025020998</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G6" t="n">
+        <v>103</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>25</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Slip 1 (Champions 3-pick, 30% NHL Boost, Won)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025020990</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>27</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Slip 2 (Champions 3-pick, $30 entry, $125.30 payout, Lost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025020995</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Merzlikins</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8478007</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0.8849557522123894</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Slip 2 (Champions 3-pick, $30 entry, $125.30 payout, Lost)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-08 07:42:08</t>
+          <t>2026-03-08 08:00:41</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -35175,7 +35175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37069,6 +37069,314 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021058</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6750327348709106</v>
+      </c>
+      <c r="N25" t="n">
+        <v>35.00654602050781</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1423224806785583</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021058</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BetMGM</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.6750327348709106</v>
+      </c>
+      <c r="N26" t="n">
+        <v>35.00654602050781</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.1337483525276184</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2025021060</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BetMGM</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>28.70000076293945</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5467358231544495</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9.347164154052734</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.0184815526008606</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021060</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BetMGM</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Wallstedt</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8482661</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4964665174484253</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.7066965103149414</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.03135025501251221</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -41213,7 +41213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41875,6 +41875,468 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021070</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G9" t="n">
+        <v>105</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.317453145980835</v>
+      </c>
+      <c r="N9" t="n">
+        <v>36.50936889648438</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.19474196434021</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021072</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6459309458732605</v>
+      </c>
+      <c r="N10" t="n">
+        <v>29.18618965148926</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1176290512084961</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025021073</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4727703332901001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.44593334197998</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.001072227954864502</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021070</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6182592511177063</v>
+      </c>
+      <c r="N12" t="n">
+        <v>23.6518497467041</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.07280468940734863</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021068</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Woll</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G13" t="n">
+        <v>106</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8479361</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.70000076293945</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5444204807281494</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8.884096145629883</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.02079689502716064</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021071</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Saros</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8477424</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.525579571723938</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.115914344787598</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.01987498998641968</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -41213,7 +41213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42019,10 +42019,12 @@
       <c r="Q10" t="n">
         <v>0.1176290512084961</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -42173,10 +42175,12 @@
       <c r="Q12" t="n">
         <v>0.07280468940734863</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -42337,6 +42341,780 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021070</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>105</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.60000038146973</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3127377331256866</v>
+      </c>
+      <c r="N15" t="n">
+        <v>37.45245361328125</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1239435076713562</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021069</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>103</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3519134819507599</v>
+      </c>
+      <c r="N16" t="n">
+        <v>29.6173038482666</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1554757058620453</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021073</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4727703332901001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.44593334197998</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.01742571592330933</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021076</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Grubauer</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8475831</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5258022546768188</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.16045093536377</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.001992702484130859</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021073</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>100</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>26</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1964979022741318</v>
+      </c>
+      <c r="N19" t="n">
+        <v>60.70041656494141</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2539525628089905</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021075</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Luukkonen</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8480045</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>26</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3914657235145569</v>
+      </c>
+      <c r="N20" t="n">
+        <v>21.70685577392578</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.06307971477508545</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021075</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21.60000038146973</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5245155692100525</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.903113842010498</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.02451556921005249</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025021076</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Grubauer</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8475831</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>25.60000038146973</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5258022546768188</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.16045093536377</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.006907999515533447</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025021075</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G23" t="n">
+        <v>103</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.60000038146973</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.5245155692100525</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.903113842010498</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.0171264111995697</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021074</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bobrovsky</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G24" t="n">
+        <v>101</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8475683</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4673324525356293</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.533509254455566</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.03515508770942688</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -41213,7 +41213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43500,6 +43500,237 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2025021070</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G30" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.6182592511177063</v>
+      </c>
+      <c r="N30" t="n">
+        <v>23.6518497467041</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.06468784809112549</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2025021069</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>104</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>24</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.5986740589141846</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19.73481178283691</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.1084779798984528</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2025021073</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G32" t="n">
+        <v>103</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.4727703332901001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.44593334197998</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.03461882472038269</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-17 08:32:03</t>
+          <t>2026-03-18 07:18:41</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -614,7 +614,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+10.73</t>
+          <t>+12.69</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+9.50%</t>
+          <t>+10.23%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>-31.00%</t>
+          <t>-11.14%</t>
         </is>
       </c>
     </row>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+13.61%</t>
+          <t>+8.02%</t>
         </is>
       </c>
     </row>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>+27.95%</t>
+          <t>+31.86%</t>
         </is>
       </c>
     </row>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>+15.11%</t>
+          <t>+6.89%</t>
         </is>
       </c>
     </row>
@@ -41407,10 +41407,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41486,10 +41493,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1.96078431372549</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -41557,16 +41571,22 @@
       <c r="Q4" t="n">
         <v>0.06314593553543091</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>26</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41634,16 +41654,22 @@
       <c r="Q5" t="n">
         <v>-0.005129039287567139</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>31</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41711,16 +41737,22 @@
       <c r="Q6" t="n">
         <v>0.008264720439910889</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>21</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -41788,16 +41820,22 @@
       <c r="Q7" t="n">
         <v>0.09400284290313721</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>20</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41865,16 +41903,22 @@
       <c r="Q8" t="n">
         <v>-0.008730173110961914</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>21</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41942,16 +41986,22 @@
       <c r="Q9" t="n">
         <v>0.19474196434021</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>27</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -42027,10 +42077,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>21</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -42098,16 +42155,22 @@
       <c r="Q11" t="n">
         <v>-0.001072227954864502</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>27</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -42183,10 +42246,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>25</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1.666666666666667</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -42254,16 +42324,22 @@
       <c r="Q13" t="n">
         <v>-0.02079689502716064</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>31</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -42331,16 +42407,22 @@
       <c r="Q14" t="n">
         <v>-0.01987498998641968</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>36</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42416,10 +42498,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>27</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>2.325581395348837</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42487,16 +42576,22 @@
       <c r="Q16" t="n">
         <v>0.1554757058620453</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>28</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42564,16 +42659,22 @@
       <c r="Q17" t="n">
         <v>0.01742571592330933</v>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>27</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42641,16 +42742,22 @@
       <c r="Q18" t="n">
         <v>0.001992702484130859</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>19</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42726,10 +42833,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>32</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42797,16 +42911,22 @@
       <c r="Q20" t="n">
         <v>0.06307971477508545</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>28</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42874,16 +42994,22 @@
       <c r="Q21" t="n">
         <v>-0.02451556921005249</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>23</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -42951,16 +43077,22 @@
       <c r="Q22" t="n">
         <v>-0.006907999515533447</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>19</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -43028,16 +43160,22 @@
       <c r="Q23" t="n">
         <v>-0.0171264111995697</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>23</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -43105,16 +43243,22 @@
       <c r="Q24" t="n">
         <v>0.03515508770942688</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>17</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -43182,16 +43326,22 @@
       <c r="Q25" t="n">
         <v>-0.01841309666633606</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>19</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43259,16 +43409,22 @@
       <c r="Q26" t="n">
         <v>-0.003636598587036133</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>31</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -43336,16 +43492,22 @@
       <c r="Q27" t="n">
         <v>0.2479465007781982</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>32</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -43413,16 +43575,22 @@
       <c r="Q28" t="n">
         <v>0.05297869443893433</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>28</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -43490,16 +43658,22 @@
       <c r="Q29" t="n">
         <v>-0.01736074686050415</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>17</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -43567,16 +43741,22 @@
       <c r="Q30" t="n">
         <v>0.06468784809112549</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>25</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -43644,16 +43824,22 @@
       <c r="Q31" t="n">
         <v>0.1084779798984528</v>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>26</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -43721,16 +43907,22 @@
       <c r="Q32" t="n">
         <v>0.03461882472038269</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>27</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2026-03-19" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2026-03-18" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026-03-17" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026-03-16" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-03-15" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026-03-14" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026-03-13" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2026-03-12" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="2026-03-11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="2026-03-10" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="2026-03-09" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="2026-03-07" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="2026-03-06" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="2026-03-05" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="2026-03-04" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="2026-03-03" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="2026-03-02" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="2026-03-01" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="2026-02-28" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="2026-02-27" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="2026-02-26" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="2026-02-25" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="2026-02-05" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="2026-02-04" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="2026-02-03" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="2026-02-02" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="2026-02-01" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45560,7 +45560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45725,26 +45725,26 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>22.60000038146973</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3129619956016541</v>
+        <v>0.3668053448200226</v>
       </c>
       <c r="N2" t="n">
-        <v>37.40760040283203</v>
+        <v>26.63893127441406</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>0.152154266834259</v>
+        <v>0.09831094741821289</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
@@ -45802,13 +45802,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>21.39999961853027</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="M3" t="n">
-        <v>0.48086217045784</v>
+        <v>0.540851891040802</v>
       </c>
       <c r="N3" t="n">
-        <v>3.827565908432007</v>
+        <v>8.170377731323242</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0.01174867153167725</v>
+        <v>-0.004602670669555664</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
@@ -45879,17 +45879,17 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>22.5</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3008734583854675</v>
+        <v>0.353707879781723</v>
       </c>
       <c r="N4" t="n">
-        <v>39.82530832290649</v>
+        <v>29.25842475891113</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -45898,7 +45898,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>0.1775954411360636</v>
+        <v>0.1247609853744507</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
@@ -45910,6 +45910,314 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021085</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3668053448200226</v>
+      </c>
+      <c r="N5" t="n">
+        <v>26.63893127441406</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09831094741821289</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021083</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.353707879781723</v>
+      </c>
+      <c r="N6" t="n">
+        <v>29.25842475891113</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1247609853744507</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021086</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.540851891040802</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8.170377731323242</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.004602670669555664</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021086</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Shesterkin</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8478048</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5074593424797058</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.491868495941162</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.007459342479705811</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45560,7 +45560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47069,6 +47069,468 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021089</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3241397440433502</v>
+      </c>
+      <c r="N20" t="n">
+        <v>35.17205119132996</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1263107064071002</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021093</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Kuemper</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-117</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8475311</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5161674022674561</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.233480453491211</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.02300310464498634</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025021092</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.3311481177806854</v>
+      </c>
+      <c r="N22" t="n">
+        <v>33.77037644386292</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.12134057000212</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025021092</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8479312</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3103089332580566</v>
+      </c>
+      <c r="N23" t="n">
+        <v>37.93821334838867</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1569807863681116</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021090</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lankinen</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8480947</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3021916151046753</v>
+      </c>
+      <c r="N24" t="n">
+        <v>39.56167697906494</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1482588353457751</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021093</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ersson</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8481035</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3202995359897614</v>
+      </c>
+      <c r="N25" t="n">
+        <v>35.94009280204773</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1384160603405139</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45560,7 +45560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47069,6 +47069,699 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021084</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Reimer</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8473503</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4443843960762024</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11.12312078475952</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.02290532354996588</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021089</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3241397440433502</v>
+      </c>
+      <c r="N21" t="n">
+        <v>35.17205119132996</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1263107064071002</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025021089</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bobrovsky</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8475683</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.4846488237380981</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.070235252380371</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.00617992421656699</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025021091</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3577680885791779</v>
+      </c>
+      <c r="N23" t="n">
+        <v>28.44638228416443</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1073481904905896</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021090</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lankinen</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8480947</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3021916151046753</v>
+      </c>
+      <c r="N24" t="n">
+        <v>39.56167697906494</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1482588353457751</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021092</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8479312</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3103089332580566</v>
+      </c>
+      <c r="N25" t="n">
+        <v>37.93821334838867</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1569807863681116</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021092</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.3311481177806854</v>
+      </c>
+      <c r="N26" t="n">
+        <v>33.77037644386292</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.12134057000212</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2025021093</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ersson</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8481035</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.3202995359897614</v>
+      </c>
+      <c r="N27" t="n">
+        <v>35.94009280204773</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1384160603405139</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021093</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kuemper</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-117</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8475311</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5161674022674561</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.233480453491211</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.02300310464498634</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45796,7 +45796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45992,6 +45992,83 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025021096</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Soderblom</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8482821</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>28.20000076293945</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.4487713277339935</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10.24573421478271</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.02741909027099609</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45796,7 +45796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46069,6 +46069,160 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G4" t="n">
+        <v>101</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5455245971679688</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9.10491943359375</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.008046805858612061</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021094</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Woll</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8479361</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3905491828918457</v>
+      </c>
+      <c r="N5" t="n">
+        <v>21.89016342163086</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.06399625539779663</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45796,7 +45796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46223,6 +46223,160 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.516499936580658</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.299987316131592</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.01649993658065796</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021097</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3404632806777954</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31.90734481811523</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1246529817581177</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-20" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-03-20" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-03-19" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-03-18" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-03-17" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-03-16" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-03-15" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-03-14" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-03-13" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-03-12" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-03-11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-03-10" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-03-09" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-03-07" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-03-06" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-03-05" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-03-04" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-03-03" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-03-02" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-03-01" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-02-28" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-02-27" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-02-26" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-02-25" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-02-05" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-02-04" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-02-03" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-02-02" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-02-01" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45796,7 +45796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46038,17 +46038,17 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>28.20000076293945</v>
+        <v>28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4487713277339935</v>
+        <v>0.3903127610683441</v>
       </c>
       <c r="N3" t="n">
-        <v>10.24573421478271</v>
+        <v>21.93744778633118</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -46057,7 +46057,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0.02741909027099609</v>
+        <v>0.08587771512213205</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
@@ -46115,13 +46115,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>25.70000076293945</v>
+        <v>25.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5455245971679688</v>
+        <v>0.4855647087097168</v>
       </c>
       <c r="N4" t="n">
-        <v>9.10491943359375</v>
+        <v>2.887058258056641</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>-0.008046805858612061</v>
+        <v>0.01692285347933792</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
@@ -46192,17 +46192,17 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3905491828918457</v>
+        <v>0.3350647687911987</v>
       </c>
       <c r="N5" t="n">
-        <v>21.89016342163086</v>
+        <v>32.98704624176025</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -46211,7 +46211,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.06399625539779663</v>
+        <v>0.1194806857542559</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -46269,13 +46269,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>23.60000038146973</v>
+        <v>23.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.516499936580658</v>
+        <v>0.4565255641937256</v>
       </c>
       <c r="N6" t="n">
-        <v>3.299987316131592</v>
+        <v>8.694887161254883</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01649993658065796</v>
+        <v>0.04347443580627441</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
@@ -46346,17 +46346,17 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>25.70000076293945</v>
+        <v>25.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3404632806777954</v>
+        <v>0.28872349858284</v>
       </c>
       <c r="N7" t="n">
-        <v>31.90734481811523</v>
+        <v>42.25530028343201</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -46365,7 +46365,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.1246529817581177</v>
+        <v>0.1763927804869275</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -46377,6 +46377,622 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4855647087097168</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.887058258056641</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01692285347933792</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4565255641937256</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.694887161254883</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.04347443580627441</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021094</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4673799276351929</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6.524014472961426</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.02766957731530217</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025021094</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Woll</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8479361</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3350647687911987</v>
+      </c>
+      <c r="N11" t="n">
+        <v>32.98704624176025</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1194806857542559</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021096</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Blackwood</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8478406</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5026932954788208</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5386590957641602</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.01960150803920724</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021096</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Soderblom</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8482821</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3903127610683441</v>
+      </c>
+      <c r="N13" t="n">
+        <v>21.93744778633118</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.08587771512213205</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021097</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.28872349858284</v>
+      </c>
+      <c r="N14" t="n">
+        <v>42.25530028343201</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1763927804869275</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021098</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5190231800079346</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.804636001586914</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.006828058056715047</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45796,7 +45796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46993,6 +46993,468 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>103</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4855647087097168</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.887058258056641</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02182445385185955</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>103</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4565255641937256</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8.694887161254883</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.05086359836785076</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021094</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>103</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4673799276351929</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.524014472961426</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.04000923492638347</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021097</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.28872349858284</v>
+      </c>
+      <c r="N19" t="n">
+        <v>42.25530028343201</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1658219559626146</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021097</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tarasov</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8480193</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5870197415351868</v>
+      </c>
+      <c r="N20" t="n">
+        <v>17.40394830703735</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.07721581996655935</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021098</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2419283390045166</v>
+      </c>
+      <c r="N21" t="n">
+        <v>51.61433219909668</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2531211659459784</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45796,7 +45796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46993,6 +46993,468 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G16" t="n">
+        <v>103</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4565255641937256</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8.694887161254883</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.05086359836785076</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021095</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>103</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4855647087097168</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.887058258056641</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.02182445385185955</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021094</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>103</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4673799276351929</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.524014472961426</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.04000923492638347</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021097</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tarasov</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8480193</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5870197415351868</v>
+      </c>
+      <c r="N19" t="n">
+        <v>17.40394830703735</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.07721581996655935</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021097</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.28872349858284</v>
+      </c>
+      <c r="N20" t="n">
+        <v>42.25530028343201</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1658219559626146</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021098</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2419283390045166</v>
+      </c>
+      <c r="N21" t="n">
+        <v>51.61433219909668</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2531211659459784</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -43984,7 +43984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44536,13 +44536,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21.60000038146973</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5219912528991699</v>
+        <v>0.5320079922676086</v>
       </c>
       <c r="N7" t="n">
-        <v>4.398250579833984</v>
+        <v>6.401598453521729</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -44555,7 +44555,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.02694174647331238</v>
+        <v>0.0369584858417511</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
@@ -45853,13 +45853,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>21.60000038146973</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5219912528991699</v>
+        <v>0.5320079922676086</v>
       </c>
       <c r="N24" t="n">
-        <v>4.398250579833984</v>
+        <v>6.401598453521729</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>0.02694174647331238</v>
+        <v>0.0369584858417511</v>
       </c>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
@@ -45884,6 +45884,160 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021116</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Johansson</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G25" t="n">
+        <v>107</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8477992</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.39999961853027</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6889694333076477</v>
+      </c>
+      <c r="N25" t="n">
+        <v>37.79388809204102</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1237520575523376</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021115</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>102</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5320079922676086</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6.401598453521729</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.0369584858417511</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -43984,7 +43984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46038,6 +46038,314 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2025021117</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8479312</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2498214095830917</v>
+      </c>
+      <c r="N27" t="n">
+        <v>50.03571319580078</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.202667236328125</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021114</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>25.29999923706055</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4693869650363922</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6.122607231140137</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.004270672798156738</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2025021114</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>24</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4084679782390594</v>
+      </c>
+      <c r="N29" t="n">
+        <v>18.30640411376953</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.08658146858215332</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2025021115</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5320079922676086</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6.401598453521729</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.0270574688911438</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,45 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-24" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-23" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-22" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-21" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-20" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-03-24" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-03-23" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-03-22" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-03-21" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-03-20" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-03-19" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-03-18" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-03-17" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-03-16" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-03-15" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-03-14" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-03-13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-03-12" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-03-11" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-03-10" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-03-09" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-03-07" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-03-06" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-03-05" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-03-04" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-03-03" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-03-02" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-03-01" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-02-28" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-02-27" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-02-26" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-02-25" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-02-05" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="2026-02-04" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="2026-02-03" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="2026-02-02" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2026-02-01" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40289,7 +40289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40533,26 +40533,26 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>23.10000038146973</v>
+        <v>22.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4273654520511627</v>
+        <v>0.3698245584964752</v>
       </c>
       <c r="N3" t="n">
-        <v>14.52690982818604</v>
+        <v>26.03508830070496</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>0.07263457775115967</v>
+        <v>0.1301754415035248</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
@@ -40610,17 +40610,17 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>27.39999961853027</v>
+        <v>27.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.480671614408493</v>
+        <v>0.4212331175804138</v>
       </c>
       <c r="N4" t="n">
-        <v>3.865677118301392</v>
+        <v>15.75337648391724</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -40629,7 +40629,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0111880898475647</v>
+        <v>0.04825045049470356</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
@@ -40687,26 +40687,26 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>23.89999961853027</v>
+        <v>23.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3835527896881104</v>
+        <v>0.3285265266895294</v>
       </c>
       <c r="N5" t="n">
-        <v>23.28944206237793</v>
+        <v>34.29469466209412</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.09263765811920166</v>
+        <v>0.1476639495009467</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -40841,26 +40841,26 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>22.60000038146973</v>
+        <v>22.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7181222438812256</v>
+        <v>0.6140996217727661</v>
       </c>
       <c r="N7" t="n">
-        <v>43.62445068359375</v>
+        <v>22.81992435455322</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.1898203492164612</v>
+        <v>0.08579773498031329</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -40920,17 +40920,17 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>25.89999961853027</v>
+        <v>25.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5817586779594421</v>
+        <v>0.5223939418792725</v>
       </c>
       <c r="N8" t="n">
-        <v>16.35173606872559</v>
+        <v>4.478788375854492</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -40939,7 +40939,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0.02818727493286133</v>
+        <v>-0.01990637969021775</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -41153,17 +41153,17 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>22.20000076293945</v>
+        <v>21.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0.636540412902832</v>
+        <v>0.579328715801239</v>
       </c>
       <c r="N11" t="n">
-        <v>27.30808258056641</v>
+        <v>15.8657431602478</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -41172,7 +41172,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0.1173096299171448</v>
+        <v>0.06009794657046974</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -41232,17 +41232,17 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26.10000038146973</v>
+        <v>25.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4174536764621735</v>
+        <v>0.3604073524475098</v>
       </c>
       <c r="N12" t="n">
-        <v>16.50926399230957</v>
+        <v>27.91852951049805</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -41251,7 +41251,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0.04983609914779663</v>
+        <v>0.1068823671786585</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -41311,13 +41311,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>27.70000076293945</v>
+        <v>27.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5375425219535828</v>
+        <v>0.4775381088256836</v>
       </c>
       <c r="N13" t="n">
-        <v>7.508504390716553</v>
+        <v>4.492378234863281</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0.02297943830490112</v>
+        <v>-0.01670861573812599</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -41388,17 +41388,17 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4914213716983795</v>
+        <v>0.4317587614059448</v>
       </c>
       <c r="N14" t="n">
-        <v>1.715725660324097</v>
+        <v>13.64824771881104</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -41407,7 +41407,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01972323656082153</v>
+        <v>0.03993935180160235</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -41465,17 +41465,17 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>25.39999961853027</v>
+        <v>25.2</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2753289639949799</v>
+        <v>0.2300351709127426</v>
       </c>
       <c r="N15" t="n">
-        <v>44.93420791625977</v>
+        <v>53.99296581745148</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>75%+</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -41484,7 +41484,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0.1710996031761169</v>
+        <v>0.2163934005158288</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -41702,13 +41702,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>24.70000076293945</v>
+        <v>24.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5300005674362183</v>
+        <v>0.4699823558330536</v>
       </c>
       <c r="N18" t="n">
-        <v>6.000113487243652</v>
+        <v>6.003528833389282</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>0.01543748378753662</v>
+        <v>-0.009152862745495982</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
@@ -41858,26 +41858,26 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>24.79999923706055</v>
+        <v>24.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3616737723350525</v>
+        <v>0.3082170188426971</v>
       </c>
       <c r="N20" t="n">
-        <v>27.66524505615234</v>
+        <v>38.35659623146057</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>0.09287166595458984</v>
+        <v>0.1463284357027574</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
@@ -41935,26 +41935,26 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>23.29999923706055</v>
+        <v>23</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6518069505691528</v>
+        <v>0.595471203327179</v>
       </c>
       <c r="N21" t="n">
-        <v>30.36138916015625</v>
+        <v>19.09424066543579</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>0.1567574441432953</v>
+        <v>0.1004216983766839</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -42014,13 +42014,13 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>23.79999923706055</v>
+        <v>25.1</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3560058176517487</v>
+        <v>0.6251416206359863</v>
       </c>
       <c r="N22" t="n">
-        <v>28.79883575439453</v>
+        <v>25.02832412719727</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -42033,7 +42033,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>0.1091104745864868</v>
+        <v>0.1082334080755999</v>
       </c>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
@@ -42091,13 +42091,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>22.89999961853027</v>
+        <v>24.2</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3718112707138062</v>
+        <v>0.6457219123840332</v>
       </c>
       <c r="N23" t="n">
-        <v>25.63774490356445</v>
+        <v>29.14438247680664</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -42106,11 +42106,11 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>0.06297135353088379</v>
+        <v>0.1626301249444197</v>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
@@ -42245,17 +42245,17 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>24.39999961853027</v>
+        <v>24.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2844393849372864</v>
+        <v>0.2381392866373062</v>
       </c>
       <c r="N25" t="n">
-        <v>43.11212158203125</v>
+        <v>52.37214267253876</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>75%+</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -42264,7 +42264,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>0.1660110950469971</v>
+        <v>0.2123111638131442</v>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
@@ -42322,17 +42322,17 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>25.39999961853027</v>
+        <v>25.1</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4814599752426147</v>
+        <v>0.4220030903816223</v>
       </c>
       <c r="N26" t="n">
-        <v>3.708004951477051</v>
+        <v>15.59938192367554</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -42341,7 +42341,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>-0.01634371280670166</v>
+        <v>0.04311318868814518</v>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
@@ -42399,17 +42399,17 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>22.10000038146973</v>
+        <v>21.8</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6146973967552185</v>
+        <v>0.5564432144165039</v>
       </c>
       <c r="N27" t="n">
-        <v>22.93947982788086</v>
+        <v>11.28864288330078</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -42418,7 +42418,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>0.0931662917137146</v>
+        <v>0.03491211393803506</v>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
@@ -42476,17 +42476,17 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>23.29999923706055</v>
+        <v>23</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4689461886882782</v>
+        <v>0.409813404083252</v>
       </c>
       <c r="N28" t="n">
-        <v>6.210762023925781</v>
+        <v>18.03731918334961</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -42495,7 +42495,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>-0.0225176215171814</v>
+        <v>0.03661516734531944</v>
       </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
@@ -42553,13 +42553,13 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>24.60000038146973</v>
+        <v>24.3</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5152634382247925</v>
+        <v>0.4552974998950958</v>
       </c>
       <c r="N29" t="n">
-        <v>3.052687644958496</v>
+        <v>8.940500020980835</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>-0.001644790172576904</v>
+        <v>0.01199221973107245</v>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
@@ -42630,13 +42630,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>23.70000076293945</v>
+        <v>23.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5419632196426392</v>
+        <v>0.4819795787334442</v>
       </c>
       <c r="N30" t="n">
-        <v>8.392643928527832</v>
+        <v>3.604084253311157</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>-0.00554811954498291</v>
+        <v>0.01306992621705083</v>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
@@ -42784,17 +42784,17 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>26.10000038146973</v>
+        <v>25.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4209735095500946</v>
+        <v>0.3637465536594391</v>
       </c>
       <c r="N32" t="n">
-        <v>15.8052978515625</v>
+        <v>27.25068926811218</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -42803,7 +42803,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>0.04414272308349609</v>
+        <v>0.1013697254103284</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
@@ -42861,26 +42861,26 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>26.20000076293945</v>
+        <v>25.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0.440240204334259</v>
+        <v>0.3821225464344025</v>
       </c>
       <c r="N33" t="n">
-        <v>11.95195960998535</v>
+        <v>23.57549071311951</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>0.06956371665000916</v>
+        <v>0.127681375134225</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
@@ -42938,17 +42938,17 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>22.89999961853027</v>
+        <v>22.6</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3793360888957977</v>
+        <v>0.3245962858200073</v>
       </c>
       <c r="N34" t="n">
-        <v>24.13278198242188</v>
+        <v>35.08074283599854</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -42957,7 +42957,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>0.06119251251220703</v>
+        <v>0.1159323485412261</v>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
@@ -43015,17 +43015,17 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5966944694519043</v>
+        <v>0.5377652049064636</v>
       </c>
       <c r="N35" t="n">
-        <v>19.33889389038086</v>
+        <v>7.553040981292725</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -43034,7 +43034,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>0.03722310066223145</v>
+        <v>-0.02170616073230291</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
@@ -43092,13 +43092,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>23.60000038146973</v>
+        <v>23.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0.5223590135574341</v>
+        <v>0.4623549282550812</v>
       </c>
       <c r="N36" t="n">
-        <v>4.471802711486816</v>
+        <v>7.529014348983765</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>0.01255506277084351</v>
+        <v>-0.003639331924805922</v>
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
@@ -43169,17 +43169,17 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>26.60000038146973</v>
+        <v>26.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7234598398208618</v>
+        <v>0.6728992462158203</v>
       </c>
       <c r="N37" t="n">
-        <v>44.69196701049805</v>
+        <v>34.57984924316406</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>70-75%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -43188,7 +43188,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>0.2234598398208618</v>
+        <v>0.1728992462158203</v>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
@@ -43246,13 +43246,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>24.70000076293945</v>
+        <v>24.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0.5358247756958008</v>
+        <v>0.4758148491382599</v>
       </c>
       <c r="N38" t="n">
-        <v>7.164955139160156</v>
+        <v>4.837030172348022</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>0.04562869668006897</v>
+        <v>-0.01438122929311264</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -43323,26 +43323,26 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>22.89999961853027</v>
+        <v>22.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3738554716110229</v>
+        <v>0.3194994032382965</v>
       </c>
       <c r="N39" t="n">
-        <v>25.22890472412109</v>
+        <v>36.1001193523407</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>65-70%</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>0.08068996667861938</v>
+        <v>0.1350460513071581</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
@@ -43354,6 +43354,2316 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2025021121</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G40" t="n">
+        <v>104</v>
+      </c>
+      <c r="H40" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.3821225464344025</v>
+      </c>
+      <c r="N40" t="n">
+        <v>23.57549071311951</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.127681375134225</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2025021121</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Andersen</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>102</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8475883</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>23</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.595471203327179</v>
+      </c>
+      <c r="N41" t="n">
+        <v>19.09424066543579</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.1004216983766839</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2025021126</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G42" t="n">
+        <v>100</v>
+      </c>
+      <c r="H42" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.3698245584964752</v>
+      </c>
+      <c r="N42" t="n">
+        <v>26.03508830070496</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.1301754415035248</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2025021126</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.4212331175804138</v>
+      </c>
+      <c r="N43" t="n">
+        <v>15.75337648391724</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.04825045049470356</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2025021122</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>103</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H44" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.3245962858200073</v>
+      </c>
+      <c r="N44" t="n">
+        <v>35.08074283599854</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.1159323485412261</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2025021122</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.3285265266895294</v>
+      </c>
+      <c r="N45" t="n">
+        <v>34.29469466209412</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.1476639495009467</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2025021123</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Daccord</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G46" t="n">
+        <v>101</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8478916</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.5223939418792725</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.478788375854492</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>-0.01990637969021775</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2025021123</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bobrovsky</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H47" t="n">
+        <v>8475683</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.6140996217727661</v>
+      </c>
+      <c r="N47" t="n">
+        <v>22.81992435455322</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.08579773498031329</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2025021125</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>107</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.6457219123840332</v>
+      </c>
+      <c r="N48" t="n">
+        <v>29.14438247680664</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.1626301249444197</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2025021125</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.6251416206359863</v>
+      </c>
+      <c r="N49" t="n">
+        <v>25.02832412719727</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.1082334080755999</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2025021124</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Soderblom</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8482821</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.3604073524475098</v>
+      </c>
+      <c r="N50" t="n">
+        <v>27.91852951049805</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.1068823671786585</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2025021124</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Rittich</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H51" t="n">
+        <v>8479496</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.579328715801239</v>
+      </c>
+      <c r="N51" t="n">
+        <v>15.8657431602478</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.06009794657046974</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2025021120</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H52" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.4775381088256836</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.492378234863281</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>-0.01670861573812599</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2025021120</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H53" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.4317587614059448</v>
+      </c>
+      <c r="N53" t="n">
+        <v>13.64824771881104</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.03993935180160235</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2025021127</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>101</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.2300351709127426</v>
+      </c>
+      <c r="N54" t="n">
+        <v>53.99296581745148</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.2163934005158288</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2025021127</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G55" t="n">
+        <v>104</v>
+      </c>
+      <c r="H55" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.5377652049064636</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7.553040981292725</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>-0.02170616073230291</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2025021130</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.4623549282550812</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7.529014348983765</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>-0.003639331924805922</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2025021130</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>100</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H57" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.2381392866373062</v>
+      </c>
+      <c r="N57" t="n">
+        <v>52.37214267253876</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.2123111638131442</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2025021129</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Saros</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H58" t="n">
+        <v>8477424</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.4699823558330536</v>
+      </c>
+      <c r="N58" t="n">
+        <v>6.003528833389282</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>-0.009152862745495982</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2025021129</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H59" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.4220030903816223</v>
+      </c>
+      <c r="N59" t="n">
+        <v>15.59938192367554</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.04311318868814518</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2025021131</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H60" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.5564432144165039</v>
+      </c>
+      <c r="N60" t="n">
+        <v>11.28864288330078</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.03491211393803506</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2025021131</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>100</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.6728992462158203</v>
+      </c>
+      <c r="N61" t="n">
+        <v>34.57984924316406</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.1728992462158203</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2025021128</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Hofer</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H62" t="n">
+        <v>8480981</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.4552974998950958</v>
+      </c>
+      <c r="N62" t="n">
+        <v>8.940500020980835</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.01199221973107245</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2025021128</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lindgren</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H63" t="n">
+        <v>8479292</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>23</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.409813404083252</v>
+      </c>
+      <c r="N63" t="n">
+        <v>18.03731918334961</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.03661516734531944</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2025021133</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H64" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.3082170188426971</v>
+      </c>
+      <c r="N64" t="n">
+        <v>38.35659623146057</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.1463284357027574</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2025021133</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Kuemper</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H65" t="n">
+        <v>8475311</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.4819795787334442</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.604084253311157</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.01306992621705083</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2025021132</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F66" t="n">
+        <v>104</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H66" t="n">
+        <v>8477465</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.4758148491382599</v>
+      </c>
+      <c r="N66" t="n">
+        <v>4.837030172348022</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>-0.01438122929311264</v>
+      </c>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2025021132</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>101</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H67" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.6984090805053711</v>
+      </c>
+      <c r="N67" t="n">
+        <v>39.68181610107422</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.2008966426944258</v>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2025021134</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H68" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.3194994032382965</v>
+      </c>
+      <c r="N68" t="n">
+        <v>36.1001193523407</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.1350460513071581</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2025021134</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lankinen</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H69" t="n">
+        <v>8480947</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.3637465536594391</v>
+      </c>
+      <c r="N69" t="n">
+        <v>27.25068926811218</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.1013697254103284</v>
+      </c>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,45 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2026-03-24" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2026-03-23" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026-03-22" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026-03-21" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-03-20" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026-03-19" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026-03-18" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2026-03-17" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="2026-03-16" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="2026-03-15" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="2026-03-14" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="2026-03-13" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="2026-03-12" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="2026-03-11" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="2026-03-10" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="2026-03-09" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="2026-03-07" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="2026-03-06" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="2026-03-05" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="2026-03-04" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="2026-03-03" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="2026-03-02" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="2026-03-01" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="2026-02-28" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="2026-02-27" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="2026-02-26" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="2026-02-25" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="2026-02-05" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="2026-02-04" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="2026-02-03" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="2026-02-02" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="2026-02-01" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-24" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-23" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-22" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-21" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-20" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40289,7 +40289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:W99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40475,12 +40475,10 @@
       <c r="Q2" t="n">
         <v>0.05480927228927612</v>
       </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -40687,26 +40685,26 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>23.6</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3285265266895294</v>
+        <v>0.3835527896881104</v>
       </c>
       <c r="N5" t="n">
-        <v>34.29469466209412</v>
+        <v>23.28944206237793</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>0.1476639495009467</v>
+        <v>0.09263765811920166</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
@@ -40841,26 +40839,26 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>22.1</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6140996217727661</v>
+        <v>0.7181222438812256</v>
       </c>
       <c r="N7" t="n">
-        <v>22.81992435455322</v>
+        <v>43.62445068359375</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>0.08579773498031329</v>
+        <v>0.1898203492164612</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -40920,17 +40918,17 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>25.6</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5223939418792725</v>
+        <v>0.5817586779594421</v>
       </c>
       <c r="N8" t="n">
-        <v>4.478788375854492</v>
+        <v>16.35173606872559</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -40939,7 +40937,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>-0.01990637969021775</v>
+        <v>0.02818727493286133</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
@@ -41153,17 +41151,17 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>21.9</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="M11" t="n">
-        <v>0.579328715801239</v>
+        <v>0.636540412902832</v>
       </c>
       <c r="N11" t="n">
-        <v>15.8657431602478</v>
+        <v>27.30808258056641</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -41172,7 +41170,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>0.06009794657046974</v>
+        <v>0.1173096299171448</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -41232,17 +41230,17 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>25.8</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3604073524475098</v>
+        <v>0.4174536764621735</v>
       </c>
       <c r="N12" t="n">
-        <v>27.91852951049805</v>
+        <v>16.50926399230957</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -41251,7 +41249,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0.1068823671786585</v>
+        <v>0.04983609914779663</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -41311,13 +41309,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>27.4</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4775381088256836</v>
+        <v>0.5375425219535828</v>
       </c>
       <c r="N13" t="n">
-        <v>4.492378234863281</v>
+        <v>7.508504390716553</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -41330,7 +41328,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>-0.01670861573812599</v>
+        <v>0.02297943830490112</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
@@ -41388,17 +41386,17 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4317587614059448</v>
+        <v>0.4914213716983795</v>
       </c>
       <c r="N14" t="n">
-        <v>13.64824771881104</v>
+        <v>1.715725660324097</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -41407,7 +41405,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>0.03993935180160235</v>
+        <v>-0.01972323656082153</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -41465,17 +41463,17 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>25.2</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2300351709127426</v>
+        <v>0.2753289639949799</v>
       </c>
       <c r="N15" t="n">
-        <v>53.99296581745148</v>
+        <v>44.93420791625977</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>75%+</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -41484,7 +41482,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>0.2163934005158288</v>
+        <v>0.1710996031761169</v>
       </c>
       <c r="R15" t="n">
         <v>2</v>
@@ -41702,13 +41700,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>24.3</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4699823558330536</v>
+        <v>0.5300005674362183</v>
       </c>
       <c r="N18" t="n">
-        <v>6.003528833389282</v>
+        <v>6.000113487243652</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -41721,7 +41719,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>-0.009152862745495982</v>
+        <v>0.01543748378753662</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
@@ -41858,26 +41856,26 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>24.5</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3082170188426971</v>
+        <v>0.3616737723350525</v>
       </c>
       <c r="N20" t="n">
-        <v>38.35659623146057</v>
+        <v>27.66524505615234</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>0.1463284357027574</v>
+        <v>0.09287166595458984</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
@@ -42091,13 +42089,13 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>24.2</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6457219123840332</v>
+        <v>0.3718112707138062</v>
       </c>
       <c r="N23" t="n">
-        <v>29.14438247680664</v>
+        <v>25.63774490356445</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -42106,11 +42104,11 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>0.1626301249444197</v>
+        <v>0.06297135353088379</v>
       </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
@@ -42245,17 +42243,17 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>24.2</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2381392866373062</v>
+        <v>0.2844393849372864</v>
       </c>
       <c r="N25" t="n">
-        <v>52.37214267253876</v>
+        <v>43.11212158203125</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>75%+</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -42264,7 +42262,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>0.2123111638131442</v>
+        <v>0.1660110950469971</v>
       </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
@@ -42322,17 +42320,17 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>25.1</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4220030903816223</v>
+        <v>0.4814599752426147</v>
       </c>
       <c r="N26" t="n">
-        <v>15.59938192367554</v>
+        <v>3.708004951477051</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -42341,7 +42339,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>0.04311318868814518</v>
+        <v>-0.01634371280670166</v>
       </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
@@ -42399,17 +42397,17 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>21.8</v>
+        <v>22.10000038146973</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5564432144165039</v>
+        <v>0.6146973967552185</v>
       </c>
       <c r="N27" t="n">
-        <v>11.28864288330078</v>
+        <v>22.93947982788086</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -42418,7 +42416,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>0.03491211393803506</v>
+        <v>0.0931662917137146</v>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
@@ -42553,13 +42551,13 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>24.3</v>
+        <v>24.60000038146973</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4552974998950958</v>
+        <v>0.5152634382247925</v>
       </c>
       <c r="N29" t="n">
-        <v>8.940500020980835</v>
+        <v>3.052687644958496</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -42572,7 +42570,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>0.01199221973107245</v>
+        <v>-0.001644790172576904</v>
       </c>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
@@ -42630,13 +42628,13 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>23.4</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4819795787334442</v>
+        <v>0.5419632196426392</v>
       </c>
       <c r="N30" t="n">
-        <v>3.604084253311157</v>
+        <v>8.392643928527832</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -42649,7 +42647,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>0.01306992621705083</v>
+        <v>-0.00554811954498291</v>
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
@@ -42784,17 +42782,17 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>25.8</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3637465536594391</v>
+        <v>0.4209735095500946</v>
       </c>
       <c r="N32" t="n">
-        <v>27.25068926811218</v>
+        <v>15.8052978515625</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -42803,7 +42801,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>0.1013697254103284</v>
+        <v>0.04414272308349609</v>
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
@@ -42861,31 +42859,33 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>25.9</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="M33" t="n">
-        <v>0.3821225464344025</v>
+        <v>0.440240204334259</v>
       </c>
       <c r="N33" t="n">
-        <v>23.57549071311951</v>
+        <v>11.95195960998535</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.06956371665000916</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
           <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.127681375134225</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>NONE</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -42938,17 +42938,17 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>22.6</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3245962858200073</v>
+        <v>0.3793360888957977</v>
       </c>
       <c r="N34" t="n">
-        <v>35.08074283599854</v>
+        <v>24.13278198242188</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -42957,7 +42957,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>0.1159323485412261</v>
+        <v>0.06119251251220703</v>
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
@@ -43015,17 +43015,17 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="M35" t="n">
-        <v>0.5377652049064636</v>
+        <v>0.5966944694519043</v>
       </c>
       <c r="N35" t="n">
-        <v>7.553040981292725</v>
+        <v>19.33889389038086</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -43034,7 +43034,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>-0.02170616073230291</v>
+        <v>0.03722310066223145</v>
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
@@ -43169,17 +43169,17 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>26.4</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6728992462158203</v>
+        <v>0.7234598398208618</v>
       </c>
       <c r="N37" t="n">
-        <v>34.57984924316406</v>
+        <v>44.69196701049805</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -43188,7 +43188,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>0.1728992462158203</v>
+        <v>0.2234598398208618</v>
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
@@ -43246,13 +43246,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>24.4</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4758148491382599</v>
+        <v>0.5358247756958008</v>
       </c>
       <c r="N38" t="n">
-        <v>4.837030172348022</v>
+        <v>7.164955139160156</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>-0.01438122929311264</v>
+        <v>0.04562869668006897</v>
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
@@ -43323,26 +43323,26 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>22.6</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3194994032382965</v>
+        <v>0.3738554716110229</v>
       </c>
       <c r="N39" t="n">
-        <v>36.1001193523407</v>
+        <v>25.22890472412109</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>0.1350460513071581</v>
+        <v>0.08068996667861938</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
@@ -43400,26 +43400,26 @@
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>25.9</v>
+        <v>26.20000076293945</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3821225464344025</v>
+        <v>0.440240204334259</v>
       </c>
       <c r="N40" t="n">
-        <v>23.57549071311951</v>
+        <v>11.95195960998535</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>0.127681375134225</v>
+        <v>0.06956371665000916</v>
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
@@ -43575,10 +43575,12 @@
       <c r="Q42" t="n">
         <v>0.1301754415035248</v>
       </c>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -43708,17 +43710,17 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>22.6</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3245962858200073</v>
+        <v>0.3793360888957977</v>
       </c>
       <c r="N44" t="n">
-        <v>35.08074283599854</v>
+        <v>24.13278198242188</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -43727,7 +43729,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>0.1159323485412261</v>
+        <v>0.06119251251220703</v>
       </c>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
@@ -43785,31 +43787,33 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>23.6</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3285265266895294</v>
+        <v>0.3835527896881104</v>
       </c>
       <c r="N45" t="n">
-        <v>34.29469466209412</v>
+        <v>23.28944206237793</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.09263765811920166</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
           <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.1476639495009467</v>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>NONE</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -43862,17 +43866,17 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>25.6</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5223939418792725</v>
+        <v>0.5817586779594421</v>
       </c>
       <c r="N46" t="n">
-        <v>4.478788375854492</v>
+        <v>16.35173606872559</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -43881,7 +43885,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>-0.01990637969021775</v>
+        <v>0.02818727493286133</v>
       </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
@@ -43939,26 +43943,26 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>22.1</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6140996217727661</v>
+        <v>0.7181222438812256</v>
       </c>
       <c r="N47" t="n">
-        <v>22.81992435455322</v>
+        <v>43.62445068359375</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO BET</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>0.08579773498031329</v>
+        <v>0.1898203492164612</v>
       </c>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
@@ -44016,13 +44020,13 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>24.2</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6457219123840332</v>
+        <v>0.3718112707138062</v>
       </c>
       <c r="N48" t="n">
-        <v>29.14438247680664</v>
+        <v>25.63774490356445</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -44031,11 +44035,11 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>NO BET</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>0.1626301249444197</v>
+        <v>0.06297135353088379</v>
       </c>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
@@ -44170,17 +44174,17 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>25.8</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="M50" t="n">
-        <v>0.3604073524475098</v>
+        <v>0.4174536764621735</v>
       </c>
       <c r="N50" t="n">
-        <v>27.91852951049805</v>
+        <v>16.50926399230957</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -44189,7 +44193,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>0.1068823671786585</v>
+        <v>0.04983609914779663</v>
       </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
@@ -44247,17 +44251,17 @@
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>21.9</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="M51" t="n">
-        <v>0.579328715801239</v>
+        <v>0.636540412902832</v>
       </c>
       <c r="N51" t="n">
-        <v>15.8657431602478</v>
+        <v>27.30808258056641</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -44266,7 +44270,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>0.06009794657046974</v>
+        <v>0.1173096299171448</v>
       </c>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
@@ -44324,13 +44328,13 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>27.4</v>
+        <v>27.70000076293945</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4775381088256836</v>
+        <v>0.5375425219535828</v>
       </c>
       <c r="N52" t="n">
-        <v>4.492378234863281</v>
+        <v>7.508504390716553</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -44343,7 +44347,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>-0.01670861573812599</v>
+        <v>0.02297943830490112</v>
       </c>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
@@ -44401,17 +44405,17 @@
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4317587614059448</v>
+        <v>0.4914213716983795</v>
       </c>
       <c r="N53" t="n">
-        <v>13.64824771881104</v>
+        <v>1.715725660324097</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -44420,7 +44424,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>0.03993935180160235</v>
+        <v>-0.01972323656082153</v>
       </c>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
@@ -44478,17 +44482,17 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>25.2</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2300351709127426</v>
+        <v>0.2753289639949799</v>
       </c>
       <c r="N54" t="n">
-        <v>53.99296581745148</v>
+        <v>44.93420791625977</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>75%+</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -44497,7 +44501,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>0.2163934005158288</v>
+        <v>0.1710996031761169</v>
       </c>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
@@ -44555,17 +44559,17 @@
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="M55" t="n">
-        <v>0.5377652049064636</v>
+        <v>0.5966944694519043</v>
       </c>
       <c r="N55" t="n">
-        <v>7.553040981292725</v>
+        <v>19.33889389038086</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>50-55%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -44574,7 +44578,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>-0.02170616073230291</v>
+        <v>0.03722310066223145</v>
       </c>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
@@ -44709,17 +44713,17 @@
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>24.2</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2381392866373062</v>
+        <v>0.2844393849372864</v>
       </c>
       <c r="N57" t="n">
-        <v>52.37214267253876</v>
+        <v>43.11212158203125</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>75%+</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -44728,7 +44732,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>0.2123111638131442</v>
+        <v>0.1660110950469971</v>
       </c>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
@@ -44786,13 +44790,13 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>24.3</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4699823558330536</v>
+        <v>0.5300005674362183</v>
       </c>
       <c r="N58" t="n">
-        <v>6.003528833389282</v>
+        <v>6.000113487243652</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -44805,7 +44809,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>-0.009152862745495982</v>
+        <v>0.01543748378753662</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
@@ -44863,17 +44867,17 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>25.1</v>
+        <v>25.39999961853027</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4220030903816223</v>
+        <v>0.4814599752426147</v>
       </c>
       <c r="N59" t="n">
-        <v>15.59938192367554</v>
+        <v>3.708004951477051</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>50-55%</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -44882,7 +44886,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>0.04311318868814518</v>
+        <v>-0.01634371280670166</v>
       </c>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
@@ -44940,17 +44944,17 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>21.8</v>
+        <v>22.10000038146973</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5564432144165039</v>
+        <v>0.6146973967552185</v>
       </c>
       <c r="N60" t="n">
-        <v>11.28864288330078</v>
+        <v>22.93947982788086</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>55-60%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -44959,7 +44963,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>0.03491211393803506</v>
+        <v>0.0931662917137146</v>
       </c>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
@@ -45017,17 +45021,17 @@
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>26.4</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="M61" t="n">
-        <v>0.6728992462158203</v>
+        <v>0.7234598398208618</v>
       </c>
       <c r="N61" t="n">
-        <v>34.57984924316406</v>
+        <v>44.69196701049805</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -45036,7 +45040,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>0.1728992462158203</v>
+        <v>0.2234598398208618</v>
       </c>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
@@ -45094,13 +45098,13 @@
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>24.3</v>
+        <v>24.60000038146973</v>
       </c>
       <c r="M62" t="n">
-        <v>0.4552974998950958</v>
+        <v>0.5152634382247925</v>
       </c>
       <c r="N62" t="n">
-        <v>8.940500020980835</v>
+        <v>3.052687644958496</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -45113,7 +45117,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>0.01199221973107245</v>
+        <v>-0.001644790172576904</v>
       </c>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
@@ -45248,31 +45252,33 @@
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>24.5</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3082170188426971</v>
+        <v>0.3616737723350525</v>
       </c>
       <c r="N64" t="n">
-        <v>38.35659623146057</v>
+        <v>27.66524505615234</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.09287166595458984</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
           <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>0.1463284357027574</v>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>NONE</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -45325,13 +45331,13 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>23.4</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="M65" t="n">
-        <v>0.4819795787334442</v>
+        <v>0.5419632196426392</v>
       </c>
       <c r="N65" t="n">
-        <v>3.604084253311157</v>
+        <v>8.392643928527832</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -45344,7 +45350,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>0.01306992621705083</v>
+        <v>-0.00554811954498291</v>
       </c>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
@@ -45402,13 +45408,13 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>24.4</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="M66" t="n">
-        <v>0.4758148491382599</v>
+        <v>0.5358247756958008</v>
       </c>
       <c r="N66" t="n">
-        <v>4.837030172348022</v>
+        <v>7.164955139160156</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -45421,7 +45427,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>-0.01438122929311264</v>
+        <v>0.04562869668006897</v>
       </c>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
@@ -45479,17 +45485,17 @@
         <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>25.5</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="M67" t="n">
-        <v>0.6984090805053711</v>
+        <v>0.7465118765830994</v>
       </c>
       <c r="N67" t="n">
-        <v>39.68181610107422</v>
+        <v>49.30237579345703</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>70-75%</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -45498,12 +45504,14 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>0.2008966426944258</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
+        <v>0.2489994466304779</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -45556,31 +45564,33 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>22.6</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="M68" t="n">
-        <v>0.3194994032382965</v>
+        <v>0.3738554716110229</v>
       </c>
       <c r="N68" t="n">
-        <v>36.1001193523407</v>
+        <v>25.22890472412109</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>65-70%</t>
+          <t>60-65%</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.08068996667861938</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
           <t>UNDER</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>0.1350460513071581</v>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>NONE</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -45633,17 +45643,17 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>25.8</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3637465536594391</v>
+        <v>0.4209735095500946</v>
       </c>
       <c r="N69" t="n">
-        <v>27.25068926811218</v>
+        <v>15.8052978515625</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>60-65%</t>
+          <t>55-60%</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -45652,7 +45662,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>0.1013697254103284</v>
+        <v>0.04414272308349609</v>
       </c>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
@@ -45664,6 +45674,2316 @@
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2025021121</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Andersen</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G70" t="n">
+        <v>102</v>
+      </c>
+      <c r="H70" t="n">
+        <v>8475883</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.6562603116035461</v>
+      </c>
+      <c r="N70" t="n">
+        <v>31.25206184387207</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.1007047295570374</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2025021121</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G71" t="n">
+        <v>104</v>
+      </c>
+      <c r="H71" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>26.20000076293945</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.440240204334259</v>
+      </c>
+      <c r="N71" t="n">
+        <v>11.95195960998535</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.06956371665000916</v>
+      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2025021126</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>27.39999961853027</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.480671614408493</v>
+      </c>
+      <c r="N72" t="n">
+        <v>3.865677118301392</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>-0.02195602655410767</v>
+      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2025021126</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F73" t="n">
+        <v>101</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H73" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.4157732725143433</v>
+      </c>
+      <c r="N73" t="n">
+        <v>16.84534454345703</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.03065532445907593</v>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2025021122</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>103</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H74" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.3793360888957977</v>
+      </c>
+      <c r="N74" t="n">
+        <v>24.13278198242188</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.06119251251220703</v>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2025021122</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H75" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3835527896881104</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.28944206237793</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.09263765811920166</v>
+      </c>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2025021123</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Bobrovsky</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H76" t="n">
+        <v>8475683</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.7181222438812256</v>
+      </c>
+      <c r="N76" t="n">
+        <v>43.62445068359375</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.1898203492164612</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2025021123</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Daccord</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G77" t="n">
+        <v>101</v>
+      </c>
+      <c r="H77" t="n">
+        <v>8478916</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.5817586779594421</v>
+      </c>
+      <c r="N77" t="n">
+        <v>16.35173606872559</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.02818727493286133</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2025021125</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>101</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H78" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.3560058176517487</v>
+      </c>
+      <c r="N78" t="n">
+        <v>28.79883575439453</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.09042280912399292</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2025021125</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F79" t="n">
+        <v>107</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-130</v>
+      </c>
+      <c r="H79" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.3718112707138062</v>
+      </c>
+      <c r="N79" t="n">
+        <v>25.63774490356445</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.06297135353088379</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2025021124</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Rittich</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H80" t="n">
+        <v>8479496</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.636540412902832</v>
+      </c>
+      <c r="N80" t="n">
+        <v>27.30808258056641</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.1173096299171448</v>
+      </c>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2025021124</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Soderblom</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H81" t="n">
+        <v>8482821</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.4174536764621735</v>
+      </c>
+      <c r="N81" t="n">
+        <v>16.50926399230957</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.04983609914779663</v>
+      </c>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2025021120</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H82" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>27.70000076293945</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.5375425219535828</v>
+      </c>
+      <c r="N82" t="n">
+        <v>7.508504390716553</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.02297943830490112</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2025021120</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H83" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.4914213716983795</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1.715725660324097</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>-0.01972323656082153</v>
+      </c>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2025021127</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F84" t="n">
+        <v>101</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H84" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.2753289639949799</v>
+      </c>
+      <c r="N84" t="n">
+        <v>44.93420791625977</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.1710996031761169</v>
+      </c>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2025021127</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G85" t="n">
+        <v>104</v>
+      </c>
+      <c r="H85" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>25</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.5966944694519043</v>
+      </c>
+      <c r="N85" t="n">
+        <v>19.33889389038086</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.03722310066223145</v>
+      </c>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2025021130</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F86" t="n">
+        <v>101</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H86" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.5223590135574341</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4.471802711486816</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.02484658360481262</v>
+      </c>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2025021130</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F87" t="n">
+        <v>100</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H87" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>24.39999961853027</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.2844393849372864</v>
+      </c>
+      <c r="N87" t="n">
+        <v>43.11212158203125</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.1660110950469971</v>
+      </c>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2025021129</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Saros</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H88" t="n">
+        <v>8477424</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.5300005674362183</v>
+      </c>
+      <c r="N88" t="n">
+        <v>6.000113487243652</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.01543748378753662</v>
+      </c>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2025021129</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H89" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.4814599752426147</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3.708004951477051</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>-0.01634371280670166</v>
+      </c>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2025021131</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H90" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.6146973967552185</v>
+      </c>
+      <c r="N90" t="n">
+        <v>22.93947982788086</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.0931662917137146</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2025021131</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>100</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H91" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>26.60000038146973</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.7234598398208618</v>
+      </c>
+      <c r="N91" t="n">
+        <v>44.69196701049805</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.2234598398208618</v>
+      </c>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2025021128</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H92" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>23.70000076293945</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.5431087613105774</v>
+      </c>
+      <c r="N92" t="n">
+        <v>8.62175178527832</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.03815823793411255</v>
+      </c>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2025021128</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Hofer</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H93" t="n">
+        <v>8480981</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.5152634382247925</v>
+      </c>
+      <c r="N93" t="n">
+        <v>3.052687644958496</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>-0.001644790172576904</v>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2025021133</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Kuemper</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H94" t="n">
+        <v>8475311</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>23.70000076293945</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.5419632196426392</v>
+      </c>
+      <c r="N94" t="n">
+        <v>8.392643928527832</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>-0.00554811954498291</v>
+      </c>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2025021133</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H95" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.3616737723350525</v>
+      </c>
+      <c r="N95" t="n">
+        <v>27.66524505615234</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.09287166595458984</v>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2025021132</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>101</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H96" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.7465118765830994</v>
+      </c>
+      <c r="N96" t="n">
+        <v>49.30237579345703</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.2489994466304779</v>
+      </c>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2025021132</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F97" t="n">
+        <v>104</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H97" t="n">
+        <v>8477465</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.5358247756958008</v>
+      </c>
+      <c r="N97" t="n">
+        <v>7.164955139160156</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.04562869668006897</v>
+      </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2025021134</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lankinen</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H98" t="n">
+        <v>8480947</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.4209735095500946</v>
+      </c>
+      <c r="N98" t="n">
+        <v>15.8052978515625</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.04414272308349609</v>
+      </c>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2025021134</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H99" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.3738554716110229</v>
+      </c>
+      <c r="N99" t="n">
+        <v>25.22890472412109</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.08068996667861938</v>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -40289,7 +40289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W99"/>
+  <dimension ref="A1:W100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47984,6 +47984,83 @@
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2025021127</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G100" t="n">
+        <v>102</v>
+      </c>
+      <c r="H100" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.3849294185638428</v>
+      </c>
+      <c r="N100" t="n">
+        <v>23.01411628723145</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.1200210750102997</v>
+      </c>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-23 08:36:12</t>
+          <t>2026-03-25 06:30:27</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+15.25</t>
+          <t>+19.47</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -651,7 +651,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+10.45%</t>
+          <t>+12.40%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>-17.49%</t>
+          <t>-27.80%</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+10.76%</t>
+          <t>+10.07%</t>
         </is>
       </c>
     </row>
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>+29.55%</t>
+          <t>+30.94%</t>
         </is>
       </c>
     </row>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>+13.22%</t>
+          <t>+27.16%</t>
         </is>
       </c>
     </row>
@@ -40475,16 +40475,22 @@
       <c r="Q2" t="n">
         <v>0.05480927228927612</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>41</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40552,16 +40558,22 @@
       <c r="Q3" t="n">
         <v>0.1301754415035248</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>30</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40629,16 +40641,22 @@
       <c r="Q4" t="n">
         <v>0.04825045049470356</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>24</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40706,16 +40724,22 @@
       <c r="Q5" t="n">
         <v>0.09263765811920166</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>18</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40783,16 +40807,22 @@
       <c r="Q6" t="n">
         <v>0.08578014373779297</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>32</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40868,10 +40898,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>22</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40939,16 +40976,22 @@
       <c r="Q8" t="n">
         <v>0.02818727493286133</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>21</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41024,10 +41067,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.9090909090909092</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41095,16 +41145,22 @@
       <c r="Q10" t="n">
         <v>0.07863920927047729</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -41180,10 +41236,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -41259,10 +41322,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>44</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41330,16 +41400,22 @@
       <c r="Q13" t="n">
         <v>0.02297943830490112</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>18</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -41407,16 +41483,22 @@
       <c r="Q14" t="n">
         <v>-0.01972323656082153</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>31</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41485,17 +41567,24 @@
         <v>0.1710996031761169</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>19</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41571,10 +41660,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>20</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41643,17 +41739,24 @@
         <v>0.1763901114463806</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>2.564102564102564</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41721,16 +41824,22 @@
       <c r="Q18" t="n">
         <v>0.01543748378753662</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>27</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41799,17 +41908,24 @@
         <v>0.2088967561721802</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>26</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>2.830188679245283</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41877,16 +41993,22 @@
       <c r="Q20" t="n">
         <v>0.09287166595458984</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>23</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -41962,10 +42084,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>14</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -42033,16 +42162,22 @@
       <c r="Q22" t="n">
         <v>0.1082334080755999</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -42110,16 +42245,22 @@
       <c r="Q23" t="n">
         <v>0.06297135353088379</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>24</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -42187,16 +42328,22 @@
       <c r="Q24" t="n">
         <v>0.003128230571746826</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>23</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -42264,16 +42411,22 @@
       <c r="Q25" t="n">
         <v>0.1660110950469971</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -42341,16 +42494,22 @@
       <c r="Q26" t="n">
         <v>-0.01634371280670166</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>13</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -42418,16 +42577,22 @@
       <c r="Q27" t="n">
         <v>0.0931662917137146</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>17</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -42495,16 +42660,22 @@
       <c r="Q28" t="n">
         <v>0.03661516734531944</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -42572,16 +42743,22 @@
       <c r="Q29" t="n">
         <v>-0.001644790172576904</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>21</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -42649,16 +42826,22 @@
       <c r="Q30" t="n">
         <v>-0.00554811954498291</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>21</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -42726,16 +42909,22 @@
       <c r="Q31" t="n">
         <v>0.02362966537475586</v>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>16</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -42803,16 +42992,22 @@
       <c r="Q32" t="n">
         <v>0.04414272308349609</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>29</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -42888,10 +43083,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>41</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -42959,16 +43161,22 @@
       <c r="Q34" t="n">
         <v>0.06119251251220703</v>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>32</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -43036,16 +43244,22 @@
       <c r="Q35" t="n">
         <v>0.03722310066223145</v>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>20</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -43113,16 +43327,22 @@
       <c r="Q36" t="n">
         <v>-0.003639331924805922</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>23</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -43190,16 +43410,22 @@
       <c r="Q37" t="n">
         <v>0.2234598398208618</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>26</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -43267,16 +43493,22 @@
       <c r="Q38" t="n">
         <v>0.04562869668006897</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>16</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -43344,16 +43576,22 @@
       <c r="Q39" t="n">
         <v>0.08068996667861938</v>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>27</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -43421,16 +43659,22 @@
       <c r="Q40" t="n">
         <v>0.06956371665000916</v>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>41</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -43498,16 +43742,22 @@
       <c r="Q41" t="n">
         <v>0.1004216983766839</v>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>14</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -43583,10 +43833,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>30</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -43654,16 +43911,22 @@
       <c r="Q43" t="n">
         <v>0.04825045049470356</v>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>24</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -43731,16 +43994,22 @@
       <c r="Q44" t="n">
         <v>0.06119251251220703</v>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>32</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -43816,10 +44085,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>18</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -43887,16 +44163,22 @@
       <c r="Q46" t="n">
         <v>0.02818727493286133</v>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>21</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -43964,16 +44246,22 @@
       <c r="Q47" t="n">
         <v>0.1898203492164612</v>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>22</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -44041,16 +44329,22 @@
       <c r="Q48" t="n">
         <v>0.06297135353088379</v>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="T48" t="n">
+        <v>24</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -44118,16 +44412,22 @@
       <c r="Q49" t="n">
         <v>0.1082334080755999</v>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>16</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -44195,16 +44495,22 @@
       <c r="Q50" t="n">
         <v>0.04983609914779663</v>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>44</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -44272,16 +44578,22 @@
       <c r="Q51" t="n">
         <v>0.1173096299171448</v>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>9</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -44349,16 +44661,22 @@
       <c r="Q52" t="n">
         <v>0.02297943830490112</v>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>18</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -44426,16 +44744,22 @@
       <c r="Q53" t="n">
         <v>-0.01972323656082153</v>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="T53" t="n">
+        <v>31</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -44503,16 +44827,22 @@
       <c r="Q54" t="n">
         <v>0.1710996031761169</v>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>19</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -44580,16 +44910,22 @@
       <c r="Q55" t="n">
         <v>0.03722310066223145</v>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="T55" t="n">
+        <v>20</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -44657,16 +44993,22 @@
       <c r="Q56" t="n">
         <v>-0.003639331924805922</v>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>23</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -44734,16 +45076,22 @@
       <c r="Q57" t="n">
         <v>0.1660110950469971</v>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -44811,16 +45159,22 @@
       <c r="Q58" t="n">
         <v>0.01543748378753662</v>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="T58" t="n">
+        <v>27</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -44888,16 +45242,22 @@
       <c r="Q59" t="n">
         <v>-0.01634371280670166</v>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>13</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -44965,16 +45325,22 @@
       <c r="Q60" t="n">
         <v>0.0931662917137146</v>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>17</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -45042,16 +45408,22 @@
       <c r="Q61" t="n">
         <v>0.2234598398208618</v>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="T61" t="n">
+        <v>26</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -45119,16 +45491,22 @@
       <c r="Q62" t="n">
         <v>-0.001644790172576904</v>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="T62" t="n">
+        <v>21</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -45196,16 +45574,22 @@
       <c r="Q63" t="n">
         <v>0.03661516734531944</v>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -45281,10 +45665,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="T64" t="n">
+        <v>23</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -45352,16 +45743,22 @@
       <c r="Q65" t="n">
         <v>-0.00554811954498291</v>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="T65" t="n">
+        <v>21</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -45429,16 +45826,22 @@
       <c r="Q66" t="n">
         <v>0.04562869668006897</v>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="T66" t="n">
+        <v>16</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -45514,10 +45917,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="T67" t="n">
+        <v>11</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -45593,10 +46003,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="T68" t="n">
+        <v>27</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -45664,16 +46081,22 @@
       <c r="Q69" t="n">
         <v>0.04414272308349609</v>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="T69" t="n">
+        <v>29</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -45741,16 +46164,22 @@
       <c r="Q70" t="n">
         <v>0.1007047295570374</v>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="T70" t="n">
+        <v>14</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -45818,16 +46247,22 @@
       <c r="Q71" t="n">
         <v>0.06956371665000916</v>
       </c>
-      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="T71" t="n">
+        <v>41</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -45895,16 +46330,22 @@
       <c r="Q72" t="n">
         <v>-0.02195602655410767</v>
       </c>
-      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="T72" t="n">
+        <v>24</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -45972,16 +46413,22 @@
       <c r="Q73" t="n">
         <v>0.03065532445907593</v>
       </c>
-      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="T73" t="n">
+        <v>30</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -46049,16 +46496,22 @@
       <c r="Q74" t="n">
         <v>0.06119251251220703</v>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="T74" t="n">
+        <v>32</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -46126,16 +46579,22 @@
       <c r="Q75" t="n">
         <v>0.09263765811920166</v>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
+      <c r="T75" t="n">
+        <v>18</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -46203,16 +46662,22 @@
       <c r="Q76" t="n">
         <v>0.1898203492164612</v>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="T76" t="n">
+        <v>22</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -46280,16 +46745,22 @@
       <c r="Q77" t="n">
         <v>0.02818727493286133</v>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="T77" t="n">
+        <v>21</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -46357,16 +46828,22 @@
       <c r="Q78" t="n">
         <v>0.09042280912399292</v>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="T78" t="n">
+        <v>16</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -46434,16 +46911,22 @@
       <c r="Q79" t="n">
         <v>0.06297135353088379</v>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="T79" t="n">
+        <v>24</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -46511,16 +46994,22 @@
       <c r="Q80" t="n">
         <v>0.1173096299171448</v>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="T80" t="n">
+        <v>9</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -46588,16 +47077,22 @@
       <c r="Q81" t="n">
         <v>0.04983609914779663</v>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="T81" t="n">
+        <v>44</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -46665,16 +47160,22 @@
       <c r="Q82" t="n">
         <v>0.02297943830490112</v>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="T82" t="n">
+        <v>18</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -46742,16 +47243,22 @@
       <c r="Q83" t="n">
         <v>-0.01972323656082153</v>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="T83" t="n">
+        <v>31</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -46819,16 +47326,22 @@
       <c r="Q84" t="n">
         <v>0.1710996031761169</v>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="T84" t="n">
+        <v>19</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -46896,16 +47409,22 @@
       <c r="Q85" t="n">
         <v>0.03722310066223145</v>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="T85" t="n">
+        <v>20</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -46973,16 +47492,22 @@
       <c r="Q86" t="n">
         <v>0.02484658360481262</v>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="T86" t="n">
+        <v>23</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -47050,16 +47575,22 @@
       <c r="Q87" t="n">
         <v>0.1660110950469971</v>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="T87" t="n">
+        <v>4</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -47127,16 +47658,22 @@
       <c r="Q88" t="n">
         <v>0.01543748378753662</v>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="T88" t="n">
+        <v>27</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -47204,16 +47741,22 @@
       <c r="Q89" t="n">
         <v>-0.01634371280670166</v>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="T89" t="n">
+        <v>13</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -47281,16 +47824,22 @@
       <c r="Q90" t="n">
         <v>0.0931662917137146</v>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="T90" t="n">
+        <v>17</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -47358,16 +47907,22 @@
       <c r="Q91" t="n">
         <v>0.2234598398208618</v>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
+      <c r="T91" t="n">
+        <v>26</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -47435,16 +47990,22 @@
       <c r="Q92" t="n">
         <v>0.03815823793411255</v>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+      <c r="T92" t="n">
+        <v>24</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -47512,16 +48073,22 @@
       <c r="Q93" t="n">
         <v>-0.001644790172576904</v>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
+      <c r="T93" t="n">
+        <v>21</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -47589,16 +48156,22 @@
       <c r="Q94" t="n">
         <v>-0.00554811954498291</v>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
+      <c r="T94" t="n">
+        <v>21</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -47666,16 +48239,22 @@
       <c r="Q95" t="n">
         <v>0.09287166595458984</v>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="T95" t="n">
+        <v>23</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -47743,16 +48322,22 @@
       <c r="Q96" t="n">
         <v>0.2489994466304779</v>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="T96" t="n">
+        <v>11</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -47820,16 +48405,22 @@
       <c r="Q97" t="n">
         <v>0.04562869668006897</v>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+      <c r="T97" t="n">
+        <v>16</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -47897,16 +48488,22 @@
       <c r="Q98" t="n">
         <v>0.04414272308349609</v>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+      <c r="T98" t="n">
+        <v>29</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -47974,16 +48571,22 @@
       <c r="Q99" t="n">
         <v>0.08068996667861938</v>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
+      <c r="T99" t="n">
+        <v>27</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -48051,16 +48654,22 @@
       <c r="Q100" t="n">
         <v>0.1200210750102997</v>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
+      <c r="T100" t="n">
+        <v>19</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37092,7 +37092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37442,6 +37442,83 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021136</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Shesterkin</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8478048</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5843603014945984</v>
+      </c>
+      <c r="N5" t="n">
+        <v>16.87206029891968</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.07940980644509343</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -36970,7 +36970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37397,6 +37397,83 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021145</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G6" t="n">
+        <v>102</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26.79999923706055</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3651619553565979</v>
+      </c>
+      <c r="N6" t="n">
+        <v>26.96760940551758</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1397885382175446</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,47 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-25" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-24" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-23" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-22" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-21" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-20" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-03-26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-03-25" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-03-24" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-03-23" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-03-22" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-03-21" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-03-20" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-03-19" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-03-18" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-03-17" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-03-16" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-03-15" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-03-14" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-03-13" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-03-12" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-03-11" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-03-10" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-03-09" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-03-07" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-03-06" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-03-05" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-03-04" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-03-03" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-03-02" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-03-01" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-02-28" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-02-27" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-02-26" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="2026-02-25" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="2026-02-05" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="2026-02-04" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2026-02-03" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="2026-02-02" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="2026-02-01" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36957,7 +36957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38162,6 +38162,314 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021140</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wallstedt</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8482661</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5034285187721252</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6857037544250488</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.01323244034075266</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021137</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>102</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3072288334369659</v>
+      </c>
+      <c r="N17" t="n">
+        <v>38.55423331260681</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1372156110074785</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021143</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Askarov</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8482137</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3756062686443329</v>
+      </c>
+      <c r="N18" t="n">
+        <v>24.87874627113342</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.08522322444322472</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021144</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Markstrom</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8474593</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4058224558830261</v>
+      </c>
+      <c r="N19" t="n">
+        <v>18.83550882339478</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.06587565732452105</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -36957,7 +36957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38162,6 +38162,853 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021140</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wallstedt</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8482661</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>25.79999923706055</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5631794333457947</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12.63588714599609</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02189505100250244</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021137</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>102</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3606036007404327</v>
+      </c>
+      <c r="N17" t="n">
+        <v>27.87928009033203</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.08384084701538086</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021145</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Blackwood</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8478406</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4512533247470856</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.749335289001465</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.02493715286254883</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021143</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Askarov</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8482137</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4334280490875244</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13.31439018249512</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.02740144729614258</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021144</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Markstrom</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8474593</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23.29999923706055</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4648329019546509</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.033419609069824</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.006865203380584717</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021146</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Vanecek</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8477970</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5681180357933044</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.62360763549805</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.03323429822921753</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025021146</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.462631493806839</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7.473701477050781</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.02997934818267822</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025021147</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cooley</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8482445</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.339826226234436</v>
+      </c>
+      <c r="N23" t="n">
+        <v>32.03475570678711</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.136364221572876</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021148</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6142014265060425</v>
+      </c>
+      <c r="N24" t="n">
+        <v>22.84028625488281</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.08368498086929321</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021148</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5578325390815735</v>
+      </c>
+      <c r="N25" t="n">
+        <v>11.56650733947754</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.02731609344482422</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021149</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lankinen</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8480947</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.388818770647049</v>
+      </c>
+      <c r="N26" t="n">
+        <v>22.23624610900879</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.0698968768119812</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -36958,7 +36958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39164,6 +39164,83 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2025021142</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ersson</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>101</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8481035</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5941640138626099</v>
+      </c>
+      <c r="N29" t="n">
+        <v>18.83280181884766</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.0966515839099884</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -36958,7 +36958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39241,6 +39241,314 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2025021141</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>23.29999923706055</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.4527040719985962</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9.459185600280762</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>-0.002253592014312744</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2025021141</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4199078381061554</v>
+      </c>
+      <c r="N31" t="n">
+        <v>16.0184326171875</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.03880780935287476</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2025021139</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Grubauer</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G32" t="n">
+        <v>101</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8475831</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.6175904273986816</v>
+      </c>
+      <c r="N32" t="n">
+        <v>23.51808547973633</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.06401902437210083</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2025021139</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>103</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>22.39999961853027</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.4770855307579041</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.582893848419189</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>-0.01552531123161316</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -38222,9 +38222,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -38299,9 +38307,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -38376,9 +38392,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>33</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37898,7 +37898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38402,6 +38402,237 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021165</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4227294623851776</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15.4541072845459</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.04238677024841309</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021152</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G8" t="n">
+        <v>101</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.445372074842453</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.92558479309082</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.05711546540260315</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021163</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4616363346576691</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7.672733306884766</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.0008068084716796875</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37898,7 +37898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38402,6 +38402,545 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021163</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4616363346576691</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.672733306884766</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.0008068084716796875</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021165</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4227294623851776</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15.4541072845459</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.04238677024841309</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021161</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fowler</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8484170</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3324140608310699</v>
+      </c>
+      <c r="N9" t="n">
+        <v>33.51718902587891</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1626354455947876</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021160</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Woll</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G10" t="n">
+        <v>102</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8479361</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4005590081214905</v>
+      </c>
+      <c r="N10" t="n">
+        <v>19.88819885253906</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.104391485452652</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025021152</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Reimer</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8473503</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>22</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4008736312389374</v>
+      </c>
+      <c r="N11" t="n">
+        <v>19.82527351379395</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.09417581558227539</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021152</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3939701318740845</v>
+      </c>
+      <c r="N12" t="n">
+        <v>21.20597457885742</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05851852893829346</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021153</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G13" t="n">
+        <v>102</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3788540065288544</v>
+      </c>
+      <c r="N13" t="n">
+        <v>24.22919845581055</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1260964572429657</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37898,7 +37898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38941,6 +38941,83 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021165</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.4227294623851776</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.4541072845459</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0489686131477356</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37885,7 +37885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40024,6 +40024,391 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021157</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G28" t="n">
+        <v>105</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5711036324501038</v>
+      </c>
+      <c r="N28" t="n">
+        <v>14.22072601318359</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.007784843444824219</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2025021156</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.4325841665267944</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13.48316669464111</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.0199044942855835</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2025021155</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Gustavsson</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F30" t="n">
+        <v>102</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8479406</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.2512136995792389</v>
+      </c>
+      <c r="N30" t="n">
+        <v>49.75725936889648</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1932307481765747</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2025021155</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>25.70000076293945</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.335680216550827</v>
+      </c>
+      <c r="N31" t="n">
+        <v>32.86395645141602</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.1569305658340454</v>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2025021157</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Markstrom</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8474593</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>26.70000076293945</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.3373665511608124</v>
+      </c>
+      <c r="N32" t="n">
+        <v>32.52669143676758</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.1151220798492432</v>
+      </c>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37885,7 +37885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40409,6 +40409,160 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2025021164</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.5201260447502136</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.025208950042725</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>-0.01475769281387329</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2025021166</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>20.89999961853027</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.3762874007225037</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24.74251937866211</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.09990304708480835</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -37885,7 +37885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40409,6 +40409,314 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2025021162</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>102</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>28.10000038146973</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.4123566150665283</v>
+      </c>
+      <c r="N33" t="n">
+        <v>17.52867698669434</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.09259387850761414</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2025021166</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hill</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8478499</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>20.89999961853027</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.3762874007225037</v>
+      </c>
+      <c r="N34" t="n">
+        <v>24.74251937866211</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.09990304708480835</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2025021162</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Blackwood</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8478406</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>20.60000038146973</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3238889276981354</v>
+      </c>
+      <c r="N35" t="n">
+        <v>35.22221374511719</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.1434008479118347</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2025021164</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.5201260447502136</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4.025208950042725</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>-0.01475769281387329</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -38077,9 +38077,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -38154,9 +38162,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>35</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -38233,9 +38249,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8771929824561404</v>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -38312,9 +38336,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>-1</v>
+      </c>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -38389,9 +38421,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>33</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -38466,9 +38506,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>32</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -38543,9 +38591,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>31</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -38622,9 +38678,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>23</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0.9803921568627452</v>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -38699,9 +38763,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>33</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -38776,9 +38848,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>23</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -38853,9 +38933,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>26</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -38930,9 +39018,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>19</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -39009,9 +39105,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>23</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -39088,9 +39192,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>-1</v>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -39165,9 +39277,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>31</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -39242,9 +39362,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>22</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -39319,9 +39447,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>33</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -39396,9 +39532,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>17</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -39473,9 +39617,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>29</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -39552,9 +39704,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>30</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>-1</v>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -39629,9 +39789,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>29</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -39708,9 +39876,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>11</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0.8333333333333335</v>
+      </c>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -39787,9 +39963,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>20</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0.925925925925926</v>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -39866,9 +40050,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>30</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>-1</v>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -39943,9 +40135,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>30</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -40020,9 +40220,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>25</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -40097,9 +40305,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>17</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -40174,9 +40390,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -40251,9 +40475,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>25</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
       <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -40328,9 +40560,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>31</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -40405,9 +40645,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>29</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
       <c r="W32" t="inlineStr"/>
     </row>
   </sheetData>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -39660,7 +39660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40164,6 +40164,83 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021170</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4185842871665955</v>
+      </c>
+      <c r="N7" t="n">
+        <v>16.28314208984375</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.08141571283340454</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -39660,7 +39660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40164,6 +40164,160 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021171</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G7" t="n">
+        <v>104</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6653375029563904</v>
+      </c>
+      <c r="N7" t="n">
+        <v>33.06750106811523</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1058661341667175</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021172</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ersson</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8481035</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4540565609931946</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.188688278198242</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.03855425119400024</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -38656,7 +38656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38852,6 +38852,314 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025021173</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3244228065013885</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35.11544036865234</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1517676115036011</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025021173</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3759295344352722</v>
+      </c>
+      <c r="N4" t="n">
+        <v>24.8140926361084</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1118753552436829</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021174</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5070978999137878</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.419579982757568</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.002147376537322998</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021174</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>28.89999961853027</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1802056878805161</v>
+      </c>
+      <c r="N6" t="n">
+        <v>63.95885848999023</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2785099148750305</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -38656,7 +38656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38852,6 +38852,314 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025021173</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3759295344352722</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24.8140926361084</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1118753552436829</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025021173</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3244228065013885</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35.11544036865234</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1517676115036011</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021174</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28.89999961853027</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1802056878805161</v>
+      </c>
+      <c r="N5" t="n">
+        <v>63.95885848999023</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2785099148750305</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021174</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>103</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5070978999137878</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.419579982757568</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01448705792427063</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -38656,7 +38656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38852,6 +38852,622 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025021173</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3759295344352722</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24.8140926361084</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1118753552436829</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2025021173</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3244228065013885</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35.11544036865234</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1517676115036011</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021174</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>103</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5070978999137878</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.419579982757568</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01448705792427063</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021174</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Wolf</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8481692</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>28.89999961853027</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1802056878805161</v>
+      </c>
+      <c r="N6" t="n">
+        <v>63.95885848999023</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2785099148750305</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021176</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Husso</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8478024</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21.89999961853027</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3868311643600464</v>
+      </c>
+      <c r="N7" t="n">
+        <v>22.63376617431641</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1009737253189087</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021176</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>29.70000076293945</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3459508419036865</v>
+      </c>
+      <c r="N8" t="n">
+        <v>30.8098316192627</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1191654205322266</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021177</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Askarov</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8482137</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.605582594871521</v>
+      </c>
+      <c r="N9" t="n">
+        <v>21.11651992797852</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.08177304267883301</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021177</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Hofer</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8480981</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4614397883415222</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.712042331695557</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.003676474094390869</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,51 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2026-03-30" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2026-03-29" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2026-03-28" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026-03-27" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="2026-03-26" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="2026-03-25" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="2026-03-24" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="2026-03-23" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="2026-03-22" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="2026-03-21" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="2026-03-20" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="2026-03-19" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="2026-03-18" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="2026-03-17" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="2026-03-16" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="2026-03-15" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="2026-03-14" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="2026-03-13" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="2026-03-12" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="2026-03-11" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="2026-03-10" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="2026-03-09" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="2026-03-07" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="2026-03-06" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="2026-03-05" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="2026-03-04" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="2026-03-03" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="2026-03-02" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="2026-03-01" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="2026-02-28" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="2026-02-27" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="2026-02-26" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="2026-02-25" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="2026-02-05" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="2026-02-04" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="2026-02-03" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="2026-02-02" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="2026-02-01" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-30" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-29" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-28" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-27" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-26" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-25" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-24" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-23" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-22" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-21" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-20" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,7 +55,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -84,23 +84,13 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -151,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,9 +205,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +537,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-27 11:45:34</t>
+          <t>2026-03-31 07:26:48</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -587,7 +574,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -600,7 +587,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -613,7 +600,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -640,7 +627,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -655,7 +642,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+20.20</t>
+          <t>+21.38</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -670,7 +657,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+11.95%</t>
+          <t>+11.56%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -780,19 +767,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+3.04%</t>
+          <t>+0.89%</t>
         </is>
       </c>
     </row>
@@ -803,19 +790,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>+28.77%</t>
+          <t>+34.35%</t>
         </is>
       </c>
     </row>
@@ -826,19 +813,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>17</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>+31.66%</t>
+          <t>+21.53%</t>
         </is>
       </c>
     </row>
@@ -849,19 +836,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>-6.36%</t>
+          <t>-6.57%</t>
         </is>
       </c>
     </row>
@@ -38842,16 +38829,25 @@
       <c r="Q2" t="n">
         <v>0.1681879758834839</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>21</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.970873786407767</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38919,16 +38915,22 @@
       <c r="Q3" t="n">
         <v>0.1118753552436829</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>20</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -38996,16 +38998,22 @@
       <c r="Q4" t="n">
         <v>0.1517676115036011</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>21</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39073,16 +39081,22 @@
       <c r="Q5" t="n">
         <v>0.01448705792427063</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>27</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39150,16 +39164,25 @@
       <c r="Q6" t="n">
         <v>0.2785099148750305</v>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>12</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>1.694915254237288</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39227,16 +39250,22 @@
       <c r="Q7" t="n">
         <v>0.1009737253189087</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>23</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39304,16 +39333,25 @@
       <c r="Q8" t="n">
         <v>0.1191654205322266</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>28</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0.8695652173913042</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39381,16 +39419,22 @@
       <c r="Q9" t="n">
         <v>0.08177304267883301</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>22</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39458,16 +39502,22 @@
       <c r="Q10" t="n">
         <v>0.003676474094390869</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>24</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -68178,124 +68228,124 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>game_date</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>game_id</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>goalie_name</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>betting_line</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>line_over</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>line_under</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>goalie_id</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>team_abbrev</t>
         </is>
       </c>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>opponent_team</t>
         </is>
       </c>
-      <c r="K1" s="23" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>is_home</t>
         </is>
       </c>
-      <c r="L1" s="23" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>predicted_saves</t>
         </is>
       </c>
-      <c r="M1" s="23" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>prob_over</t>
         </is>
       </c>
-      <c r="N1" s="23" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>confidence_pct</t>
         </is>
       </c>
-      <c r="O1" s="23" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>confidence_bucket</t>
         </is>
       </c>
-      <c r="P1" s="23" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>recommendation</t>
         </is>
       </c>
-      <c r="Q1" s="23" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>ev</t>
         </is>
       </c>
-      <c r="R1" s="23" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>bet_amount</t>
         </is>
       </c>
-      <c r="S1" s="23" t="inlineStr">
+      <c r="S1" s="10" t="inlineStr">
         <is>
           <t>bet_selection</t>
         </is>
       </c>
-      <c r="T1" s="23" t="inlineStr">
+      <c r="T1" s="10" t="inlineStr">
         <is>
           <t>actual_saves</t>
         </is>
       </c>
-      <c r="U1" s="23" t="inlineStr">
+      <c r="U1" s="10" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="V1" s="23" t="inlineStr">
+      <c r="V1" s="10" t="inlineStr">
         <is>
           <t>profit_loss</t>
         </is>
       </c>
-      <c r="W1" s="23" t="inlineStr">
+      <c r="W1" s="10" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -68723,7 +68773,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -1,52 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-31" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-30" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-29" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-28" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-27" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-26" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-25" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-24" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-23" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-22" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-21" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-20" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-19" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-18" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-17" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-16" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-15" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-14" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-13" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-12" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-11" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-10" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-09" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-07" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-06" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-05" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-04" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-03" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-02" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-03-01" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-28" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-27" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-26" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-25" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-05" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-04" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-03" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-02" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-02-01" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-03-31" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-03-30" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-03-29" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-03-28" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-03-27" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-03-26" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-03-25" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-03-24" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-03-23" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-03-22" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-03-21" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-03-20" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-03-19" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-03-18" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-03-17" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-03-16" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-03-15" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-03-14" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-03-13" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-03-12" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-03-11" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-03-10" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-03-09" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-03-07" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-03-06" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-03-05" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-03-04" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-03-03" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="2026-03-02" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="2026-03-01" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="2026-02-28" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2026-02-27" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="2026-02-26" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="2026-02-25" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="2026-02-05" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="2026-02-04" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="2026-02-03" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="2026-02-02" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="2026-02-01" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44772,7 +44772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45588,6 +45588,699 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025021178</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Korpisalo</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8476914</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2662003934383392</v>
+      </c>
+      <c r="N11" t="n">
+        <v>46.75992202758789</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2337995767593384</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021180</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.4451220333576202</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10.97559356689453</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.02657610177993774</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021180</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3370403349399567</v>
+      </c>
+      <c r="N13" t="n">
+        <v>32.59193420410156</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1391501426696777</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021182</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Shesterkin</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8478048</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>27.10000038146973</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.4221058785915375</v>
+      </c>
+      <c r="N14" t="n">
+        <v>15.57882404327393</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.03872358798980713</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021181</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G15" t="n">
+        <v>101</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4507530033588409</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.849399566650391</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.05173459649085999</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021184</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.10000038146973</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4279305636882782</v>
+      </c>
+      <c r="N16" t="n">
+        <v>14.41388702392578</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.04825985431671143</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021185</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>26.60000038146973</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3253508508205414</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34.92982864379883</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1508395671844482</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021185</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.89999961853027</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3882698714733124</v>
+      </c>
+      <c r="N18" t="n">
+        <v>22.34602546691895</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.09482187032699585</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021186</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>101</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8481519</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.3186401426792145</v>
+      </c>
+      <c r="N19" t="n">
+        <v>36.27197265625</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1277884840965271</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -44772,7 +44772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46599,6 +46599,391 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021179</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sorokin</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8478009</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NYI</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2221478819847107</v>
+      </c>
+      <c r="N24" t="n">
+        <v>55.5704231262207</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2386816143989563</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021183</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.258517324924469</v>
+      </c>
+      <c r="N25" t="n">
+        <v>48.29653549194336</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.2131807804107666</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021181</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4507530033588409</v>
+      </c>
+      <c r="N26" t="n">
+        <v>9.849399566650391</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.04185783863067627</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2025021186</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>102</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8481519</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.60000038146973</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.3186401426792145</v>
+      </c>
+      <c r="N27" t="n">
+        <v>36.27197265625</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1258043050765991</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021186</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.5318290591239929</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6.365811824798584</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.01259827613830566</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -44964,9 +44964,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -45041,9 +45049,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -45120,9 +45136,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>22</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>-2</v>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -45199,9 +45223,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>11</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>1.739130434782608</v>
+      </c>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -45276,9 +45308,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>25</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -45355,9 +45395,17 @@
           <t>OVER</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>18</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -45432,9 +45480,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -45509,9 +45565,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>23</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -45586,9 +45650,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>12</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -45663,9 +45735,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>17</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -45742,9 +45822,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>13</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -45819,9 +45907,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>36</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -45898,9 +45994,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>19</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0.9090909090909092</v>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -45975,9 +46079,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>22</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -46052,9 +46164,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>11</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -46129,9 +46249,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -46208,9 +46336,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>26</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.9090909090909092</v>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
@@ -46285,9 +46421,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>23</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -46364,9 +46508,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>20</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8064516129032258</v>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -46441,9 +46593,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>27</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -46518,9 +46678,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>22</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -46595,9 +46763,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -46672,9 +46848,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>29</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -46749,9 +46933,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>11</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -46826,9 +47018,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>11</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -46903,9 +47103,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>20</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
       <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -46980,9 +47188,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>18</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
   </sheetData>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-03-31 07:26:48</t>
+          <t>2026-04-02 07:51:58</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+21.38</t>
+          <t>+27.23</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+11.56%</t>
+          <t>+13.75%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+2.20%</t>
         </is>
       </c>
     </row>
@@ -792,19 +792,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>+34.35%</t>
+          <t>+35.96%</t>
         </is>
       </c>
     </row>
@@ -815,19 +815,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>+21.53%</t>
+          <t>+23.49%</t>
         </is>
       </c>
     </row>
@@ -44948,16 +44948,22 @@
       <c r="Q2" t="n">
         <v>0.08500194549560547</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>13</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -45026,17 +45032,24 @@
         <v>0.102674663066864</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>1.694915254237288</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -45105,17 +45118,24 @@
         <v>0.122144877910614</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>17</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>1.785714285714286</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -45183,16 +45203,22 @@
       <c r="Q5" t="n">
         <v>0.008401274681091309</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>28</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -45260,16 +45286,22 @@
       <c r="Q6" t="n">
         <v>0.02387911081314087</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>24</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -45337,16 +45369,22 @@
       <c r="Q7" t="n">
         <v>0.09191769361495972</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>23</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -46369,7 +46369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47264,6 +47264,853 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021192</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Skinner</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8479973</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5301843285560608</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.036865711212158</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.01527023315429688</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021193</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4677119255065918</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.457614898681641</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02733755111694336</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021191</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Luukkonen</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8480045</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.10000038146973</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.4152154326438904</v>
+      </c>
+      <c r="N14" t="n">
+        <v>16.95691299438477</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.06787633895874023</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021196</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>23.70000076293945</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.541120707988739</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8.224142074584961</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.0001636743545532227</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021196</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ersson</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8481035</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4601620733737946</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.967585563659668</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02764284610748291</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021194</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1677803844213486</v>
+      </c>
+      <c r="N17" t="n">
+        <v>66.44392395019531</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3248304128646851</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021198</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>23.29999923706055</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4637311398983002</v>
+      </c>
+      <c r="N18" t="n">
+        <v>7.253771781921387</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.005752384662628174</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021198</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.79999923706055</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5630559325218201</v>
+      </c>
+      <c r="N19" t="n">
+        <v>12.61118698120117</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0176013708114624</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021200</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8477465</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.10000038146973</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6267138123512268</v>
+      </c>
+      <c r="N20" t="n">
+        <v>25.3427619934082</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1029042601585388</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021199</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tolopilo</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8484268</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>27.60000038146973</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5297555327415466</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5.951106548309326</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.01569902896881104</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025021202</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>22.79999923706055</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5530027151107788</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10.60054302215576</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.005491375923156738</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -46369,7 +46369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48111,6 +48111,83 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025021197</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Merzlikins</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8478007</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3052873313426971</v>
+      </c>
+      <c r="N23" t="n">
+        <v>38.94253540039062</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1897621154785156</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -46369,7 +46369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:W37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48889,6 +48889,391 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2025021196</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Gibson</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>102</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8476434</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>23.70000076293945</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.541120707988739</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8.224142074584961</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>-0.01443487405776978</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2025021200</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F34" t="n">
+        <v>103</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-125</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8481519</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>27.29999923706055</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2555769979953766</v>
+      </c>
+      <c r="N34" t="n">
+        <v>48.88460159301758</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.188867449760437</v>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2025021203</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.5002678036689758</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.05356073379516602</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>-0.01664042472839355</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2025021204</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Kuemper</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G36" t="n">
+        <v>104</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8475311</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.3953443467617035</v>
+      </c>
+      <c r="N36" t="n">
+        <v>20.93113136291504</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.1144595444202423</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2025021204</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Saros</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G37" t="n">
+        <v>100</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8477424</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>25.79999923706055</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5592069625854492</v>
+      </c>
+      <c r="N37" t="n">
+        <v>11.84139251708984</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.009657442569732666</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-04-02 07:51:58</t>
+          <t>2026-04-03 12:51:58</t>
         </is>
       </c>
       <c r="C3" s="5" t="n"/>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="5" t="n"/>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C11" s="5" t="n"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>+27.23</t>
+          <t>+30.95</t>
         </is>
       </c>
       <c r="C12" s="5" t="n"/>
@@ -660,7 +660,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>+13.75%</t>
+          <t>+14.74%</t>
         </is>
       </c>
       <c r="C13" s="5" t="n"/>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>19</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>+2.20%</t>
+          <t>+0.24%</t>
         </is>
       </c>
     </row>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>+35.96%</t>
+          <t>+38.25%</t>
         </is>
       </c>
     </row>
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>+23.49%</t>
+          <t>+17.61%</t>
         </is>
       </c>
     </row>
@@ -839,19 +839,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>+4.94%</t>
         </is>
       </c>
     </row>
@@ -46563,10 +46563,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>28</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -46642,10 +46649,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>31</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -46713,16 +46727,22 @@
       <c r="Q4" t="n">
         <v>0.08542484045028687</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>30</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -46790,16 +46810,22 @@
       <c r="Q5" t="n">
         <v>-0.0006434917449951172</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -46875,10 +46901,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>21</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9090909090909092</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -46946,16 +46979,22 @@
       <c r="Q7" t="n">
         <v>0.0008699893951416016</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>21</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -47023,16 +47062,22 @@
       <c r="Q8" t="n">
         <v>0.07592189311981201</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -47100,16 +47145,22 @@
       <c r="Q9" t="n">
         <v>-0.02473840117454529</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>22</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -47177,16 +47228,22 @@
       <c r="Q10" t="n">
         <v>0.006034135818481445</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>29</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -47254,16 +47311,22 @@
       <c r="Q11" t="n">
         <v>0.01682335138320923</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>21</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -47331,16 +47394,22 @@
       <c r="Q12" t="n">
         <v>-0.01527023315429688</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="T12" t="n">
+        <v>27</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -47408,16 +47477,22 @@
       <c r="Q13" t="n">
         <v>0.02733755111694336</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="T13" t="n">
+        <v>22</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -47485,16 +47560,22 @@
       <c r="Q14" t="n">
         <v>0.06787633895874023</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>20</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -47562,16 +47643,22 @@
       <c r="Q15" t="n">
         <v>-0.0001636743545532227</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>32</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -47639,16 +47726,22 @@
       <c r="Q16" t="n">
         <v>0.02764284610748291</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>15</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -47717,17 +47810,24 @@
         <v>0.3248304128646851</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>23</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>2.912621359223301</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -47795,16 +47895,22 @@
       <c r="Q18" t="n">
         <v>0.005752384662628174</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>18</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47872,16 +47978,22 @@
       <c r="Q19" t="n">
         <v>0.0176013708114624</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>22</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47949,16 +48061,22 @@
       <c r="Q20" t="n">
         <v>0.1029042601585388</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>17</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48026,16 +48144,22 @@
       <c r="Q21" t="n">
         <v>-0.01569902896881104</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>34</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48103,16 +48227,22 @@
       <c r="Q22" t="n">
         <v>0.005491375923156738</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>19</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -48188,10 +48318,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>16</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>1.96078431372549</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -48259,16 +48396,22 @@
       <c r="Q24" t="n">
         <v>0.05616855621337891</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>25</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -48336,16 +48479,22 @@
       <c r="Q25" t="n">
         <v>-0.02523383498191833</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>27</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -48413,16 +48562,22 @@
       <c r="Q26" t="n">
         <v>0.03723856806755066</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>22</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -48490,16 +48645,22 @@
       <c r="Q27" t="n">
         <v>0.06787765026092529</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>22</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -48567,16 +48728,22 @@
       <c r="Q28" t="n">
         <v>0.04996904730796814</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>22</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -48652,10 +48819,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>32</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -48723,16 +48897,22 @@
       <c r="Q30" t="n">
         <v>0.08965235948562622</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>19</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -48808,10 +48988,17 @@
           <t>UNDER</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>28</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -48879,16 +49066,25 @@
       <c r="Q32" t="n">
         <v>0.1824104785919189</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>21</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>1.941747572815534</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -48956,16 +49152,22 @@
       <c r="Q33" t="n">
         <v>-0.01443487405776978</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>32</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -49033,16 +49235,22 @@
       <c r="Q34" t="n">
         <v>0.188867449760437</v>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>32</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -49110,16 +49318,22 @@
       <c r="Q35" t="n">
         <v>-0.01664042472839355</v>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>25</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -49187,16 +49401,22 @@
       <c r="Q36" t="n">
         <v>0.1144595444202423</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>30</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -49264,16 +49484,22 @@
       <c r="Q37" t="n">
         <v>0.009657442569732666</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>29</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -46449,9 +46449,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -46526,9 +46534,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>21</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -46603,9 +46619,17 @@
           <t>NONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>23</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" t="inlineStr"/>
     </row>
   </sheetData>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -48210,7 +48210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48868,6 +48868,468 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021215</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hellebuyck</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>105</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8476945</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.70000076293945</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3452522158622742</v>
+      </c>
+      <c r="N9" t="n">
+        <v>30.94955635070801</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.09142899513244629</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021212</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>21.79999923706055</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3623945713043213</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27.52108573913574</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1137958765029907</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025021220</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Askarov</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8482137</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>24.29999923706055</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4649761021137238</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.004779815673828</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0001401901245117188</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021221</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Grubauer</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8475831</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5878669023513794</v>
+      </c>
+      <c r="N12" t="n">
+        <v>17.57337951660156</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.08291637897491455</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021218</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>23.60000038146973</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.314822643995285</v>
+      </c>
+      <c r="N13" t="n">
+        <v>37.03547286987305</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1502935886383057</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021209</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DeSmith</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8479193</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2877406179904938</v>
+      </c>
+      <c r="N14" t="n">
+        <v>42.45187759399414</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1817429661750793</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -48210,7 +48210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49330,6 +49330,237 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021209</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.5332468152046204</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.649363040924072</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.02829629182815552</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021219</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cooley</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8482445</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27.60000038146973</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5182396769523621</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.647935390472412</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.01006221771240234</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021221</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Soderblom</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8482821</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4404516220092773</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11.90967559814453</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.03573882579803467</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -48210,7 +48210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49330,6 +49330,391 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021221</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Soderblom</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8482821</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.20000076293945</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4404516220092773</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11.90967559814453</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.03573882579803467</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025021211</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Silovs</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8481668</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4527846872806549</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9.443062782287598</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02340579032897949</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021211</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bobrovsky</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8475683</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2993879616260529</v>
+      </c>
+      <c r="N17" t="n">
+        <v>40.12240600585938</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1551575064659119</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021220</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Saros</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8477424</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.39999961853027</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4782436490058899</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.351270198822021</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.02369821071624756</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021219</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Cooley</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8482445</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.60000038146973</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5182396769523621</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.647935390472412</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.01006221771240234</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -48197,7 +48197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50020,6 +50020,391 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021215</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>103</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.60000038146973</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5270569324493408</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.411386489868164</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.01966777443885803</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021216</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vejmelka</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-107</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8478872</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5736033916473389</v>
+      </c>
+      <c r="N25" t="n">
+        <v>14.72067832946777</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.05669516324996948</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021212</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.10000038146973</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4149432182312012</v>
+      </c>
+      <c r="N26" t="n">
+        <v>17.01135635375977</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.06124722957611084</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2025021216</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tolopilo</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8484268</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5700428485870361</v>
+      </c>
+      <c r="N27" t="n">
+        <v>14.00856971740723</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.04174095392227173</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021217</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kuemper</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-112</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8475311</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>LAK</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.4765485525131226</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.690289497375488</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>-0.0003581047058105469</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -43619,7 +43619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44200,6 +44200,83 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021231</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-118</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>21.70000076293945</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.542755663394928</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8.551132202148438</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.03056055307388306</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45199,7 +45199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46481,6 +46481,237 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025021238</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-117</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H17" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4519895017147064</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.602099418640137</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.03344738483428955</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025021242</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tolopilo</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-118</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8484268</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>VGK</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5055038928985596</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.100778579711914</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.01769900321960449</v>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025021238</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-102</v>
+      </c>
+      <c r="H19" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4519895017147064</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.602099418640137</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.04305994510650635</v>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45199,7 +45199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46712,6 +46712,237 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2025021241</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Jarry</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>104</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8477465</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>23</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.4090677797794342</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18.18644332885742</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.03146088123321533</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025021240</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wallstedt</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G21" t="n">
+        <v>104</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8482661</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.29999923706055</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.4683946371078491</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6.321072578430176</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.04140928387641907</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025021238</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wedgewood</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-129</v>
+      </c>
+      <c r="G22" t="n">
+        <v>105</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8475809</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.4519895017147064</v>
+      </c>
+      <c r="N22" t="n">
+        <v>9.602099418640137</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.06020557880401611</v>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45199,7 +45199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46943,6 +46943,83 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2025021236</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-103</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-121</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3767088949680328</v>
+      </c>
+      <c r="N23" t="n">
+        <v>24.6582202911377</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.07577979564666748</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45199,7 +45199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47020,6 +47020,83 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021237</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G24" t="n">
+        <v>104</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.89999961853027</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5877079963684082</v>
+      </c>
+      <c r="N24" t="n">
+        <v>17.54159927368164</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.02823662757873535</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45199,7 +45199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47020,6 +47020,468 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021236</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Markstrom</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8474593</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>22.10000038146973</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6190829873085022</v>
+      </c>
+      <c r="N24" t="n">
+        <v>23.81659698486328</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.07362842559814453</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021243</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G25" t="n">
+        <v>103</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6182534694671631</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23.65069389343262</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.0626978874206543</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021237</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bussi</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G26" t="n">
+        <v>104</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8483548</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.89999961853027</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5877079963684082</v>
+      </c>
+      <c r="N26" t="n">
+        <v>17.54159927368164</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.02823662757873535</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2025021235</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G27" t="n">
+        <v>102</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5073130130767822</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.462602615356445</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.002362519502639771</v>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2025021237</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Swayman</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>103</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8480280</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>26.79999923706055</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1657934784889221</v>
+      </c>
+      <c r="N28" t="n">
+        <v>66.84130096435547</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>75%+</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.274735152721405</v>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2025021234</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Johansson</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8477992</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.89999961853027</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.3863885700702667</v>
+      </c>
+      <c r="N29" t="n">
+        <v>22.72228622436523</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.09438067674636841</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -45199,7 +45199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47020,6 +47020,237 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2025021239</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G24" t="n">
+        <v>104</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>CGY</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5073918700218201</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.478374004364014</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.00241205096244812</v>
+      </c>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2025021243</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Dostal</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-125</v>
+      </c>
+      <c r="G25" t="n">
+        <v>103</v>
+      </c>
+      <c r="H25" t="n">
+        <v>8480843</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ANA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NSH</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6182534694671631</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23.65069389343262</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.0626978874206543</v>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2025021240</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Daccord</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8478916</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>26.39999961853027</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4839060306549072</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.218793869018555</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.005437135696411133</v>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -42308,7 +42308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42658,6 +42658,160 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021245</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3935364186763763</v>
+      </c>
+      <c r="N5" t="n">
+        <v>21.29271697998047</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.07375329732894897</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021246</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>101</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.3891740143299103</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22.16519737243652</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0572546124458313</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -42308,7 +42308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42658,6 +42658,468 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025021246</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Nedeljkovic</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-104</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8477968</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>25</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4068208336830139</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18.63583374023438</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.04772460460662842</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2025021244</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Luukkonen</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8480045</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4973961412906647</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5207717418670654</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.002603888511657715</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021246</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ingram</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-124</v>
+      </c>
+      <c r="G7" t="n">
+        <v>101</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8478971</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>SJS</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4397478401660919</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.0504322052002</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.06273975968360901</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021245</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stolarz</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G8" t="n">
+        <v>104</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8476932</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3542101681232452</v>
+      </c>
+      <c r="N8" t="n">
+        <v>29.15796661376953</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1555937826633453</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021244</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shesterkin</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-127</v>
+      </c>
+      <c r="G9" t="n">
+        <v>104</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8478048</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NYR</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2943671345710754</v>
+      </c>
+      <c r="N9" t="n">
+        <v>41.12657165527344</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>70-75%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2154367864131927</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021245</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thompson</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-108</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8480313</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>23</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3935364186763763</v>
+      </c>
+      <c r="N10" t="n">
+        <v>21.29271697998047</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.07375329732894897</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/betting_tracker.xlsx
+++ b/betting_tracker.xlsx
@@ -44654,7 +44654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45158,6 +45158,699 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025021248</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dobes</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8482487</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4191119074821472</v>
+      </c>
+      <c r="N7" t="n">
+        <v>16.1776180267334</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.07349890470504761</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2025021255</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Knight</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>101</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-124</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8481519</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>29.70000076293945</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5388286709785461</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.765734195709229</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.04131624102592468</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025021247</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Greaves</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8482982</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CBJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BUF</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.79999923706055</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5500796437263489</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10.01592826843262</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.004625082015991211</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2025021250</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vladar</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-106</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8478435</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3889172673225403</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22.2165470123291</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.07191222906112671</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2025021251</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-122</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8474596</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>NJD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>PIT</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>22.89999961853027</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3739542067050934</v>
+      </c>
+      <c r="N11" t="n">
+        <v>25.20915794372559</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>60-65%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.126045823097229</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2025021248</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vasilevskiy</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8476883</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TBL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3390340507030487</v>
+      </c>
+      <c r="N12" t="n">
+        <v>32.19319152832031</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1014945507049561</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2025021249</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ullmark</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-114</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8476999</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OTT</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>21.79999923706055</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5613469481468201</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.26939010620117</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>55-60%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.02863669395446777</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025021254</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oettinger</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8479979</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.3049263656139374</v>
+      </c>
+      <c r="N14" t="n">
+        <v>39.01472854614258</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>65-70%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>UNDER</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1735424995422363</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025021253</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Underdog</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Binnington</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-109</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8476412</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>STL</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WPG</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4922195374965668</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.556092500686646</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>50-55%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NO BET</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.02273601293563843</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
